--- a/EBAY.xlsx
+++ b/EBAY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE23655-BA7F-49C7-9160-C73D57E43788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC193735-F1AC-446C-9685-4EEF248AD76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{ED1C07FE-A50A-4536-AFF7-C55D5EA00969}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{ED1C07FE-A50A-4536-AFF7-C55D5EA00969}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -222,13 +222,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -291,28 +297,32 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -668,8 +678,8 @@
       <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2">
-        <v>92.17</v>
+      <c r="H2" s="14">
+        <v>84.016999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -677,10 +687,10 @@
         <v>14</v>
       </c>
       <c r="H3" s="3">
-        <v>457</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>41</v>
+        <v>448</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -692,7 +702,7 @@
       </c>
       <c r="H4" s="3">
         <f>+H2*H3</f>
-        <v>42121.69</v>
+        <v>37639.615999999995</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -703,11 +713,11 @@
         <v>16</v>
       </c>
       <c r="H5" s="3">
-        <f>2070+1680</f>
-        <v>3750</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>41</v>
+        <f>1867+1052</f>
+        <v>2919</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -715,11 +725,11 @@
         <v>17</v>
       </c>
       <c r="H6" s="3">
-        <f>1746+5002</f>
-        <v>6748</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>41</v>
+        <f>5996+750</f>
+        <v>6746</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -728,7 +738,7 @@
       </c>
       <c r="H7" s="3">
         <f>+H4-H5+H6</f>
-        <v>45119.69</v>
+        <v>41466.615999999995</v>
       </c>
     </row>
   </sheetData>
@@ -847,8 +857,12 @@
       <c r="L3" s="4">
         <v>134</v>
       </c>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
+      <c r="M3" s="4">
+        <v>135</v>
+      </c>
+      <c r="N3" s="4">
+        <v>135</v>
+      </c>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
@@ -861,7 +875,9 @@
       <c r="U3" s="10">
         <v>134</v>
       </c>
-      <c r="V3" s="10"/>
+      <c r="V3" s="10">
+        <v>135</v>
+      </c>
     </row>
     <row r="4" spans="1:74" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
@@ -899,8 +915,13 @@
       <c r="L4" s="3">
         <v>19514</v>
       </c>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
+      <c r="M4" s="3">
+        <v>20105</v>
+      </c>
+      <c r="N4" s="3">
+        <f>+V4-SUM(K4:M4)</f>
+        <v>18237</v>
+      </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
@@ -914,7 +935,9 @@
       <c r="U4" s="3">
         <v>74667</v>
       </c>
-      <c r="V4" s="3"/>
+      <c r="V4" s="3">
+        <v>76609</v>
+      </c>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
@@ -1012,13 +1035,13 @@
         <f t="shared" ref="L5" si="9">+L9/L4</f>
         <v>0.13989955929076561</v>
       </c>
-      <c r="M5" s="11" t="e">
+      <c r="M5" s="11">
         <f t="shared" ref="M5" si="10">+M9/M4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N5" s="11" t="e">
+        <v>0.14026361601591644</v>
+      </c>
+      <c r="N5" s="11">
         <f t="shared" ref="N5" si="11">+N9/N4</f>
-        <v>#DIV/0!</v>
+        <v>0.16258156495037562</v>
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="11" t="e">
@@ -1045,7 +1068,10 @@
         <f>+U9/U4</f>
         <v>0.13771813518689649</v>
       </c>
-      <c r="V5" s="3"/>
+      <c r="V5" s="11">
+        <f>+V9/V4</f>
+        <v>0.14489159237165347</v>
+      </c>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
@@ -1210,8 +1236,13 @@
       <c r="L7" s="3">
         <v>2248</v>
       </c>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
+      <c r="M7" s="3">
+        <v>2295</v>
+      </c>
+      <c r="N7" s="3">
+        <f>+V7-SUM(K7:M7)</f>
+        <v>2421</v>
+      </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
@@ -1225,7 +1256,9 @@
       <c r="U7" s="3">
         <v>8648</v>
       </c>
-      <c r="V7" s="3"/>
+      <c r="V7" s="3">
+        <v>9107</v>
+      </c>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
@@ -1314,8 +1347,13 @@
       <c r="L8" s="3">
         <v>482</v>
       </c>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
+      <c r="M8" s="3">
+        <v>525</v>
+      </c>
+      <c r="N8" s="3">
+        <f>+V8-SUM(K8:M8)</f>
+        <v>544</v>
+      </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
@@ -1329,7 +1367,9 @@
       <c r="U8" s="3">
         <v>1635</v>
       </c>
-      <c r="V8" s="3"/>
+      <c r="V8" s="3">
+        <v>1993</v>
+      </c>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
@@ -1419,8 +1459,13 @@
       <c r="L9" s="7">
         <v>2730</v>
       </c>
-      <c r="M9" s="7"/>
-      <c r="N9" s="3"/>
+      <c r="M9" s="7">
+        <v>2820</v>
+      </c>
+      <c r="N9" s="7">
+        <f>+V9-SUM(K9:M9)</f>
+        <v>2965</v>
+      </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
@@ -1434,7 +1479,9 @@
       <c r="U9" s="7">
         <v>10283</v>
       </c>
-      <c r="V9" s="3"/>
+      <c r="V9" s="7">
+        <v>11100</v>
+      </c>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
@@ -1524,8 +1571,13 @@
       <c r="L10" s="3">
         <v>776</v>
       </c>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
+      <c r="M10" s="3">
+        <v>821</v>
+      </c>
+      <c r="N10" s="3">
+        <f>+V10-SUM(K10:M10)</f>
+        <v>849</v>
+      </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
@@ -1539,7 +1591,9 @@
       <c r="U10" s="3">
         <v>2880</v>
       </c>
-      <c r="V10" s="3"/>
+      <c r="V10" s="3">
+        <v>3169</v>
+      </c>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
@@ -1622,7 +1676,7 @@
         <v>1837</v>
       </c>
       <c r="I11" s="3">
-        <f t="shared" ref="I11:U11" si="14">+I9-I10</f>
+        <f t="shared" ref="I11:V12" si="14">+I9-I10</f>
         <v>1849</v>
       </c>
       <c r="J11" s="3">
@@ -1639,11 +1693,11 @@
       </c>
       <c r="M11" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1999</v>
       </c>
       <c r="N11" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2116</v>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3">
@@ -1670,7 +1724,10 @@
         <f t="shared" si="14"/>
         <v>7403</v>
       </c>
-      <c r="V11" s="3"/>
+      <c r="V11" s="3">
+        <f t="shared" si="14"/>
+        <v>7931</v>
+      </c>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
@@ -1760,8 +1817,13 @@
       <c r="L12" s="3">
         <v>586</v>
       </c>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
+      <c r="M12" s="3">
+        <v>606</v>
+      </c>
+      <c r="N12" s="3">
+        <f>+V12-SUM(K12:M12)</f>
+        <v>666</v>
+      </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -1775,7 +1837,9 @@
       <c r="U12" s="3">
         <v>2319</v>
       </c>
-      <c r="V12" s="3"/>
+      <c r="V12" s="3">
+        <v>2394</v>
+      </c>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
@@ -1865,8 +1929,13 @@
       <c r="L13" s="3">
         <v>421</v>
       </c>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
+      <c r="M13" s="3">
+        <v>423</v>
+      </c>
+      <c r="N13" s="3">
+        <f>+V13-SUM(K13:M13)</f>
+        <v>436</v>
+      </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
@@ -1880,7 +1949,9 @@
       <c r="U13" s="3">
         <v>1479</v>
       </c>
-      <c r="V13" s="3"/>
+      <c r="V13" s="3">
+        <v>1642</v>
+      </c>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
@@ -1970,8 +2041,13 @@
       <c r="L14" s="3">
         <v>371</v>
       </c>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
+      <c r="M14" s="3">
+        <v>282</v>
+      </c>
+      <c r="N14" s="3">
+        <f>+V14-SUM(K14:M14)</f>
+        <v>284</v>
+      </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
@@ -1985,7 +2061,9 @@
       <c r="U14" s="3">
         <v>914</v>
       </c>
-      <c r="V14" s="3"/>
+      <c r="V14" s="3">
+        <v>1198</v>
+      </c>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
@@ -2075,8 +2153,13 @@
       <c r="L15" s="3">
         <v>86</v>
       </c>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
+      <c r="M15" s="3">
+        <v>106</v>
+      </c>
+      <c r="N15" s="3">
+        <f>+V15-SUM(K15:M15)</f>
+        <v>123</v>
+      </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
@@ -2090,7 +2173,9 @@
       <c r="U15" s="3">
         <v>353</v>
       </c>
-      <c r="V15" s="3"/>
+      <c r="V15" s="3">
+        <v>396</v>
+      </c>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
@@ -2180,8 +2265,13 @@
       <c r="L16" s="3">
         <v>6</v>
       </c>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
+      <c r="M16" s="3">
+        <v>6</v>
+      </c>
+      <c r="N16" s="3">
+        <f>+V16-SUM(K16:M16)</f>
+        <v>6</v>
+      </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
@@ -2195,7 +2285,9 @@
       <c r="U16" s="3">
         <v>20</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="3">
+        <v>24</v>
+      </c>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
@@ -2278,7 +2370,7 @@
         <v>549</v>
       </c>
       <c r="I17" s="3">
-        <f t="shared" ref="I17:U17" si="16">+I11-SUM(I12:I16)</f>
+        <f t="shared" ref="I17:V17" si="16">+I11-SUM(I12:I16)</f>
         <v>595</v>
       </c>
       <c r="J17" s="3">
@@ -2295,11 +2387,11 @@
       </c>
       <c r="M17" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="N17" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>601</v>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3">
@@ -2326,7 +2418,10 @@
         <f t="shared" si="16"/>
         <v>2318</v>
       </c>
-      <c r="V17" s="3"/>
+      <c r="V17" s="3">
+        <f t="shared" si="16"/>
+        <v>2277</v>
+      </c>
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
@@ -2416,8 +2511,13 @@
       <c r="L18" s="3">
         <v>-4</v>
       </c>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
+      <c r="M18" s="3">
+        <v>-10</v>
+      </c>
+      <c r="N18" s="3">
+        <f>+V18-SUM(K18:M18)</f>
+        <v>21</v>
+      </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
@@ -2431,7 +2531,9 @@
       <c r="U18" s="3">
         <v>-76</v>
       </c>
-      <c r="V18" s="3"/>
+      <c r="V18" s="3">
+        <v>5</v>
+      </c>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
@@ -2521,8 +2623,13 @@
       <c r="L19" s="3">
         <v>62</v>
       </c>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
+      <c r="M19" s="3">
+        <v>62</v>
+      </c>
+      <c r="N19" s="3">
+        <f>+V19-SUM(K19:M19)</f>
+        <v>61</v>
+      </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
@@ -2536,7 +2643,9 @@
       <c r="U19" s="3">
         <v>259</v>
       </c>
-      <c r="V19" s="3"/>
+      <c r="V19" s="3">
+        <v>246</v>
+      </c>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
@@ -2626,8 +2735,13 @@
       <c r="L20" s="3">
         <v>59</v>
       </c>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
+      <c r="M20" s="3">
+        <v>69</v>
+      </c>
+      <c r="N20" s="3">
+        <f>+V20-SUM(K20:M20)</f>
+        <v>62</v>
+      </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
@@ -2641,7 +2755,9 @@
       <c r="U20" s="3">
         <v>295</v>
       </c>
-      <c r="V20" s="3"/>
+      <c r="V20" s="3">
+        <v>271</v>
+      </c>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
@@ -2724,7 +2840,7 @@
         <v>328</v>
       </c>
       <c r="I21" s="3">
-        <f t="shared" ref="I21:U21" si="18">+I17+I18-I19+I20</f>
+        <f t="shared" ref="I21:V21" si="18">+I17+I18-I19+I20</f>
         <v>797</v>
       </c>
       <c r="J21" s="3">
@@ -2741,11 +2857,11 @@
       </c>
       <c r="M21" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>573</v>
       </c>
       <c r="N21" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3">
@@ -2772,7 +2888,10 @@
         <f t="shared" si="18"/>
         <v>2278</v>
       </c>
-      <c r="V21" s="3"/>
+      <c r="V21" s="3">
+        <f t="shared" si="18"/>
+        <v>2307</v>
+      </c>
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
@@ -2862,8 +2981,13 @@
       <c r="L22" s="3">
         <v>108</v>
       </c>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
+      <c r="M22" s="3">
+        <v>-24</v>
+      </c>
+      <c r="N22" s="3">
+        <f>+V22-SUM(K22:M22)</f>
+        <v>98</v>
+      </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
@@ -2877,7 +3001,9 @@
       <c r="U22" s="3">
         <v>297</v>
       </c>
-      <c r="V22" s="3"/>
+      <c r="V22" s="3">
+        <v>311</v>
+      </c>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
@@ -2977,11 +3103,11 @@
       </c>
       <c r="M23" s="3">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>597</v>
       </c>
       <c r="N23" s="3">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -3005,7 +3131,10 @@
         <f>+U21-U22</f>
         <v>1981</v>
       </c>
-      <c r="V23" s="3"/>
+      <c r="V23" s="3">
+        <f>+V21-V22</f>
+        <v>1996</v>
+      </c>
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
@@ -3095,8 +3224,13 @@
       <c r="L24" s="3">
         <v>-1</v>
       </c>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
+      <c r="M24" s="3">
+        <v>35</v>
+      </c>
+      <c r="N24" s="3">
+        <f>+V24-SUM(K24:M24)</f>
+        <v>3</v>
+      </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
@@ -3110,7 +3244,9 @@
       <c r="U24" s="3">
         <v>-6</v>
       </c>
-      <c r="V24" s="3"/>
+      <c r="V24" s="3">
+        <v>35</v>
+      </c>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
@@ -3210,11 +3346,11 @@
       </c>
       <c r="M25" s="3">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="N25" s="3">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -3238,7 +3374,10 @@
         <f>+U23+U24</f>
         <v>1975</v>
       </c>
-      <c r="V25" s="3"/>
+      <c r="V25" s="3">
+        <f>+V23+V24</f>
+        <v>2031</v>
+      </c>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
@@ -3410,18 +3549,18 @@
         <f t="shared" si="26"/>
         <v>0.79826464208242953</v>
       </c>
-      <c r="M27" s="8" t="e">
+      <c r="M27" s="8">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N27" s="8" t="e">
+        <v>1.3859649122807018</v>
+      </c>
+      <c r="N27" s="8">
         <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
+        <v>1.1785714285714286</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="8" t="e">
-        <f t="shared" ref="Q27:U27" si="27">+Q25/Q28</f>
+        <f t="shared" ref="Q27:V27" si="27">+Q25/Q28</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R27" s="8" t="e">
@@ -3440,7 +3579,10 @@
         <f t="shared" si="27"/>
         <v>3.9818548387096775</v>
       </c>
-      <c r="V27" s="3"/>
+      <c r="V27" s="8">
+        <f t="shared" si="27"/>
+        <v>4.4248366013071898</v>
+      </c>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
@@ -3530,8 +3672,12 @@
       <c r="L28" s="3">
         <v>461</v>
       </c>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
+      <c r="M28" s="3">
+        <v>456</v>
+      </c>
+      <c r="N28" s="3">
+        <v>448</v>
+      </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
@@ -3545,7 +3691,9 @@
       <c r="U28" s="3">
         <v>496</v>
       </c>
-      <c r="V28" s="3"/>
+      <c r="V28" s="3">
+        <v>459</v>
+      </c>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
@@ -3704,18 +3852,18 @@
       </c>
       <c r="M31" s="6">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>9.8273790014203E-2</v>
       </c>
       <c r="N31" s="6">
         <f t="shared" si="28"/>
-        <v>-1</v>
+        <v>-5.6055900621117982E-2</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
       <c r="S31" s="6" t="e">
-        <f t="shared" ref="S31:U31" si="29">+S4/R4-1</f>
+        <f t="shared" ref="S31:T31" si="29">+S4/R4-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T31" s="6">
@@ -3726,7 +3874,10 @@
         <f>+U4/T4-1</f>
         <v>1.9957380542578562E-2</v>
       </c>
-      <c r="V31" s="3"/>
+      <c r="V31" s="6">
+        <f>+V4/U4-1</f>
+        <v>2.6008812460658559E-2</v>
+      </c>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
@@ -3811,18 +3962,18 @@
       </c>
       <c r="M32" s="13">
         <f t="shared" si="30"/>
-        <v>-1</v>
+        <v>9.4720496894409978E-2</v>
       </c>
       <c r="N32" s="13">
         <f t="shared" si="30"/>
-        <v>-1</v>
+        <v>0.14967041488949206</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
       <c r="S32" s="13" t="e">
-        <f t="shared" ref="S32:U32" si="31">+S9/R9-1</f>
+        <f t="shared" ref="S32:T32" si="31">+S9/R9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T32" s="13">
@@ -3833,7 +3984,10 @@
         <f>+U9/T9-1</f>
         <v>1.6910601265822889E-2</v>
       </c>
-      <c r="V32" s="3"/>
+      <c r="V32" s="13">
+        <f>+V9/U9-1</f>
+        <v>7.9451521929398083E-2</v>
+      </c>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
@@ -3931,13 +4085,13 @@
         <f t="shared" si="33"/>
         <v>0.71575091575091576</v>
       </c>
-      <c r="M33" s="6" t="e">
+      <c r="M33" s="6">
         <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N33" s="6" t="e">
+        <v>0.70886524822695041</v>
+      </c>
+      <c r="N33" s="6">
         <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
+        <v>0.71365935919055645</v>
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="6" t="e">
@@ -3964,7 +4118,10 @@
         <f t="shared" si="34"/>
         <v>0.71992609160750753</v>
       </c>
-      <c r="V33" s="3"/>
+      <c r="V33" s="6">
+        <f t="shared" ref="V33" si="35">+V11/V9</f>
+        <v>0.71450450450450453</v>
+      </c>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
@@ -4023,23 +4180,23 @@
         <v>37</v>
       </c>
       <c r="C34" s="6">
-        <f t="shared" ref="C34:G34" si="35">+C17/C9</f>
+        <f t="shared" ref="C34:G34" si="36">+C17/C9</f>
         <v>0.22231075697211156</v>
       </c>
       <c r="D34" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.20393700787401575</v>
       </c>
       <c r="E34" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.182</v>
       </c>
       <c r="F34" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.16003122560499611</v>
       </c>
       <c r="G34" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.24687010954616589</v>
       </c>
       <c r="H34" s="6">
@@ -4047,55 +4204,58 @@
         <v>0.21345256609642302</v>
       </c>
       <c r="I34" s="6">
-        <f t="shared" ref="I34:N34" si="36">+I17/I9</f>
+        <f t="shared" ref="I34:N34" si="37">+I17/I9</f>
         <v>0.23097826086956522</v>
       </c>
       <c r="J34" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.21054672353625437</v>
       </c>
       <c r="K34" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.23829787234042554</v>
       </c>
       <c r="L34" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.1772893772893773</v>
       </c>
-      <c r="M34" s="6" t="e">
-        <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N34" s="6" t="e">
-        <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
+      <c r="M34" s="6">
+        <f t="shared" si="37"/>
+        <v>0.20425531914893616</v>
+      </c>
+      <c r="N34" s="6">
+        <f t="shared" si="37"/>
+        <v>0.20269814502529512</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="6" t="e">
-        <f t="shared" ref="P34:U34" si="37">+P17/P9</f>
+        <f t="shared" ref="P34:U34" si="38">+P17/P9</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q34" s="6" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R34" s="6" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S34" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.23991832567636548</v>
       </c>
       <c r="T34" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.19195015822784811</v>
       </c>
       <c r="U34" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.22542059710201304</v>
       </c>
-      <c r="V34" s="3"/>
+      <c r="V34" s="6">
+        <f t="shared" ref="V34" si="39">+V17/V9</f>
+        <v>0.20513513513513512</v>
+      </c>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
@@ -4154,23 +4314,23 @@
         <v>39</v>
       </c>
       <c r="C35" s="6">
-        <f t="shared" ref="C35:G35" si="38">+C22/C21</f>
+        <f t="shared" ref="C35:G35" si="40">+C22/C21</f>
         <v>0.22054794520547946</v>
       </c>
       <c r="D35" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.39649122807017545</v>
       </c>
       <c r="E35" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.21372667068031306</v>
       </c>
       <c r="F35" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.29388942774005822</v>
       </c>
       <c r="G35" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.18097014925373134</v>
       </c>
       <c r="H35" s="6">
@@ -4178,55 +4338,58 @@
         <v>0.31097560975609756</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" ref="I35:N35" si="39">+I22/I21</f>
+        <f t="shared" ref="I35:N35" si="41">+I22/I21</f>
         <v>0.20200752823086573</v>
       </c>
       <c r="J35" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>-0.10210696920583469</v>
       </c>
       <c r="K35" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.20347003154574134</v>
       </c>
       <c r="L35" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.22641509433962265</v>
       </c>
-      <c r="M35" s="6" t="e">
-        <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N35" s="6" t="e">
-        <f t="shared" si="39"/>
-        <v>#DIV/0!</v>
+      <c r="M35" s="6">
+        <f t="shared" si="41"/>
+        <v>-4.1884816753926704E-2</v>
+      </c>
+      <c r="N35" s="6">
+        <f t="shared" si="41"/>
+        <v>0.15730337078651685</v>
       </c>
       <c r="O35" s="3"/>
       <c r="P35" s="6" t="e">
-        <f t="shared" ref="P35:U35" si="40">+P22/P21</f>
+        <f t="shared" ref="P35:U35" si="42">+P22/P21</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q35" s="6" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R35" s="6" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S35" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.20424734540911929</v>
       </c>
       <c r="T35" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.25141623954680337</v>
       </c>
       <c r="U35" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.13037752414398596</v>
       </c>
-      <c r="V35" s="3"/>
+      <c r="V35" s="6">
+        <f t="shared" ref="V35" si="43">+V22/V21</f>
+        <v>0.13480710879930646</v>
+      </c>
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>

--- a/EBAY.xlsx
+++ b/EBAY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC193735-F1AC-446C-9685-4EEF248AD76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3015CBAA-6657-4D8A-B25F-9939C42AFEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{ED1C07FE-A50A-4536-AFF7-C55D5EA00969}"/>
+    <workbookView xWindow="225" yWindow="4680" windowWidth="38175" windowHeight="15240" xr2:uid="{ED1C07FE-A50A-4536-AFF7-C55D5EA00969}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -679,7 +679,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="14">
-        <v>84.016999999999996</v>
+        <v>115.31</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -702,7 +702,7 @@
       </c>
       <c r="H4" s="3">
         <f>+H2*H3</f>
-        <v>37639.615999999995</v>
+        <v>51658.880000000005</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -738,7 +738,7 @@
       </c>
       <c r="H7" s="3">
         <f>+H4-H5+H6</f>
-        <v>41466.615999999995</v>
+        <v>55485.880000000005</v>
       </c>
     </row>
   </sheetData>
@@ -1676,7 +1676,7 @@
         <v>1837</v>
       </c>
       <c r="I11" s="3">
-        <f t="shared" ref="I11:V12" si="14">+I9-I10</f>
+        <f t="shared" ref="I11:V11" si="14">+I9-I10</f>
         <v>1849</v>
       </c>
       <c r="J11" s="3">

--- a/EBAY.xlsx
+++ b/EBAY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3015CBAA-6657-4D8A-B25F-9939C42AFEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84154040-7635-4538-BBE7-DC2A86FAC5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="4680" windowWidth="38175" windowHeight="15240" xr2:uid="{ED1C07FE-A50A-4536-AFF7-C55D5EA00969}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{ED1C07FE-A50A-4536-AFF7-C55D5EA00969}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -679,7 +679,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="14">
-        <v>115.31</v>
+        <v>107.58</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -702,7 +702,7 @@
       </c>
       <c r="H4" s="3">
         <f>+H2*H3</f>
-        <v>51658.880000000005</v>
+        <v>48195.839999999997</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -738,7 +738,7 @@
       </c>
       <c r="H7" s="3">
         <f>+H4-H5+H6</f>
-        <v>55485.880000000005</v>
+        <v>52022.84</v>
       </c>
     </row>
   </sheetData>

--- a/EBAY.xlsx
+++ b/EBAY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84154040-7635-4538-BBE7-DC2A86FAC5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6394F27E-34E5-4F8B-925F-A6E27A74DB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{ED1C07FE-A50A-4536-AFF7-C55D5EA00969}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{ED1C07FE-A50A-4536-AFF7-C55D5EA00969}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
   <si>
     <t>Ebay</t>
   </si>
@@ -211,6 +211,18 @@
   </si>
   <si>
     <t>Active Buyers</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -679,7 +691,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="14">
-        <v>107.58</v>
+        <v>113.5</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -687,10 +699,10 @@
         <v>14</v>
       </c>
       <c r="H3" s="3">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -702,7 +714,7 @@
       </c>
       <c r="H4" s="3">
         <f>+H2*H3</f>
-        <v>48195.839999999997</v>
+        <v>50394</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -717,7 +729,7 @@
         <v>2919</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -729,7 +741,7 @@
         <v>6746</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -738,7 +750,7 @@
       </c>
       <c r="H7" s="3">
         <f>+H4-H5+H6</f>
-        <v>52022.84</v>
+        <v>54221</v>
       </c>
     </row>
   </sheetData>
@@ -751,7 +763,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A8A4D81-598D-4355-8C6E-5A128DF97FC3}">
-  <dimension ref="A1:BV500"/>
+  <dimension ref="A1:BZ500"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -759,12 +771,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:78" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:78" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
@@ -801,29 +813,41 @@
       <c r="N2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="O2" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="T2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="U2" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="V2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="W2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="X2" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="U2" s="10" t="s">
+      <c r="Y2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="V2" s="10" t="s">
+      <c r="Z2" s="10" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:78" x14ac:dyDescent="0.2">
       <c r="B3" s="9" t="s">
         <v>57</v>
       </c>
@@ -863,23 +887,31 @@
       <c r="N3" s="4">
         <v>135</v>
       </c>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10">
+      <c r="O3" s="4">
+        <v>136</v>
+      </c>
+      <c r="P3" s="4">
+        <v>136</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10">
         <v>134</v>
       </c>
-      <c r="T3" s="10">
+      <c r="X3" s="10">
         <v>132</v>
       </c>
-      <c r="U3" s="10">
+      <c r="Y3" s="10">
         <v>134</v>
       </c>
-      <c r="V3" s="10">
+      <c r="Z3" s="10">
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:78" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>33</v>
       </c>
@@ -893,7 +925,7 @@
         <v>17991</v>
       </c>
       <c r="F4" s="3">
-        <f>+T4-SUM(C4:E4)</f>
+        <f>+X4-SUM(C4:E4)</f>
         <v>18591</v>
       </c>
       <c r="G4" s="3">
@@ -906,7 +938,7 @@
         <v>18306</v>
       </c>
       <c r="J4" s="3">
-        <f>+U4-SUM(G4:I4)</f>
+        <f>+Y4-SUM(G4:I4)</f>
         <v>19320</v>
       </c>
       <c r="K4" s="3">
@@ -919,29 +951,33 @@
         <v>20105</v>
       </c>
       <c r="N4" s="3">
-        <f>+V4-SUM(K4:M4)</f>
+        <f>+Z4-SUM(K4:M4)</f>
         <v>18237</v>
       </c>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
+      <c r="O4" s="3">
+        <v>22197</v>
+      </c>
+      <c r="P4" s="3">
+        <v>22398</v>
+      </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
-      <c r="S4" s="12">
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="12">
         <v>73250</v>
       </c>
-      <c r="T4" s="3">
+      <c r="X4" s="3">
         <v>73206</v>
       </c>
-      <c r="U4" s="3">
+      <c r="Y4" s="3">
         <v>74667</v>
       </c>
-      <c r="V4" s="3">
+      <c r="Z4" s="3">
         <v>76609</v>
       </c>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
@@ -990,8 +1026,12 @@
       <c r="BT4" s="3"/>
       <c r="BU4" s="3"/>
       <c r="BV4" s="3"/>
-    </row>
-    <row r="5" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW4" s="3"/>
+      <c r="BX4" s="3"/>
+      <c r="BY4" s="3"/>
+      <c r="BZ4" s="3"/>
+    </row>
+    <row r="5" spans="1:78" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1040,42 +1080,48 @@
         <v>0.14026361601591644</v>
       </c>
       <c r="N5" s="11">
-        <f t="shared" ref="N5" si="11">+N9/N4</f>
+        <f t="shared" ref="N5:P5" si="11">+N9/N4</f>
         <v>0.16258156495037562</v>
       </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="11" t="e">
-        <f t="shared" ref="P5:T5" si="12">+P9/P4</f>
+      <c r="O5" s="11">
+        <f t="shared" si="11"/>
+        <v>0.1391629499481912</v>
+      </c>
+      <c r="P5" s="11">
+        <f t="shared" si="11"/>
+        <v>0.13992320742923475</v>
+      </c>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="11" t="e">
+        <f t="shared" ref="T5:X5" si="12">+T9/T4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q5" s="11" t="e">
+      <c r="U5" s="11" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R5" s="11" t="e">
+      <c r="V5" s="11" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S5" s="11">
+      <c r="W5" s="11">
         <f t="shared" si="12"/>
         <v>0.13372013651877132</v>
       </c>
-      <c r="T5" s="11">
+      <c r="X5" s="11">
         <f t="shared" si="12"/>
         <v>0.13813075430975602</v>
       </c>
-      <c r="U5" s="11">
-        <f>+U9/U4</f>
+      <c r="Y5" s="11">
+        <f>+Y9/Y4</f>
         <v>0.13771813518689649</v>
       </c>
-      <c r="V5" s="11">
-        <f>+V9/V4</f>
+      <c r="Z5" s="11">
+        <f>+Z9/Z4</f>
         <v>0.14489159237165347</v>
       </c>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="3"/>
@@ -1124,8 +1170,12 @@
       <c r="BT5" s="3"/>
       <c r="BU5" s="3"/>
       <c r="BV5" s="3"/>
-    </row>
-    <row r="6" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW5" s="3"/>
+      <c r="BX5" s="3"/>
+      <c r="BY5" s="3"/>
+      <c r="BZ5" s="3"/>
+    </row>
+    <row r="6" spans="1:78" x14ac:dyDescent="0.2">
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -1198,8 +1248,12 @@
       <c r="BT6" s="3"/>
       <c r="BU6" s="3"/>
       <c r="BV6" s="3"/>
-    </row>
-    <row r="7" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW6" s="3"/>
+      <c r="BX6" s="3"/>
+      <c r="BY6" s="3"/>
+      <c r="BZ6" s="3"/>
+    </row>
+    <row r="7" spans="1:78" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>47</v>
       </c>
@@ -1213,7 +1267,7 @@
         <v>2134</v>
       </c>
       <c r="F7" s="3">
-        <f>+T7-SUM(C7:E7)</f>
+        <f>+X7-SUM(C7:E7)</f>
         <v>2169</v>
       </c>
       <c r="G7" s="3">
@@ -1227,7 +1281,7 @@
         <v>2168</v>
       </c>
       <c r="J7" s="3">
-        <f>+U7-SUM(G7:I7)</f>
+        <f>+Y7-SUM(G7:I7)</f>
         <v>2134</v>
       </c>
       <c r="K7" s="3">
@@ -1240,29 +1294,33 @@
         <v>2295</v>
       </c>
       <c r="N7" s="3">
-        <f>+V7-SUM(K7:M7)</f>
+        <f>+Z7-SUM(K7:M7)</f>
         <v>2421</v>
       </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
+      <c r="O7" s="3">
+        <v>2508</v>
+      </c>
+      <c r="P7" s="3">
+        <v>2538</v>
+      </c>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-      <c r="S7" s="3">
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3">
         <v>8644</v>
       </c>
-      <c r="T7" s="3">
+      <c r="X7" s="3">
         <v>8669</v>
       </c>
-      <c r="U7" s="3">
+      <c r="Y7" s="3">
         <v>8648</v>
       </c>
-      <c r="V7" s="3">
+      <c r="Z7" s="3">
         <v>9107</v>
       </c>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
       <c r="AC7" s="3"/>
@@ -1311,8 +1369,12 @@
       <c r="BT7" s="3"/>
       <c r="BU7" s="3"/>
       <c r="BV7" s="3"/>
-    </row>
-    <row r="8" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW7" s="3"/>
+      <c r="BX7" s="3"/>
+      <c r="BY7" s="3"/>
+      <c r="BZ7" s="3"/>
+    </row>
+    <row r="8" spans="1:78" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>48</v>
       </c>
@@ -1338,7 +1400,7 @@
         <v>408</v>
       </c>
       <c r="J8" s="3">
-        <f>+U8-SUM(G8:I8)</f>
+        <f>+Y8-SUM(G8:I8)</f>
         <v>445</v>
       </c>
       <c r="K8" s="3">
@@ -1351,29 +1413,33 @@
         <v>525</v>
       </c>
       <c r="N8" s="3">
-        <f>+V8-SUM(K8:M8)</f>
+        <f>+Z8-SUM(K8:M8)</f>
         <v>544</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
+      <c r="O8" s="3">
+        <v>581</v>
+      </c>
+      <c r="P8" s="3">
+        <v>596</v>
+      </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-      <c r="S8" s="3">
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3">
         <v>1151</v>
       </c>
-      <c r="T8" s="3">
+      <c r="X8" s="3">
         <v>1443</v>
       </c>
-      <c r="U8" s="3">
+      <c r="Y8" s="3">
         <v>1635</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Z8" s="3">
         <v>1993</v>
       </c>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
       <c r="AC8" s="3"/>
@@ -1422,8 +1488,12 @@
       <c r="BT8" s="3"/>
       <c r="BU8" s="3"/>
       <c r="BV8" s="3"/>
-    </row>
-    <row r="9" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW8" s="3"/>
+      <c r="BX8" s="3"/>
+      <c r="BY8" s="3"/>
+      <c r="BZ8" s="3"/>
+    </row>
+    <row r="9" spans="1:78" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1437,7 +1507,7 @@
         <v>2500</v>
       </c>
       <c r="F9" s="7">
-        <f>+T9-SUM(C9:E9)</f>
+        <f>+X9-SUM(C9:E9)</f>
         <v>2562</v>
       </c>
       <c r="G9" s="7">
@@ -1450,7 +1520,7 @@
         <v>2576</v>
       </c>
       <c r="J9" s="7">
-        <f>+U9-SUM(G9:I9)</f>
+        <f>+Y9-SUM(G9:I9)</f>
         <v>2579</v>
       </c>
       <c r="K9" s="7">
@@ -1463,29 +1533,33 @@
         <v>2820</v>
       </c>
       <c r="N9" s="7">
-        <f>+V9-SUM(K9:M9)</f>
+        <f>+Z9-SUM(K9:M9)</f>
         <v>2965</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="7">
+      <c r="O9" s="7">
+        <v>3089</v>
+      </c>
+      <c r="P9" s="7">
+        <v>3134</v>
+      </c>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="7">
         <v>9795</v>
       </c>
-      <c r="T9" s="7">
+      <c r="X9" s="7">
         <v>10112</v>
       </c>
-      <c r="U9" s="7">
+      <c r="Y9" s="7">
         <v>10283</v>
       </c>
-      <c r="V9" s="7">
+      <c r="Z9" s="7">
         <v>11100</v>
       </c>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
@@ -1534,8 +1608,12 @@
       <c r="BT9" s="3"/>
       <c r="BU9" s="3"/>
       <c r="BV9" s="3"/>
-    </row>
-    <row r="10" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW9" s="3"/>
+      <c r="BX9" s="3"/>
+      <c r="BY9" s="3"/>
+      <c r="BZ9" s="3"/>
+    </row>
+    <row r="10" spans="1:78" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
@@ -1549,7 +1627,7 @@
         <v>705</v>
       </c>
       <c r="F10" s="3">
-        <f>+T10-SUM(C10:E10)</f>
+        <f>+X10-SUM(C10:E10)</f>
         <v>710</v>
       </c>
       <c r="G10" s="3">
@@ -1562,7 +1640,7 @@
         <v>727</v>
       </c>
       <c r="J10" s="3">
-        <f>+U10-SUM(G10:I10)</f>
+        <f>+Y10-SUM(G10:I10)</f>
         <v>718</v>
       </c>
       <c r="K10" s="3">
@@ -1575,29 +1653,33 @@
         <v>821</v>
       </c>
       <c r="N10" s="3">
-        <f>+V10-SUM(K10:M10)</f>
+        <f>+Z10-SUM(K10:M10)</f>
         <v>849</v>
       </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
+      <c r="O10" s="3">
+        <v>802</v>
+      </c>
+      <c r="P10" s="3">
+        <v>832</v>
+      </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="S10" s="3">
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3">
         <v>2680</v>
       </c>
-      <c r="T10" s="3">
+      <c r="X10" s="3">
         <v>2833</v>
       </c>
-      <c r="U10" s="3">
+      <c r="Y10" s="3">
         <v>2880</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Z10" s="3">
         <v>3169</v>
       </c>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
@@ -1646,8 +1728,12 @@
       <c r="BT10" s="3"/>
       <c r="BU10" s="3"/>
       <c r="BV10" s="3"/>
-    </row>
-    <row r="11" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW10" s="3"/>
+      <c r="BX10" s="3"/>
+      <c r="BY10" s="3"/>
+      <c r="BZ10" s="3"/>
+    </row>
+    <row r="11" spans="1:78" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1676,7 +1762,7 @@
         <v>1837</v>
       </c>
       <c r="I11" s="3">
-        <f t="shared" ref="I11:V11" si="14">+I9-I10</f>
+        <f t="shared" ref="I11:Z11" si="14">+I9-I10</f>
         <v>1849</v>
       </c>
       <c r="J11" s="3">
@@ -1699,39 +1785,45 @@
         <f t="shared" si="14"/>
         <v>2116</v>
       </c>
-      <c r="O11" s="3"/>
+      <c r="O11" s="3">
+        <f t="shared" si="14"/>
+        <v>2287</v>
+      </c>
       <c r="P11" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="3">
+        <v>2302</v>
+      </c>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="R11" s="3">
+      <c r="U11" s="3">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="S11" s="3">
+      <c r="V11" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="W11" s="3">
         <f t="shared" si="14"/>
         <v>7115</v>
       </c>
-      <c r="T11" s="3">
+      <c r="X11" s="3">
         <f t="shared" si="14"/>
         <v>7279</v>
       </c>
-      <c r="U11" s="3">
+      <c r="Y11" s="3">
         <f t="shared" si="14"/>
         <v>7403</v>
       </c>
-      <c r="V11" s="3">
+      <c r="Z11" s="3">
         <f t="shared" si="14"/>
         <v>7931</v>
       </c>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
@@ -1780,8 +1872,12 @@
       <c r="BT11" s="3"/>
       <c r="BU11" s="3"/>
       <c r="BV11" s="3"/>
-    </row>
-    <row r="12" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW11" s="3"/>
+      <c r="BX11" s="3"/>
+      <c r="BY11" s="3"/>
+      <c r="BZ11" s="3"/>
+    </row>
+    <row r="12" spans="1:78" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
@@ -1795,7 +1891,7 @@
         <v>567</v>
       </c>
       <c r="F12" s="3">
-        <f>+T12-SUM(C12:E12)</f>
+        <f>+X12-SUM(C12:E12)</f>
         <v>573</v>
       </c>
       <c r="G12" s="3">
@@ -1808,7 +1904,7 @@
         <v>592</v>
       </c>
       <c r="J12" s="3">
-        <f>+U12-SUM(G12:I12)</f>
+        <f>+Y12-SUM(G12:I12)</f>
         <v>609</v>
       </c>
       <c r="K12" s="3">
@@ -1821,29 +1917,33 @@
         <v>606</v>
       </c>
       <c r="N12" s="3">
-        <f>+V12-SUM(K12:M12)</f>
+        <f>+Z12-SUM(K12:M12)</f>
         <v>666</v>
       </c>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
+      <c r="O12" s="3">
+        <v>673</v>
+      </c>
+      <c r="P12" s="3">
+        <v>697</v>
+      </c>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-      <c r="S12" s="3">
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3">
         <v>2136</v>
       </c>
-      <c r="T12" s="3">
+      <c r="X12" s="3">
         <v>2217</v>
       </c>
-      <c r="U12" s="3">
+      <c r="Y12" s="3">
         <v>2319</v>
       </c>
-      <c r="V12" s="3">
+      <c r="Z12" s="3">
         <v>2394</v>
       </c>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
@@ -1892,8 +1992,12 @@
       <c r="BT12" s="3"/>
       <c r="BU12" s="3"/>
       <c r="BV12" s="3"/>
-    </row>
-    <row r="13" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW12" s="3"/>
+      <c r="BX12" s="3"/>
+      <c r="BY12" s="3"/>
+      <c r="BZ12" s="3"/>
+    </row>
+    <row r="13" spans="1:78" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>24</v>
       </c>
@@ -1907,7 +2011,7 @@
         <v>401</v>
       </c>
       <c r="F13" s="3">
-        <f>+T13-SUM(C13:E13)</f>
+        <f>+X13-SUM(C13:E13)</f>
         <v>399</v>
       </c>
       <c r="G13" s="3">
@@ -1920,7 +2024,7 @@
         <v>374</v>
       </c>
       <c r="J13" s="3">
-        <f>+U13-SUM(G13:I13)</f>
+        <f>+Y13-SUM(G13:I13)</f>
         <v>375</v>
       </c>
       <c r="K13" s="3">
@@ -1933,29 +2037,33 @@
         <v>423</v>
       </c>
       <c r="N13" s="3">
-        <f>+V13-SUM(K13:M13)</f>
+        <f>+Z13-SUM(K13:M13)</f>
         <v>436</v>
       </c>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
+      <c r="O13" s="3">
+        <v>450</v>
+      </c>
+      <c r="P13" s="3">
+        <v>484</v>
+      </c>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-      <c r="S13" s="3">
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3">
         <v>1330</v>
       </c>
-      <c r="T13" s="3">
+      <c r="X13" s="3">
         <v>1544</v>
       </c>
-      <c r="U13" s="3">
+      <c r="Y13" s="3">
         <v>1479</v>
       </c>
-      <c r="V13" s="3">
+      <c r="Z13" s="3">
         <v>1642</v>
       </c>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
       <c r="AC13" s="3"/>
@@ -2004,8 +2112,12 @@
       <c r="BT13" s="3"/>
       <c r="BU13" s="3"/>
       <c r="BV13" s="3"/>
-    </row>
-    <row r="14" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW13" s="3"/>
+      <c r="BX13" s="3"/>
+      <c r="BY13" s="3"/>
+      <c r="BZ13" s="3"/>
+    </row>
+    <row r="14" spans="1:78" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>23</v>
       </c>
@@ -2019,7 +2131,7 @@
         <v>283</v>
       </c>
       <c r="F14" s="3">
-        <f>+T14-SUM(C14:E14)</f>
+        <f>+X14-SUM(C14:E14)</f>
         <v>365</v>
       </c>
       <c r="G14" s="3">
@@ -2032,7 +2144,7 @@
         <v>194</v>
       </c>
       <c r="J14" s="3">
-        <f>+U14-SUM(G14:I14)</f>
+        <f>+Y14-SUM(G14:I14)</f>
         <v>241</v>
       </c>
       <c r="K14" s="3">
@@ -2045,29 +2157,33 @@
         <v>282</v>
       </c>
       <c r="N14" s="3">
-        <f>+V14-SUM(K14:M14)</f>
+        <f>+Z14-SUM(K14:M14)</f>
         <v>284</v>
       </c>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
+      <c r="O14" s="3">
+        <v>410</v>
+      </c>
+      <c r="P14" s="3">
+        <v>306</v>
+      </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-      <c r="S14" s="3">
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3">
         <v>963</v>
       </c>
-      <c r="T14" s="3">
+      <c r="X14" s="3">
         <v>1196</v>
       </c>
-      <c r="U14" s="3">
+      <c r="Y14" s="3">
         <v>914</v>
       </c>
-      <c r="V14" s="3">
+      <c r="Z14" s="3">
         <v>1198</v>
       </c>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
@@ -2116,8 +2232,12 @@
       <c r="BT14" s="3"/>
       <c r="BU14" s="3"/>
       <c r="BV14" s="3"/>
-    </row>
-    <row r="15" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW14" s="3"/>
+      <c r="BX14" s="3"/>
+      <c r="BY14" s="3"/>
+      <c r="BZ14" s="3"/>
+    </row>
+    <row r="15" spans="1:78" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>44</v>
       </c>
@@ -2131,7 +2251,7 @@
         <v>85</v>
       </c>
       <c r="F15" s="3">
-        <f>+T15-SUM(C15:E15)</f>
+        <f>+X15-SUM(C15:E15)</f>
         <v>101</v>
       </c>
       <c r="G15" s="3">
@@ -2144,7 +2264,7 @@
         <v>89</v>
       </c>
       <c r="J15" s="3">
-        <f>+U15-SUM(G15:I15)</f>
+        <f>+Y15-SUM(G15:I15)</f>
         <v>87</v>
       </c>
       <c r="K15" s="3">
@@ -2157,29 +2277,33 @@
         <v>106</v>
       </c>
       <c r="N15" s="3">
-        <f>+V15-SUM(K15:M15)</f>
+        <f>+Z15-SUM(K15:M15)</f>
         <v>123</v>
       </c>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
+      <c r="O15" s="3">
+        <v>138</v>
+      </c>
+      <c r="P15" s="3">
+        <v>133</v>
+      </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-      <c r="S15" s="3">
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3">
         <v>332</v>
       </c>
-      <c r="T15" s="3">
+      <c r="X15" s="3">
         <v>360</v>
       </c>
-      <c r="U15" s="3">
+      <c r="Y15" s="3">
         <v>353</v>
       </c>
-      <c r="V15" s="3">
+      <c r="Z15" s="3">
         <v>396</v>
       </c>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
@@ -2228,8 +2352,12 @@
       <c r="BT15" s="3"/>
       <c r="BU15" s="3"/>
       <c r="BV15" s="3"/>
-    </row>
-    <row r="16" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW15" s="3"/>
+      <c r="BX15" s="3"/>
+      <c r="BY15" s="3"/>
+      <c r="BZ15" s="3"/>
+    </row>
+    <row r="16" spans="1:78" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>45</v>
       </c>
@@ -2243,7 +2371,7 @@
         <v>4</v>
       </c>
       <c r="F16" s="3">
-        <f>+T16-SUM(C16:E16)</f>
+        <f>+X16-SUM(C16:E16)</f>
         <v>4</v>
       </c>
       <c r="G16" s="3">
@@ -2256,7 +2384,7 @@
         <v>5</v>
       </c>
       <c r="J16" s="3">
-        <f>+U16-SUM(G16:I16)</f>
+        <f>+Y16-SUM(G16:I16)</f>
         <v>6</v>
       </c>
       <c r="K16" s="3">
@@ -2269,29 +2397,33 @@
         <v>6</v>
       </c>
       <c r="N16" s="3">
-        <f>+V16-SUM(K16:M16)</f>
+        <f>+Z16-SUM(K16:M16)</f>
         <v>6</v>
       </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
+      <c r="O16" s="3">
+        <v>5</v>
+      </c>
+      <c r="P16" s="3">
+        <v>6</v>
+      </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-      <c r="S16" s="3">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3">
         <v>4</v>
       </c>
-      <c r="T16" s="3">
+      <c r="X16" s="3">
         <v>21</v>
       </c>
-      <c r="U16" s="3">
+      <c r="Y16" s="3">
         <v>20</v>
       </c>
-      <c r="V16" s="3">
+      <c r="Z16" s="3">
         <v>24</v>
       </c>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
@@ -2340,8 +2472,12 @@
       <c r="BT16" s="3"/>
       <c r="BU16" s="3"/>
       <c r="BV16" s="3"/>
-    </row>
-    <row r="17" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW16" s="3"/>
+      <c r="BX16" s="3"/>
+      <c r="BY16" s="3"/>
+      <c r="BZ16" s="3"/>
+    </row>
+    <row r="17" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>25</v>
       </c>
@@ -2370,7 +2506,7 @@
         <v>549</v>
       </c>
       <c r="I17" s="3">
-        <f t="shared" ref="I17:V17" si="16">+I11-SUM(I12:I16)</f>
+        <f t="shared" ref="I17:Z17" si="16">+I11-SUM(I12:I16)</f>
         <v>595</v>
       </c>
       <c r="J17" s="3">
@@ -2393,39 +2529,45 @@
         <f t="shared" si="16"/>
         <v>601</v>
       </c>
-      <c r="O17" s="3"/>
+      <c r="O17" s="3">
+        <f t="shared" si="16"/>
+        <v>611</v>
+      </c>
       <c r="P17" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3">
+        <v>676</v>
+      </c>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="R17" s="3">
+      <c r="U17" s="3">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="3">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="3">
         <f t="shared" si="16"/>
         <v>2350</v>
       </c>
-      <c r="T17" s="3">
+      <c r="X17" s="3">
         <f t="shared" si="16"/>
         <v>1941</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <f t="shared" si="16"/>
         <v>2318</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <f t="shared" si="16"/>
         <v>2277</v>
       </c>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17" s="3"/>
@@ -2474,8 +2616,12 @@
       <c r="BT17" s="3"/>
       <c r="BU17" s="3"/>
       <c r="BV17" s="3"/>
-    </row>
-    <row r="18" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW17" s="3"/>
+      <c r="BX17" s="3"/>
+      <c r="BY17" s="3"/>
+      <c r="BZ17" s="3"/>
+    </row>
+    <row r="18" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>46</v>
       </c>
@@ -2489,7 +2635,7 @@
         <v>1212</v>
       </c>
       <c r="F18" s="3">
-        <f>+T18-SUM(C18:E18)</f>
+        <f>+X18-SUM(C18:E18)</f>
         <v>636</v>
       </c>
       <c r="G18" s="3">
@@ -2502,7 +2648,7 @@
         <v>199</v>
       </c>
       <c r="J18" s="3">
-        <f>+U18-SUM(G18:I18)</f>
+        <f>+Y18-SUM(G18:I18)</f>
         <v>44</v>
       </c>
       <c r="K18" s="3">
@@ -2515,29 +2661,33 @@
         <v>-10</v>
       </c>
       <c r="N18" s="3">
-        <f>+V18-SUM(K18:M18)</f>
+        <f>+Z18-SUM(K18:M18)</f>
         <v>21</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
+      <c r="O18" s="3">
+        <v>2</v>
+      </c>
+      <c r="P18" s="3">
+        <v>2</v>
+      </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-      <c r="S18" s="3">
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3">
         <v>-3786</v>
       </c>
-      <c r="T18" s="3">
+      <c r="X18" s="3">
         <v>1832</v>
       </c>
-      <c r="U18" s="3">
+      <c r="Y18" s="3">
         <v>-76</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Z18" s="3">
         <v>5</v>
       </c>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
@@ -2586,8 +2736,12 @@
       <c r="BT18" s="3"/>
       <c r="BU18" s="3"/>
       <c r="BV18" s="3"/>
-    </row>
-    <row r="19" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW18" s="3"/>
+      <c r="BX18" s="3"/>
+      <c r="BY18" s="3"/>
+      <c r="BZ18" s="3"/>
+    </row>
+    <row r="19" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>26</v>
       </c>
@@ -2601,7 +2755,7 @@
         <v>65</v>
       </c>
       <c r="F19" s="3">
-        <f>+T19-SUM(C19:E19)</f>
+        <f>+X19-SUM(C19:E19)</f>
         <v>65</v>
       </c>
       <c r="G19" s="3">
@@ -2614,7 +2768,7 @@
         <v>63</v>
       </c>
       <c r="J19" s="3">
-        <f>+U19-SUM(G19:I19)</f>
+        <f>+Y19-SUM(G19:I19)</f>
         <v>65</v>
       </c>
       <c r="K19" s="3">
@@ -2627,29 +2781,33 @@
         <v>62</v>
       </c>
       <c r="N19" s="3">
-        <f>+V19-SUM(K19:M19)</f>
+        <f>+Z19-SUM(K19:M19)</f>
         <v>61</v>
       </c>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
+      <c r="O19" s="3">
+        <v>61</v>
+      </c>
+      <c r="P19" s="3">
+        <v>65</v>
+      </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-      <c r="S19" s="3">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3">
         <v>235</v>
       </c>
-      <c r="T19" s="3">
+      <c r="X19" s="3">
         <v>263</v>
       </c>
-      <c r="U19" s="3">
+      <c r="Y19" s="3">
         <v>259</v>
       </c>
-      <c r="V19" s="3">
+      <c r="Z19" s="3">
         <v>246</v>
       </c>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
@@ -2698,8 +2856,12 @@
       <c r="BT19" s="3"/>
       <c r="BU19" s="3"/>
       <c r="BV19" s="3"/>
-    </row>
-    <row r="20" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW19" s="3"/>
+      <c r="BX19" s="3"/>
+      <c r="BY19" s="3"/>
+      <c r="BZ19" s="3"/>
+    </row>
+    <row r="20" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>27</v>
       </c>
@@ -2713,7 +2875,7 @@
         <v>59</v>
       </c>
       <c r="F20" s="3">
-        <f>+T20-SUM(C20:E20)</f>
+        <f>+X20-SUM(C20:E20)</f>
         <v>50</v>
       </c>
       <c r="G20" s="3">
@@ -2726,7 +2888,7 @@
         <v>66</v>
       </c>
       <c r="J20" s="3">
-        <f>+U20-SUM(G20:I20)</f>
+        <f>+Y20-SUM(G20:I20)</f>
         <v>95</v>
       </c>
       <c r="K20" s="3">
@@ -2739,29 +2901,33 @@
         <v>69</v>
       </c>
       <c r="N20" s="3">
-        <f>+V20-SUM(K20:M20)</f>
+        <f>+Z20-SUM(K20:M20)</f>
         <v>62</v>
       </c>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
+      <c r="O20" s="3">
+        <v>66</v>
+      </c>
+      <c r="P20" s="3">
+        <v>52</v>
+      </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
-      <c r="S20" s="3">
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3">
         <v>70</v>
       </c>
-      <c r="T20" s="3">
+      <c r="X20" s="3">
         <v>197</v>
       </c>
-      <c r="U20" s="3">
+      <c r="Y20" s="3">
         <v>295</v>
       </c>
-      <c r="V20" s="3">
+      <c r="Z20" s="3">
         <v>271</v>
       </c>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
       <c r="AC20" s="3"/>
@@ -2810,8 +2976,12 @@
       <c r="BT20" s="3"/>
       <c r="BU20" s="3"/>
       <c r="BV20" s="3"/>
-    </row>
-    <row r="21" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW20" s="3"/>
+      <c r="BX20" s="3"/>
+      <c r="BY20" s="3"/>
+      <c r="BZ20" s="3"/>
+    </row>
+    <row r="21" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
@@ -2840,7 +3010,7 @@
         <v>328</v>
       </c>
       <c r="I21" s="3">
-        <f t="shared" ref="I21:V21" si="18">+I17+I18-I19+I20</f>
+        <f t="shared" ref="I21:Z21" si="18">+I17+I18-I19+I20</f>
         <v>797</v>
       </c>
       <c r="J21" s="3">
@@ -2863,39 +3033,45 @@
         <f t="shared" si="18"/>
         <v>623</v>
       </c>
-      <c r="O21" s="3"/>
+      <c r="O21" s="3">
+        <f t="shared" si="18"/>
+        <v>618</v>
+      </c>
       <c r="P21" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3">
+        <v>665</v>
+      </c>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="R21" s="3">
+      <c r="U21" s="3">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="S21" s="3">
+      <c r="V21" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="3">
         <f t="shared" si="18"/>
         <v>-1601</v>
       </c>
-      <c r="T21" s="3">
+      <c r="X21" s="3">
         <f t="shared" si="18"/>
         <v>3707</v>
       </c>
-      <c r="U21" s="3">
+      <c r="Y21" s="3">
         <f t="shared" si="18"/>
         <v>2278</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Z21" s="3">
         <f t="shared" si="18"/>
         <v>2307</v>
       </c>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
       <c r="AC21" s="3"/>
@@ -2944,8 +3120,12 @@
       <c r="BT21" s="3"/>
       <c r="BU21" s="3"/>
       <c r="BV21" s="3"/>
-    </row>
-    <row r="22" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW21" s="3"/>
+      <c r="BX21" s="3"/>
+      <c r="BY21" s="3"/>
+      <c r="BZ21" s="3"/>
+    </row>
+    <row r="22" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
@@ -2959,7 +3139,7 @@
         <v>355</v>
       </c>
       <c r="F22" s="3">
-        <f>+T22-SUM(C22:E22)</f>
+        <f>+X22-SUM(C22:E22)</f>
         <v>303</v>
       </c>
       <c r="G22" s="3">
@@ -2972,7 +3152,7 @@
         <v>161</v>
       </c>
       <c r="J22" s="3">
-        <f>+U22-SUM(G22:I22)</f>
+        <f>+Y22-SUM(G22:I22)</f>
         <v>-63</v>
       </c>
       <c r="K22" s="3">
@@ -2985,29 +3165,33 @@
         <v>-24</v>
       </c>
       <c r="N22" s="3">
-        <f>+V22-SUM(K22:M22)</f>
+        <f>+Z22-SUM(K22:M22)</f>
         <v>98</v>
       </c>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
+      <c r="O22" s="3">
+        <v>106</v>
+      </c>
+      <c r="P22" s="3">
+        <v>113</v>
+      </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
-      <c r="S22" s="3">
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3">
         <v>-327</v>
       </c>
-      <c r="T22" s="3">
+      <c r="X22" s="3">
         <v>932</v>
       </c>
-      <c r="U22" s="3">
+      <c r="Y22" s="3">
         <v>297</v>
       </c>
-      <c r="V22" s="3">
+      <c r="Z22" s="3">
         <v>311</v>
       </c>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
       <c r="AC22" s="3"/>
@@ -3056,8 +3240,12 @@
       <c r="BT22" s="3"/>
       <c r="BU22" s="3"/>
       <c r="BV22" s="3"/>
-    </row>
-    <row r="23" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW22" s="3"/>
+      <c r="BX22" s="3"/>
+      <c r="BY22" s="3"/>
+      <c r="BZ22" s="3"/>
+    </row>
+    <row r="23" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>32</v>
       </c>
@@ -3086,7 +3274,7 @@
         <v>226</v>
       </c>
       <c r="I23" s="3">
-        <f t="shared" ref="I23:N23" si="20">+I21-I22</f>
+        <f t="shared" ref="I23:P23" si="20">+I21-I22</f>
         <v>636</v>
       </c>
       <c r="J23" s="3">
@@ -3109,36 +3297,42 @@
         <f t="shared" si="20"/>
         <v>525</v>
       </c>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3">
-        <f t="shared" ref="Q23:T23" si="21">+Q21-Q22</f>
+      <c r="O23" s="3">
+        <f t="shared" si="20"/>
+        <v>512</v>
+      </c>
+      <c r="P23" s="3">
+        <f t="shared" si="20"/>
+        <v>552</v>
+      </c>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3">
+        <f t="shared" ref="U23:X23" si="21">+U21-U22</f>
         <v>0</v>
       </c>
-      <c r="R23" s="3">
+      <c r="V23" s="3">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="S23" s="3">
+      <c r="W23" s="3">
         <f t="shared" si="21"/>
         <v>-1274</v>
       </c>
-      <c r="T23" s="3">
+      <c r="X23" s="3">
         <f t="shared" si="21"/>
         <v>2775</v>
       </c>
-      <c r="U23" s="3">
-        <f>+U21-U22</f>
+      <c r="Y23" s="3">
+        <f>+Y21-Y22</f>
         <v>1981</v>
       </c>
-      <c r="V23" s="3">
-        <f>+V21-V22</f>
+      <c r="Z23" s="3">
+        <f>+Z21-Z22</f>
         <v>1996</v>
       </c>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
       <c r="AC23" s="3"/>
@@ -3187,8 +3381,12 @@
       <c r="BT23" s="3"/>
       <c r="BU23" s="3"/>
       <c r="BV23" s="3"/>
-    </row>
-    <row r="24" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW23" s="3"/>
+      <c r="BX23" s="3"/>
+      <c r="BY23" s="3"/>
+      <c r="BZ23" s="3"/>
+    </row>
+    <row r="24" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>31</v>
       </c>
@@ -3202,7 +3400,7 @@
         <v>-1</v>
       </c>
       <c r="F24" s="3">
-        <f>+T24-SUM(C24:E24)</f>
+        <f>+X24-SUM(C24:E24)</f>
         <v>-4</v>
       </c>
       <c r="G24" s="3">
@@ -3215,7 +3413,7 @@
         <v>-2</v>
       </c>
       <c r="J24" s="3">
-        <f>+U24-SUM(G24:I24)</f>
+        <f>+Y24-SUM(G24:I24)</f>
         <v>-1</v>
       </c>
       <c r="K24" s="3">
@@ -3228,29 +3426,33 @@
         <v>35</v>
       </c>
       <c r="N24" s="3">
-        <f>+V24-SUM(K24:M24)</f>
+        <f>+Z24-SUM(K24:M24)</f>
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>-2</v>
+      </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
-      <c r="S24" s="3">
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3">
         <v>5</v>
       </c>
-      <c r="T24" s="3">
+      <c r="X24" s="3">
         <v>-8</v>
       </c>
-      <c r="U24" s="3">
+      <c r="Y24" s="3">
         <v>-6</v>
       </c>
-      <c r="V24" s="3">
+      <c r="Z24" s="3">
         <v>35</v>
       </c>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
       <c r="AC24" s="3"/>
@@ -3299,8 +3501,12 @@
       <c r="BT24" s="3"/>
       <c r="BU24" s="3"/>
       <c r="BV24" s="3"/>
-    </row>
-    <row r="25" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW24" s="3"/>
+      <c r="BX24" s="3"/>
+      <c r="BY24" s="3"/>
+      <c r="BZ24" s="3"/>
+    </row>
+    <row r="25" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>30</v>
       </c>
@@ -3329,7 +3535,7 @@
         <v>224</v>
       </c>
       <c r="I25" s="3">
-        <f t="shared" ref="I25:N25" si="23">+I23+I24</f>
+        <f t="shared" ref="I25:P25" si="23">+I23+I24</f>
         <v>634</v>
       </c>
       <c r="J25" s="3">
@@ -3352,36 +3558,42 @@
         <f t="shared" si="23"/>
         <v>528</v>
       </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3">
-        <f t="shared" ref="Q25:T25" si="24">+Q23+Q24</f>
+      <c r="O25" s="3">
+        <f t="shared" si="23"/>
+        <v>512</v>
+      </c>
+      <c r="P25" s="3">
+        <f t="shared" si="23"/>
+        <v>550</v>
+      </c>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3">
+        <f t="shared" ref="U25:X25" si="24">+U23+U24</f>
         <v>0</v>
       </c>
-      <c r="R25" s="3">
+      <c r="V25" s="3">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="S25" s="3">
+      <c r="W25" s="3">
         <f t="shared" si="24"/>
         <v>-1269</v>
       </c>
-      <c r="T25" s="3">
+      <c r="X25" s="3">
         <f t="shared" si="24"/>
         <v>2767</v>
       </c>
-      <c r="U25" s="3">
-        <f>+U23+U24</f>
+      <c r="Y25" s="3">
+        <f>+Y23+Y24</f>
         <v>1975</v>
       </c>
-      <c r="V25" s="3">
-        <f>+V23+V24</f>
+      <c r="Z25" s="3">
+        <f>+Z23+Z24</f>
         <v>2031</v>
       </c>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
@@ -3430,8 +3642,12 @@
       <c r="BT25" s="3"/>
       <c r="BU25" s="3"/>
       <c r="BV25" s="3"/>
-    </row>
-    <row r="26" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW25" s="3"/>
+      <c r="BX25" s="3"/>
+      <c r="BY25" s="3"/>
+      <c r="BZ25" s="3"/>
+    </row>
+    <row r="26" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -3504,8 +3720,12 @@
       <c r="BT26" s="3"/>
       <c r="BU26" s="3"/>
       <c r="BV26" s="3"/>
-    </row>
-    <row r="27" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW26" s="3"/>
+      <c r="BX26" s="3"/>
+      <c r="BY26" s="3"/>
+      <c r="BZ26" s="3"/>
+    </row>
+    <row r="27" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>19</v>
       </c>
@@ -3542,7 +3762,7 @@
         <v>1.3689516129032258</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" ref="K27:N27" si="26">+K25/K28</f>
+        <f t="shared" ref="K27:P27" si="26">+K25/K28</f>
         <v>1.0770877944325481</v>
       </c>
       <c r="L27" s="8">
@@ -3557,36 +3777,42 @@
         <f t="shared" si="26"/>
         <v>1.1785714285714286</v>
       </c>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="8" t="e">
-        <f t="shared" ref="Q27:V27" si="27">+Q25/Q28</f>
+      <c r="O27" s="8">
+        <f t="shared" si="26"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="P27" s="8">
+        <f t="shared" si="26"/>
+        <v>1.2359550561797752</v>
+      </c>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="8" t="e">
+        <f t="shared" ref="U27:Z27" si="27">+U25/U28</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R27" s="8" t="e">
+      <c r="V27" s="8" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S27" s="8">
+      <c r="W27" s="8">
         <f t="shared" si="27"/>
         <v>-2.274193548387097</v>
       </c>
-      <c r="T27" s="8">
+      <c r="X27" s="8">
         <f t="shared" si="27"/>
         <v>5.2207547169811317</v>
       </c>
-      <c r="U27" s="8">
+      <c r="Y27" s="8">
         <f t="shared" si="27"/>
         <v>3.9818548387096775</v>
       </c>
-      <c r="V27" s="8">
+      <c r="Z27" s="8">
         <f t="shared" si="27"/>
         <v>4.4248366013071898</v>
       </c>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
@@ -3635,8 +3861,12 @@
       <c r="BT27" s="3"/>
       <c r="BU27" s="3"/>
       <c r="BV27" s="3"/>
-    </row>
-    <row r="28" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW27" s="3"/>
+      <c r="BX27" s="3"/>
+      <c r="BY27" s="3"/>
+      <c r="BZ27" s="3"/>
+    </row>
+    <row r="28" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>14</v>
       </c>
@@ -3650,7 +3880,7 @@
         <v>529</v>
       </c>
       <c r="F28" s="3">
-        <f>+T28</f>
+        <f>+X28</f>
         <v>530</v>
       </c>
       <c r="G28" s="3">
@@ -3663,7 +3893,7 @@
         <v>487</v>
       </c>
       <c r="J28" s="3">
-        <f>+U28</f>
+        <f>+Y28</f>
         <v>496</v>
       </c>
       <c r="K28" s="3">
@@ -3678,26 +3908,30 @@
       <c r="N28" s="3">
         <v>448</v>
       </c>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
+      <c r="O28" s="3">
+        <v>448</v>
+      </c>
+      <c r="P28" s="3">
+        <v>445</v>
+      </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
-      <c r="S28" s="3">
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3">
         <v>558</v>
       </c>
-      <c r="T28" s="3">
+      <c r="X28" s="3">
         <v>530</v>
       </c>
-      <c r="U28" s="3">
+      <c r="Y28" s="3">
         <v>496</v>
       </c>
-      <c r="V28" s="3">
+      <c r="Z28" s="3">
         <v>459</v>
       </c>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
       <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
@@ -3746,8 +3980,12 @@
       <c r="BT28" s="3"/>
       <c r="BU28" s="3"/>
       <c r="BV28" s="3"/>
-    </row>
-    <row r="30" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW28" s="3"/>
+      <c r="BX28" s="3"/>
+      <c r="BY28" s="3"/>
+      <c r="BZ28" s="3"/>
+    </row>
+    <row r="30" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -3820,8 +4058,12 @@
       <c r="BT30" s="3"/>
       <c r="BU30" s="3"/>
       <c r="BV30" s="3"/>
-    </row>
-    <row r="31" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW30" s="3"/>
+      <c r="BX30" s="3"/>
+      <c r="BY30" s="3"/>
+      <c r="BZ30" s="3"/>
+    </row>
+    <row r="31" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>35</v>
       </c>
@@ -3835,7 +4077,7 @@
         <v>1.1200175689030312E-2</v>
       </c>
       <c r="I31" s="6">
-        <f t="shared" ref="I31:N31" si="28">+I4/E4-1</f>
+        <f t="shared" ref="I31:P31" si="28">+I4/E4-1</f>
         <v>1.7508754377188573E-2</v>
       </c>
       <c r="J31" s="6">
@@ -3858,30 +4100,36 @@
         <f t="shared" si="28"/>
         <v>-5.6055900621117982E-2</v>
       </c>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
-      <c r="S31" s="6" t="e">
-        <f t="shared" ref="S31:T31" si="29">+S4/R4-1</f>
+      <c r="O31" s="6">
+        <f t="shared" si="28"/>
+        <v>0.1836506159014557</v>
+      </c>
+      <c r="P31" s="6">
+        <f t="shared" si="28"/>
+        <v>0.14779132930203964</v>
+      </c>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="6" t="e">
+        <f t="shared" ref="W31:X31" si="29">+W4/V4-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T31" s="6">
+      <c r="X31" s="6">
         <f t="shared" si="29"/>
         <v>-6.0068259385670508E-4</v>
       </c>
-      <c r="U31" s="6">
-        <f>+U4/T4-1</f>
+      <c r="Y31" s="6">
+        <f>+Y4/X4-1</f>
         <v>1.9957380542578562E-2</v>
       </c>
-      <c r="V31" s="6">
-        <f>+V4/U4-1</f>
+      <c r="Z31" s="6">
+        <f>+Z4/Y4-1</f>
         <v>2.6008812460658559E-2</v>
       </c>
-      <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="3"/>
       <c r="AA31" s="3"/>
       <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
@@ -3930,8 +4178,12 @@
       <c r="BT31" s="3"/>
       <c r="BU31" s="3"/>
       <c r="BV31" s="3"/>
-    </row>
-    <row r="32" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW31" s="3"/>
+      <c r="BX31" s="3"/>
+      <c r="BY31" s="3"/>
+      <c r="BZ31" s="3"/>
+    </row>
+    <row r="32" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
         <v>36</v>
       </c>
@@ -3945,7 +4197,7 @@
         <v>1.2598425196850505E-2</v>
       </c>
       <c r="I32" s="13">
-        <f t="shared" ref="I32:N32" si="30">+I9/E9-1</f>
+        <f t="shared" ref="I32:P32" si="30">+I9/E9-1</f>
         <v>3.0399999999999983E-2</v>
       </c>
       <c r="J32" s="13">
@@ -3968,30 +4220,36 @@
         <f t="shared" si="30"/>
         <v>0.14967041488949206</v>
       </c>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
-      <c r="S32" s="13" t="e">
-        <f t="shared" ref="S32:T32" si="31">+S9/R9-1</f>
+      <c r="O32" s="13">
+        <f t="shared" si="30"/>
+        <v>0.19497098646034816</v>
+      </c>
+      <c r="P32" s="13">
+        <f t="shared" si="30"/>
+        <v>0.1479853479853479</v>
+      </c>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="13" t="e">
+        <f t="shared" ref="W32:X32" si="31">+W9/V9-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T32" s="13">
+      <c r="X32" s="13">
         <f t="shared" si="31"/>
         <v>3.2363450740173549E-2</v>
       </c>
-      <c r="U32" s="13">
-        <f>+U9/T9-1</f>
+      <c r="Y32" s="13">
+        <f>+Y9/X9-1</f>
         <v>1.6910601265822889E-2</v>
       </c>
-      <c r="V32" s="13">
-        <f>+V9/U9-1</f>
+      <c r="Z32" s="13">
+        <f>+Z9/Y9-1</f>
         <v>7.9451521929398083E-2</v>
       </c>
-      <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="3"/>
       <c r="AA32" s="3"/>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
@@ -4040,8 +4298,12 @@
       <c r="BT32" s="3"/>
       <c r="BU32" s="3"/>
       <c r="BV32" s="3"/>
-    </row>
-    <row r="33" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW32" s="3"/>
+      <c r="BX32" s="3"/>
+      <c r="BY32" s="3"/>
+      <c r="BZ32" s="3"/>
+    </row>
+    <row r="33" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>38</v>
       </c>
@@ -4093,39 +4355,45 @@
         <f t="shared" si="33"/>
         <v>0.71365935919055645</v>
       </c>
-      <c r="O33" s="3"/>
-      <c r="P33" s="6" t="e">
-        <f t="shared" ref="P33:U33" si="34">+P11/P9</f>
+      <c r="O33" s="6">
+        <f t="shared" ref="O33:P33" si="34">+O11/O9</f>
+        <v>0.74036905147296861</v>
+      </c>
+      <c r="P33" s="6">
+        <f t="shared" si="34"/>
+        <v>0.73452456924058707</v>
+      </c>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="6" t="e">
+        <f t="shared" ref="T33:Y33" si="35">+T11/T9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q33" s="6" t="e">
-        <f t="shared" si="34"/>
+      <c r="U33" s="6" t="e">
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R33" s="6" t="e">
-        <f t="shared" si="34"/>
+      <c r="V33" s="6" t="e">
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S33" s="6">
-        <f t="shared" si="34"/>
+      <c r="W33" s="6">
+        <f t="shared" si="35"/>
         <v>0.72639101582440024</v>
       </c>
-      <c r="T33" s="6">
-        <f t="shared" si="34"/>
+      <c r="X33" s="6">
+        <f t="shared" si="35"/>
         <v>0.71983781645569622</v>
       </c>
-      <c r="U33" s="6">
-        <f t="shared" si="34"/>
+      <c r="Y33" s="6">
+        <f t="shared" si="35"/>
         <v>0.71992609160750753</v>
       </c>
-      <c r="V33" s="6">
-        <f t="shared" ref="V33" si="35">+V11/V9</f>
+      <c r="Z33" s="6">
+        <f t="shared" ref="Z33" si="36">+Z11/Z9</f>
         <v>0.71450450450450453</v>
       </c>
-      <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="3"/>
       <c r="AA33" s="3"/>
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
@@ -4174,29 +4442,33 @@
       <c r="BT33" s="3"/>
       <c r="BU33" s="3"/>
       <c r="BV33" s="3"/>
-    </row>
-    <row r="34" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW33" s="3"/>
+      <c r="BX33" s="3"/>
+      <c r="BY33" s="3"/>
+      <c r="BZ33" s="3"/>
+    </row>
+    <row r="34" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C34" s="6">
-        <f t="shared" ref="C34:G34" si="36">+C17/C9</f>
+        <f t="shared" ref="C34:G34" si="37">+C17/C9</f>
         <v>0.22231075697211156</v>
       </c>
       <c r="D34" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.20393700787401575</v>
       </c>
       <c r="E34" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.182</v>
       </c>
       <c r="F34" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.16003122560499611</v>
       </c>
       <c r="G34" s="6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.24687010954616589</v>
       </c>
       <c r="H34" s="6">
@@ -4204,62 +4476,68 @@
         <v>0.21345256609642302</v>
       </c>
       <c r="I34" s="6">
-        <f t="shared" ref="I34:N34" si="37">+I17/I9</f>
+        <f t="shared" ref="I34:N34" si="38">+I17/I9</f>
         <v>0.23097826086956522</v>
       </c>
       <c r="J34" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.21054672353625437</v>
       </c>
       <c r="K34" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.23829787234042554</v>
       </c>
       <c r="L34" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.1772893772893773</v>
       </c>
       <c r="M34" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.20425531914893616</v>
       </c>
       <c r="N34" s="6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.20269814502529512</v>
       </c>
-      <c r="O34" s="3"/>
-      <c r="P34" s="6" t="e">
-        <f t="shared" ref="P34:U34" si="38">+P17/P9</f>
+      <c r="O34" s="6">
+        <f t="shared" ref="O34:P34" si="39">+O17/O9</f>
+        <v>0.19779864033667854</v>
+      </c>
+      <c r="P34" s="6">
+        <f t="shared" si="39"/>
+        <v>0.21569878749202298</v>
+      </c>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="6" t="e">
+        <f t="shared" ref="T34:Y34" si="40">+T17/T9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q34" s="6" t="e">
-        <f t="shared" si="38"/>
+      <c r="U34" s="6" t="e">
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R34" s="6" t="e">
-        <f t="shared" si="38"/>
+      <c r="V34" s="6" t="e">
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S34" s="6">
-        <f t="shared" si="38"/>
+      <c r="W34" s="6">
+        <f t="shared" si="40"/>
         <v>0.23991832567636548</v>
       </c>
-      <c r="T34" s="6">
-        <f t="shared" si="38"/>
+      <c r="X34" s="6">
+        <f t="shared" si="40"/>
         <v>0.19195015822784811</v>
       </c>
-      <c r="U34" s="6">
-        <f t="shared" si="38"/>
+      <c r="Y34" s="6">
+        <f t="shared" si="40"/>
         <v>0.22542059710201304</v>
       </c>
-      <c r="V34" s="6">
-        <f t="shared" ref="V34" si="39">+V17/V9</f>
+      <c r="Z34" s="6">
+        <f t="shared" ref="Z34" si="41">+Z17/Z9</f>
         <v>0.20513513513513512</v>
       </c>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="3"/>
       <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
@@ -4308,29 +4586,33 @@
       <c r="BT34" s="3"/>
       <c r="BU34" s="3"/>
       <c r="BV34" s="3"/>
-    </row>
-    <row r="35" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW34" s="3"/>
+      <c r="BX34" s="3"/>
+      <c r="BY34" s="3"/>
+      <c r="BZ34" s="3"/>
+    </row>
+    <row r="35" spans="2:78" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C35" s="6">
-        <f t="shared" ref="C35:G35" si="40">+C22/C21</f>
+        <f t="shared" ref="C35:G35" si="42">+C22/C21</f>
         <v>0.22054794520547946</v>
       </c>
       <c r="D35" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.39649122807017545</v>
       </c>
       <c r="E35" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.21372667068031306</v>
       </c>
       <c r="F35" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.29388942774005822</v>
       </c>
       <c r="G35" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0.18097014925373134</v>
       </c>
       <c r="H35" s="6">
@@ -4338,62 +4620,68 @@
         <v>0.31097560975609756</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" ref="I35:N35" si="41">+I22/I21</f>
+        <f t="shared" ref="I35:N35" si="43">+I22/I21</f>
         <v>0.20200752823086573</v>
       </c>
       <c r="J35" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-0.10210696920583469</v>
       </c>
       <c r="K35" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.20347003154574134</v>
       </c>
       <c r="L35" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.22641509433962265</v>
       </c>
       <c r="M35" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-4.1884816753926704E-2</v>
       </c>
       <c r="N35" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.15730337078651685</v>
       </c>
-      <c r="O35" s="3"/>
-      <c r="P35" s="6" t="e">
-        <f t="shared" ref="P35:U35" si="42">+P22/P21</f>
+      <c r="O35" s="6">
+        <f t="shared" ref="O35:P35" si="44">+O22/O21</f>
+        <v>0.17152103559870549</v>
+      </c>
+      <c r="P35" s="6">
+        <f t="shared" si="44"/>
+        <v>0.1699248120300752</v>
+      </c>
+      <c r="Q35" s="6"/>
+      <c r="R35" s="6"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="6" t="e">
+        <f t="shared" ref="T35:Y35" si="45">+T22/T21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q35" s="6" t="e">
-        <f t="shared" si="42"/>
+      <c r="U35" s="6" t="e">
+        <f t="shared" si="45"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R35" s="6" t="e">
-        <f t="shared" si="42"/>
+      <c r="V35" s="6" t="e">
+        <f t="shared" si="45"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S35" s="6">
-        <f t="shared" si="42"/>
+      <c r="W35" s="6">
+        <f t="shared" si="45"/>
         <v>0.20424734540911929</v>
       </c>
-      <c r="T35" s="6">
-        <f t="shared" si="42"/>
+      <c r="X35" s="6">
+        <f t="shared" si="45"/>
         <v>0.25141623954680337</v>
       </c>
-      <c r="U35" s="6">
-        <f t="shared" si="42"/>
+      <c r="Y35" s="6">
+        <f t="shared" si="45"/>
         <v>0.13037752414398596</v>
       </c>
-      <c r="V35" s="6">
-        <f t="shared" ref="V35" si="43">+V22/V21</f>
+      <c r="Z35" s="6">
+        <f t="shared" ref="Z35" si="46">+Z22/Z21</f>
         <v>0.13480710879930646</v>
       </c>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
@@ -4442,8 +4730,12 @@
       <c r="BT35" s="3"/>
       <c r="BU35" s="3"/>
       <c r="BV35" s="3"/>
-    </row>
-    <row r="36" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW35" s="3"/>
+      <c r="BX35" s="3"/>
+      <c r="BY35" s="3"/>
+      <c r="BZ35" s="3"/>
+    </row>
+    <row r="36" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -4516,8 +4808,12 @@
       <c r="BT36" s="3"/>
       <c r="BU36" s="3"/>
       <c r="BV36" s="3"/>
-    </row>
-    <row r="37" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW36" s="3"/>
+      <c r="BX36" s="3"/>
+      <c r="BY36" s="3"/>
+      <c r="BZ36" s="3"/>
+    </row>
+    <row r="37" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -4590,8 +4886,12 @@
       <c r="BT37" s="3"/>
       <c r="BU37" s="3"/>
       <c r="BV37" s="3"/>
-    </row>
-    <row r="38" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW37" s="3"/>
+      <c r="BX37" s="3"/>
+      <c r="BY37" s="3"/>
+      <c r="BZ37" s="3"/>
+    </row>
+    <row r="38" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -4664,8 +4964,12 @@
       <c r="BT38" s="3"/>
       <c r="BU38" s="3"/>
       <c r="BV38" s="3"/>
-    </row>
-    <row r="39" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW38" s="3"/>
+      <c r="BX38" s="3"/>
+      <c r="BY38" s="3"/>
+      <c r="BZ38" s="3"/>
+    </row>
+    <row r="39" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4738,8 +5042,12 @@
       <c r="BT39" s="3"/>
       <c r="BU39" s="3"/>
       <c r="BV39" s="3"/>
-    </row>
-    <row r="40" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW39" s="3"/>
+      <c r="BX39" s="3"/>
+      <c r="BY39" s="3"/>
+      <c r="BZ39" s="3"/>
+    </row>
+    <row r="40" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -4812,8 +5120,12 @@
       <c r="BT40" s="3"/>
       <c r="BU40" s="3"/>
       <c r="BV40" s="3"/>
-    </row>
-    <row r="41" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW40" s="3"/>
+      <c r="BX40" s="3"/>
+      <c r="BY40" s="3"/>
+      <c r="BZ40" s="3"/>
+    </row>
+    <row r="41" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -4886,8 +5198,12 @@
       <c r="BT41" s="3"/>
       <c r="BU41" s="3"/>
       <c r="BV41" s="3"/>
-    </row>
-    <row r="42" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW41" s="3"/>
+      <c r="BX41" s="3"/>
+      <c r="BY41" s="3"/>
+      <c r="BZ41" s="3"/>
+    </row>
+    <row r="42" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -4960,8 +5276,12 @@
       <c r="BT42" s="3"/>
       <c r="BU42" s="3"/>
       <c r="BV42" s="3"/>
-    </row>
-    <row r="43" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW42" s="3"/>
+      <c r="BX42" s="3"/>
+      <c r="BY42" s="3"/>
+      <c r="BZ42" s="3"/>
+    </row>
+    <row r="43" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -5034,8 +5354,12 @@
       <c r="BT43" s="3"/>
       <c r="BU43" s="3"/>
       <c r="BV43" s="3"/>
-    </row>
-    <row r="44" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW43" s="3"/>
+      <c r="BX43" s="3"/>
+      <c r="BY43" s="3"/>
+      <c r="BZ43" s="3"/>
+    </row>
+    <row r="44" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -5108,8 +5432,12 @@
       <c r="BT44" s="3"/>
       <c r="BU44" s="3"/>
       <c r="BV44" s="3"/>
-    </row>
-    <row r="45" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW44" s="3"/>
+      <c r="BX44" s="3"/>
+      <c r="BY44" s="3"/>
+      <c r="BZ44" s="3"/>
+    </row>
+    <row r="45" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -5182,8 +5510,12 @@
       <c r="BT45" s="3"/>
       <c r="BU45" s="3"/>
       <c r="BV45" s="3"/>
-    </row>
-    <row r="46" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW45" s="3"/>
+      <c r="BX45" s="3"/>
+      <c r="BY45" s="3"/>
+      <c r="BZ45" s="3"/>
+    </row>
+    <row r="46" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -5256,8 +5588,12 @@
       <c r="BT46" s="3"/>
       <c r="BU46" s="3"/>
       <c r="BV46" s="3"/>
-    </row>
-    <row r="47" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW46" s="3"/>
+      <c r="BX46" s="3"/>
+      <c r="BY46" s="3"/>
+      <c r="BZ46" s="3"/>
+    </row>
+    <row r="47" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -5330,8 +5666,12 @@
       <c r="BT47" s="3"/>
       <c r="BU47" s="3"/>
       <c r="BV47" s="3"/>
-    </row>
-    <row r="48" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW47" s="3"/>
+      <c r="BX47" s="3"/>
+      <c r="BY47" s="3"/>
+      <c r="BZ47" s="3"/>
+    </row>
+    <row r="48" spans="2:78" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -5404,8 +5744,12 @@
       <c r="BT48" s="3"/>
       <c r="BU48" s="3"/>
       <c r="BV48" s="3"/>
-    </row>
-    <row r="49" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW48" s="3"/>
+      <c r="BX48" s="3"/>
+      <c r="BY48" s="3"/>
+      <c r="BZ48" s="3"/>
+    </row>
+    <row r="49" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -5478,8 +5822,12 @@
       <c r="BT49" s="3"/>
       <c r="BU49" s="3"/>
       <c r="BV49" s="3"/>
-    </row>
-    <row r="50" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW49" s="3"/>
+      <c r="BX49" s="3"/>
+      <c r="BY49" s="3"/>
+      <c r="BZ49" s="3"/>
+    </row>
+    <row r="50" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -5552,8 +5900,12 @@
       <c r="BT50" s="3"/>
       <c r="BU50" s="3"/>
       <c r="BV50" s="3"/>
-    </row>
-    <row r="51" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW50" s="3"/>
+      <c r="BX50" s="3"/>
+      <c r="BY50" s="3"/>
+      <c r="BZ50" s="3"/>
+    </row>
+    <row r="51" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -5626,8 +5978,12 @@
       <c r="BT51" s="3"/>
       <c r="BU51" s="3"/>
       <c r="BV51" s="3"/>
-    </row>
-    <row r="52" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW51" s="3"/>
+      <c r="BX51" s="3"/>
+      <c r="BY51" s="3"/>
+      <c r="BZ51" s="3"/>
+    </row>
+    <row r="52" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -5700,8 +6056,12 @@
       <c r="BT52" s="3"/>
       <c r="BU52" s="3"/>
       <c r="BV52" s="3"/>
-    </row>
-    <row r="53" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW52" s="3"/>
+      <c r="BX52" s="3"/>
+      <c r="BY52" s="3"/>
+      <c r="BZ52" s="3"/>
+    </row>
+    <row r="53" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -5774,8 +6134,12 @@
       <c r="BT53" s="3"/>
       <c r="BU53" s="3"/>
       <c r="BV53" s="3"/>
-    </row>
-    <row r="54" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW53" s="3"/>
+      <c r="BX53" s="3"/>
+      <c r="BY53" s="3"/>
+      <c r="BZ53" s="3"/>
+    </row>
+    <row r="54" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -5848,8 +6212,12 @@
       <c r="BT54" s="3"/>
       <c r="BU54" s="3"/>
       <c r="BV54" s="3"/>
-    </row>
-    <row r="55" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW54" s="3"/>
+      <c r="BX54" s="3"/>
+      <c r="BY54" s="3"/>
+      <c r="BZ54" s="3"/>
+    </row>
+    <row r="55" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -5922,8 +6290,12 @@
       <c r="BT55" s="3"/>
       <c r="BU55" s="3"/>
       <c r="BV55" s="3"/>
-    </row>
-    <row r="56" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW55" s="3"/>
+      <c r="BX55" s="3"/>
+      <c r="BY55" s="3"/>
+      <c r="BZ55" s="3"/>
+    </row>
+    <row r="56" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -5996,8 +6368,12 @@
       <c r="BT56" s="3"/>
       <c r="BU56" s="3"/>
       <c r="BV56" s="3"/>
-    </row>
-    <row r="57" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW56" s="3"/>
+      <c r="BX56" s="3"/>
+      <c r="BY56" s="3"/>
+      <c r="BZ56" s="3"/>
+    </row>
+    <row r="57" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -6070,8 +6446,12 @@
       <c r="BT57" s="3"/>
       <c r="BU57" s="3"/>
       <c r="BV57" s="3"/>
-    </row>
-    <row r="58" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW57" s="3"/>
+      <c r="BX57" s="3"/>
+      <c r="BY57" s="3"/>
+      <c r="BZ57" s="3"/>
+    </row>
+    <row r="58" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -6144,8 +6524,12 @@
       <c r="BT58" s="3"/>
       <c r="BU58" s="3"/>
       <c r="BV58" s="3"/>
-    </row>
-    <row r="59" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW58" s="3"/>
+      <c r="BX58" s="3"/>
+      <c r="BY58" s="3"/>
+      <c r="BZ58" s="3"/>
+    </row>
+    <row r="59" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -6218,8 +6602,12 @@
       <c r="BT59" s="3"/>
       <c r="BU59" s="3"/>
       <c r="BV59" s="3"/>
-    </row>
-    <row r="60" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW59" s="3"/>
+      <c r="BX59" s="3"/>
+      <c r="BY59" s="3"/>
+      <c r="BZ59" s="3"/>
+    </row>
+    <row r="60" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -6292,8 +6680,12 @@
       <c r="BT60" s="3"/>
       <c r="BU60" s="3"/>
       <c r="BV60" s="3"/>
-    </row>
-    <row r="61" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW60" s="3"/>
+      <c r="BX60" s="3"/>
+      <c r="BY60" s="3"/>
+      <c r="BZ60" s="3"/>
+    </row>
+    <row r="61" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -6366,8 +6758,12 @@
       <c r="BT61" s="3"/>
       <c r="BU61" s="3"/>
       <c r="BV61" s="3"/>
-    </row>
-    <row r="62" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW61" s="3"/>
+      <c r="BX61" s="3"/>
+      <c r="BY61" s="3"/>
+      <c r="BZ61" s="3"/>
+    </row>
+    <row r="62" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -6440,8 +6836,12 @@
       <c r="BT62" s="3"/>
       <c r="BU62" s="3"/>
       <c r="BV62" s="3"/>
-    </row>
-    <row r="63" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW62" s="3"/>
+      <c r="BX62" s="3"/>
+      <c r="BY62" s="3"/>
+      <c r="BZ62" s="3"/>
+    </row>
+    <row r="63" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -6514,8 +6914,12 @@
       <c r="BT63" s="3"/>
       <c r="BU63" s="3"/>
       <c r="BV63" s="3"/>
-    </row>
-    <row r="64" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW63" s="3"/>
+      <c r="BX63" s="3"/>
+      <c r="BY63" s="3"/>
+      <c r="BZ63" s="3"/>
+    </row>
+    <row r="64" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -6588,8 +6992,12 @@
       <c r="BT64" s="3"/>
       <c r="BU64" s="3"/>
       <c r="BV64" s="3"/>
-    </row>
-    <row r="65" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW64" s="3"/>
+      <c r="BX64" s="3"/>
+      <c r="BY64" s="3"/>
+      <c r="BZ64" s="3"/>
+    </row>
+    <row r="65" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -6662,8 +7070,12 @@
       <c r="BT65" s="3"/>
       <c r="BU65" s="3"/>
       <c r="BV65" s="3"/>
-    </row>
-    <row r="66" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW65" s="3"/>
+      <c r="BX65" s="3"/>
+      <c r="BY65" s="3"/>
+      <c r="BZ65" s="3"/>
+    </row>
+    <row r="66" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -6736,8 +7148,12 @@
       <c r="BT66" s="3"/>
       <c r="BU66" s="3"/>
       <c r="BV66" s="3"/>
-    </row>
-    <row r="67" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW66" s="3"/>
+      <c r="BX66" s="3"/>
+      <c r="BY66" s="3"/>
+      <c r="BZ66" s="3"/>
+    </row>
+    <row r="67" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -6810,8 +7226,12 @@
       <c r="BT67" s="3"/>
       <c r="BU67" s="3"/>
       <c r="BV67" s="3"/>
-    </row>
-    <row r="68" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW67" s="3"/>
+      <c r="BX67" s="3"/>
+      <c r="BY67" s="3"/>
+      <c r="BZ67" s="3"/>
+    </row>
+    <row r="68" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -6884,8 +7304,12 @@
       <c r="BT68" s="3"/>
       <c r="BU68" s="3"/>
       <c r="BV68" s="3"/>
-    </row>
-    <row r="69" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW68" s="3"/>
+      <c r="BX68" s="3"/>
+      <c r="BY68" s="3"/>
+      <c r="BZ68" s="3"/>
+    </row>
+    <row r="69" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -6958,8 +7382,12 @@
       <c r="BT69" s="3"/>
       <c r="BU69" s="3"/>
       <c r="BV69" s="3"/>
-    </row>
-    <row r="70" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW69" s="3"/>
+      <c r="BX69" s="3"/>
+      <c r="BY69" s="3"/>
+      <c r="BZ69" s="3"/>
+    </row>
+    <row r="70" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -7032,8 +7460,12 @@
       <c r="BT70" s="3"/>
       <c r="BU70" s="3"/>
       <c r="BV70" s="3"/>
-    </row>
-    <row r="71" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW70" s="3"/>
+      <c r="BX70" s="3"/>
+      <c r="BY70" s="3"/>
+      <c r="BZ70" s="3"/>
+    </row>
+    <row r="71" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -7106,8 +7538,12 @@
       <c r="BT71" s="3"/>
       <c r="BU71" s="3"/>
       <c r="BV71" s="3"/>
-    </row>
-    <row r="72" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW71" s="3"/>
+      <c r="BX71" s="3"/>
+      <c r="BY71" s="3"/>
+      <c r="BZ71" s="3"/>
+    </row>
+    <row r="72" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -7180,8 +7616,12 @@
       <c r="BT72" s="3"/>
       <c r="BU72" s="3"/>
       <c r="BV72" s="3"/>
-    </row>
-    <row r="73" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW72" s="3"/>
+      <c r="BX72" s="3"/>
+      <c r="BY72" s="3"/>
+      <c r="BZ72" s="3"/>
+    </row>
+    <row r="73" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -7254,8 +7694,12 @@
       <c r="BT73" s="3"/>
       <c r="BU73" s="3"/>
       <c r="BV73" s="3"/>
-    </row>
-    <row r="74" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW73" s="3"/>
+      <c r="BX73" s="3"/>
+      <c r="BY73" s="3"/>
+      <c r="BZ73" s="3"/>
+    </row>
+    <row r="74" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -7328,8 +7772,12 @@
       <c r="BT74" s="3"/>
       <c r="BU74" s="3"/>
       <c r="BV74" s="3"/>
-    </row>
-    <row r="75" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW74" s="3"/>
+      <c r="BX74" s="3"/>
+      <c r="BY74" s="3"/>
+      <c r="BZ74" s="3"/>
+    </row>
+    <row r="75" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -7402,8 +7850,12 @@
       <c r="BT75" s="3"/>
       <c r="BU75" s="3"/>
       <c r="BV75" s="3"/>
-    </row>
-    <row r="76" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW75" s="3"/>
+      <c r="BX75" s="3"/>
+      <c r="BY75" s="3"/>
+      <c r="BZ75" s="3"/>
+    </row>
+    <row r="76" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -7476,8 +7928,12 @@
       <c r="BT76" s="3"/>
       <c r="BU76" s="3"/>
       <c r="BV76" s="3"/>
-    </row>
-    <row r="77" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW76" s="3"/>
+      <c r="BX76" s="3"/>
+      <c r="BY76" s="3"/>
+      <c r="BZ76" s="3"/>
+    </row>
+    <row r="77" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -7550,8 +8006,12 @@
       <c r="BT77" s="3"/>
       <c r="BU77" s="3"/>
       <c r="BV77" s="3"/>
-    </row>
-    <row r="78" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW77" s="3"/>
+      <c r="BX77" s="3"/>
+      <c r="BY77" s="3"/>
+      <c r="BZ77" s="3"/>
+    </row>
+    <row r="78" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -7624,8 +8084,12 @@
       <c r="BT78" s="3"/>
       <c r="BU78" s="3"/>
       <c r="BV78" s="3"/>
-    </row>
-    <row r="79" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW78" s="3"/>
+      <c r="BX78" s="3"/>
+      <c r="BY78" s="3"/>
+      <c r="BZ78" s="3"/>
+    </row>
+    <row r="79" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -7698,8 +8162,12 @@
       <c r="BT79" s="3"/>
       <c r="BU79" s="3"/>
       <c r="BV79" s="3"/>
-    </row>
-    <row r="80" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW79" s="3"/>
+      <c r="BX79" s="3"/>
+      <c r="BY79" s="3"/>
+      <c r="BZ79" s="3"/>
+    </row>
+    <row r="80" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -7772,8 +8240,12 @@
       <c r="BT80" s="3"/>
       <c r="BU80" s="3"/>
       <c r="BV80" s="3"/>
-    </row>
-    <row r="81" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW80" s="3"/>
+      <c r="BX80" s="3"/>
+      <c r="BY80" s="3"/>
+      <c r="BZ80" s="3"/>
+    </row>
+    <row r="81" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -7846,8 +8318,12 @@
       <c r="BT81" s="3"/>
       <c r="BU81" s="3"/>
       <c r="BV81" s="3"/>
-    </row>
-    <row r="82" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW81" s="3"/>
+      <c r="BX81" s="3"/>
+      <c r="BY81" s="3"/>
+      <c r="BZ81" s="3"/>
+    </row>
+    <row r="82" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -7920,8 +8396,12 @@
       <c r="BT82" s="3"/>
       <c r="BU82" s="3"/>
       <c r="BV82" s="3"/>
-    </row>
-    <row r="83" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW82" s="3"/>
+      <c r="BX82" s="3"/>
+      <c r="BY82" s="3"/>
+      <c r="BZ82" s="3"/>
+    </row>
+    <row r="83" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -7994,8 +8474,12 @@
       <c r="BT83" s="3"/>
       <c r="BU83" s="3"/>
       <c r="BV83" s="3"/>
-    </row>
-    <row r="84" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW83" s="3"/>
+      <c r="BX83" s="3"/>
+      <c r="BY83" s="3"/>
+      <c r="BZ83" s="3"/>
+    </row>
+    <row r="84" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -8068,8 +8552,12 @@
       <c r="BT84" s="3"/>
       <c r="BU84" s="3"/>
       <c r="BV84" s="3"/>
-    </row>
-    <row r="85" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW84" s="3"/>
+      <c r="BX84" s="3"/>
+      <c r="BY84" s="3"/>
+      <c r="BZ84" s="3"/>
+    </row>
+    <row r="85" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -8142,8 +8630,12 @@
       <c r="BT85" s="3"/>
       <c r="BU85" s="3"/>
       <c r="BV85" s="3"/>
-    </row>
-    <row r="86" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW85" s="3"/>
+      <c r="BX85" s="3"/>
+      <c r="BY85" s="3"/>
+      <c r="BZ85" s="3"/>
+    </row>
+    <row r="86" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -8216,8 +8708,12 @@
       <c r="BT86" s="3"/>
       <c r="BU86" s="3"/>
       <c r="BV86" s="3"/>
-    </row>
-    <row r="87" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW86" s="3"/>
+      <c r="BX86" s="3"/>
+      <c r="BY86" s="3"/>
+      <c r="BZ86" s="3"/>
+    </row>
+    <row r="87" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -8290,8 +8786,12 @@
       <c r="BT87" s="3"/>
       <c r="BU87" s="3"/>
       <c r="BV87" s="3"/>
-    </row>
-    <row r="88" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW87" s="3"/>
+      <c r="BX87" s="3"/>
+      <c r="BY87" s="3"/>
+      <c r="BZ87" s="3"/>
+    </row>
+    <row r="88" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -8364,8 +8864,12 @@
       <c r="BT88" s="3"/>
       <c r="BU88" s="3"/>
       <c r="BV88" s="3"/>
-    </row>
-    <row r="89" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW88" s="3"/>
+      <c r="BX88" s="3"/>
+      <c r="BY88" s="3"/>
+      <c r="BZ88" s="3"/>
+    </row>
+    <row r="89" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -8438,8 +8942,12 @@
       <c r="BT89" s="3"/>
       <c r="BU89" s="3"/>
       <c r="BV89" s="3"/>
-    </row>
-    <row r="90" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW89" s="3"/>
+      <c r="BX89" s="3"/>
+      <c r="BY89" s="3"/>
+      <c r="BZ89" s="3"/>
+    </row>
+    <row r="90" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -8512,8 +9020,12 @@
       <c r="BT90" s="3"/>
       <c r="BU90" s="3"/>
       <c r="BV90" s="3"/>
-    </row>
-    <row r="91" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW90" s="3"/>
+      <c r="BX90" s="3"/>
+      <c r="BY90" s="3"/>
+      <c r="BZ90" s="3"/>
+    </row>
+    <row r="91" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -8586,8 +9098,12 @@
       <c r="BT91" s="3"/>
       <c r="BU91" s="3"/>
       <c r="BV91" s="3"/>
-    </row>
-    <row r="92" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW91" s="3"/>
+      <c r="BX91" s="3"/>
+      <c r="BY91" s="3"/>
+      <c r="BZ91" s="3"/>
+    </row>
+    <row r="92" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -8660,8 +9176,12 @@
       <c r="BT92" s="3"/>
       <c r="BU92" s="3"/>
       <c r="BV92" s="3"/>
-    </row>
-    <row r="93" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW92" s="3"/>
+      <c r="BX92" s="3"/>
+      <c r="BY92" s="3"/>
+      <c r="BZ92" s="3"/>
+    </row>
+    <row r="93" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -8734,8 +9254,12 @@
       <c r="BT93" s="3"/>
       <c r="BU93" s="3"/>
       <c r="BV93" s="3"/>
-    </row>
-    <row r="94" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW93" s="3"/>
+      <c r="BX93" s="3"/>
+      <c r="BY93" s="3"/>
+      <c r="BZ93" s="3"/>
+    </row>
+    <row r="94" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -8808,8 +9332,12 @@
       <c r="BT94" s="3"/>
       <c r="BU94" s="3"/>
       <c r="BV94" s="3"/>
-    </row>
-    <row r="95" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW94" s="3"/>
+      <c r="BX94" s="3"/>
+      <c r="BY94" s="3"/>
+      <c r="BZ94" s="3"/>
+    </row>
+    <row r="95" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -8882,8 +9410,12 @@
       <c r="BT95" s="3"/>
       <c r="BU95" s="3"/>
       <c r="BV95" s="3"/>
-    </row>
-    <row r="96" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW95" s="3"/>
+      <c r="BX95" s="3"/>
+      <c r="BY95" s="3"/>
+      <c r="BZ95" s="3"/>
+    </row>
+    <row r="96" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -8956,8 +9488,12 @@
       <c r="BT96" s="3"/>
       <c r="BU96" s="3"/>
       <c r="BV96" s="3"/>
-    </row>
-    <row r="97" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW96" s="3"/>
+      <c r="BX96" s="3"/>
+      <c r="BY96" s="3"/>
+      <c r="BZ96" s="3"/>
+    </row>
+    <row r="97" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -9030,8 +9566,12 @@
       <c r="BT97" s="3"/>
       <c r="BU97" s="3"/>
       <c r="BV97" s="3"/>
-    </row>
-    <row r="98" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW97" s="3"/>
+      <c r="BX97" s="3"/>
+      <c r="BY97" s="3"/>
+      <c r="BZ97" s="3"/>
+    </row>
+    <row r="98" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -9104,8 +9644,12 @@
       <c r="BT98" s="3"/>
       <c r="BU98" s="3"/>
       <c r="BV98" s="3"/>
-    </row>
-    <row r="99" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW98" s="3"/>
+      <c r="BX98" s="3"/>
+      <c r="BY98" s="3"/>
+      <c r="BZ98" s="3"/>
+    </row>
+    <row r="99" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -9178,8 +9722,12 @@
       <c r="BT99" s="3"/>
       <c r="BU99" s="3"/>
       <c r="BV99" s="3"/>
-    </row>
-    <row r="100" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW99" s="3"/>
+      <c r="BX99" s="3"/>
+      <c r="BY99" s="3"/>
+      <c r="BZ99" s="3"/>
+    </row>
+    <row r="100" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -9252,8 +9800,12 @@
       <c r="BT100" s="3"/>
       <c r="BU100" s="3"/>
       <c r="BV100" s="3"/>
-    </row>
-    <row r="101" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW100" s="3"/>
+      <c r="BX100" s="3"/>
+      <c r="BY100" s="3"/>
+      <c r="BZ100" s="3"/>
+    </row>
+    <row r="101" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -9326,8 +9878,12 @@
       <c r="BT101" s="3"/>
       <c r="BU101" s="3"/>
       <c r="BV101" s="3"/>
-    </row>
-    <row r="102" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW101" s="3"/>
+      <c r="BX101" s="3"/>
+      <c r="BY101" s="3"/>
+      <c r="BZ101" s="3"/>
+    </row>
+    <row r="102" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -9400,8 +9956,12 @@
       <c r="BT102" s="3"/>
       <c r="BU102" s="3"/>
       <c r="BV102" s="3"/>
-    </row>
-    <row r="103" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW102" s="3"/>
+      <c r="BX102" s="3"/>
+      <c r="BY102" s="3"/>
+      <c r="BZ102" s="3"/>
+    </row>
+    <row r="103" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -9474,8 +10034,12 @@
       <c r="BT103" s="3"/>
       <c r="BU103" s="3"/>
       <c r="BV103" s="3"/>
-    </row>
-    <row r="104" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW103" s="3"/>
+      <c r="BX103" s="3"/>
+      <c r="BY103" s="3"/>
+      <c r="BZ103" s="3"/>
+    </row>
+    <row r="104" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -9548,8 +10112,12 @@
       <c r="BT104" s="3"/>
       <c r="BU104" s="3"/>
       <c r="BV104" s="3"/>
-    </row>
-    <row r="105" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW104" s="3"/>
+      <c r="BX104" s="3"/>
+      <c r="BY104" s="3"/>
+      <c r="BZ104" s="3"/>
+    </row>
+    <row r="105" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -9622,8 +10190,12 @@
       <c r="BT105" s="3"/>
       <c r="BU105" s="3"/>
       <c r="BV105" s="3"/>
-    </row>
-    <row r="106" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW105" s="3"/>
+      <c r="BX105" s="3"/>
+      <c r="BY105" s="3"/>
+      <c r="BZ105" s="3"/>
+    </row>
+    <row r="106" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -9696,8 +10268,12 @@
       <c r="BT106" s="3"/>
       <c r="BU106" s="3"/>
       <c r="BV106" s="3"/>
-    </row>
-    <row r="107" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW106" s="3"/>
+      <c r="BX106" s="3"/>
+      <c r="BY106" s="3"/>
+      <c r="BZ106" s="3"/>
+    </row>
+    <row r="107" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -9770,8 +10346,12 @@
       <c r="BT107" s="3"/>
       <c r="BU107" s="3"/>
       <c r="BV107" s="3"/>
-    </row>
-    <row r="108" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW107" s="3"/>
+      <c r="BX107" s="3"/>
+      <c r="BY107" s="3"/>
+      <c r="BZ107" s="3"/>
+    </row>
+    <row r="108" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -9844,8 +10424,12 @@
       <c r="BT108" s="3"/>
       <c r="BU108" s="3"/>
       <c r="BV108" s="3"/>
-    </row>
-    <row r="109" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW108" s="3"/>
+      <c r="BX108" s="3"/>
+      <c r="BY108" s="3"/>
+      <c r="BZ108" s="3"/>
+    </row>
+    <row r="109" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -9918,8 +10502,12 @@
       <c r="BT109" s="3"/>
       <c r="BU109" s="3"/>
       <c r="BV109" s="3"/>
-    </row>
-    <row r="110" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW109" s="3"/>
+      <c r="BX109" s="3"/>
+      <c r="BY109" s="3"/>
+      <c r="BZ109" s="3"/>
+    </row>
+    <row r="110" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -9992,8 +10580,12 @@
       <c r="BT110" s="3"/>
       <c r="BU110" s="3"/>
       <c r="BV110" s="3"/>
-    </row>
-    <row r="111" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW110" s="3"/>
+      <c r="BX110" s="3"/>
+      <c r="BY110" s="3"/>
+      <c r="BZ110" s="3"/>
+    </row>
+    <row r="111" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -10066,8 +10658,12 @@
       <c r="BT111" s="3"/>
       <c r="BU111" s="3"/>
       <c r="BV111" s="3"/>
-    </row>
-    <row r="112" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW111" s="3"/>
+      <c r="BX111" s="3"/>
+      <c r="BY111" s="3"/>
+      <c r="BZ111" s="3"/>
+    </row>
+    <row r="112" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -10140,8 +10736,12 @@
       <c r="BT112" s="3"/>
       <c r="BU112" s="3"/>
       <c r="BV112" s="3"/>
-    </row>
-    <row r="113" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW112" s="3"/>
+      <c r="BX112" s="3"/>
+      <c r="BY112" s="3"/>
+      <c r="BZ112" s="3"/>
+    </row>
+    <row r="113" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -10214,8 +10814,12 @@
       <c r="BT113" s="3"/>
       <c r="BU113" s="3"/>
       <c r="BV113" s="3"/>
-    </row>
-    <row r="114" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW113" s="3"/>
+      <c r="BX113" s="3"/>
+      <c r="BY113" s="3"/>
+      <c r="BZ113" s="3"/>
+    </row>
+    <row r="114" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -10288,8 +10892,12 @@
       <c r="BT114" s="3"/>
       <c r="BU114" s="3"/>
       <c r="BV114" s="3"/>
-    </row>
-    <row r="115" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW114" s="3"/>
+      <c r="BX114" s="3"/>
+      <c r="BY114" s="3"/>
+      <c r="BZ114" s="3"/>
+    </row>
+    <row r="115" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -10362,8 +10970,12 @@
       <c r="BT115" s="3"/>
       <c r="BU115" s="3"/>
       <c r="BV115" s="3"/>
-    </row>
-    <row r="116" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW115" s="3"/>
+      <c r="BX115" s="3"/>
+      <c r="BY115" s="3"/>
+      <c r="BZ115" s="3"/>
+    </row>
+    <row r="116" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -10436,8 +11048,12 @@
       <c r="BT116" s="3"/>
       <c r="BU116" s="3"/>
       <c r="BV116" s="3"/>
-    </row>
-    <row r="117" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW116" s="3"/>
+      <c r="BX116" s="3"/>
+      <c r="BY116" s="3"/>
+      <c r="BZ116" s="3"/>
+    </row>
+    <row r="117" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -10510,8 +11126,12 @@
       <c r="BT117" s="3"/>
       <c r="BU117" s="3"/>
       <c r="BV117" s="3"/>
-    </row>
-    <row r="118" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW117" s="3"/>
+      <c r="BX117" s="3"/>
+      <c r="BY117" s="3"/>
+      <c r="BZ117" s="3"/>
+    </row>
+    <row r="118" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -10584,8 +11204,12 @@
       <c r="BT118" s="3"/>
       <c r="BU118" s="3"/>
       <c r="BV118" s="3"/>
-    </row>
-    <row r="119" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW118" s="3"/>
+      <c r="BX118" s="3"/>
+      <c r="BY118" s="3"/>
+      <c r="BZ118" s="3"/>
+    </row>
+    <row r="119" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -10658,8 +11282,12 @@
       <c r="BT119" s="3"/>
       <c r="BU119" s="3"/>
       <c r="BV119" s="3"/>
-    </row>
-    <row r="120" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW119" s="3"/>
+      <c r="BX119" s="3"/>
+      <c r="BY119" s="3"/>
+      <c r="BZ119" s="3"/>
+    </row>
+    <row r="120" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -10732,8 +11360,12 @@
       <c r="BT120" s="3"/>
       <c r="BU120" s="3"/>
       <c r="BV120" s="3"/>
-    </row>
-    <row r="121" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW120" s="3"/>
+      <c r="BX120" s="3"/>
+      <c r="BY120" s="3"/>
+      <c r="BZ120" s="3"/>
+    </row>
+    <row r="121" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -10806,8 +11438,12 @@
       <c r="BT121" s="3"/>
       <c r="BU121" s="3"/>
       <c r="BV121" s="3"/>
-    </row>
-    <row r="122" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW121" s="3"/>
+      <c r="BX121" s="3"/>
+      <c r="BY121" s="3"/>
+      <c r="BZ121" s="3"/>
+    </row>
+    <row r="122" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -10880,8 +11516,12 @@
       <c r="BT122" s="3"/>
       <c r="BU122" s="3"/>
       <c r="BV122" s="3"/>
-    </row>
-    <row r="123" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW122" s="3"/>
+      <c r="BX122" s="3"/>
+      <c r="BY122" s="3"/>
+      <c r="BZ122" s="3"/>
+    </row>
+    <row r="123" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -10954,8 +11594,12 @@
       <c r="BT123" s="3"/>
       <c r="BU123" s="3"/>
       <c r="BV123" s="3"/>
-    </row>
-    <row r="124" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW123" s="3"/>
+      <c r="BX123" s="3"/>
+      <c r="BY123" s="3"/>
+      <c r="BZ123" s="3"/>
+    </row>
+    <row r="124" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -11028,8 +11672,12 @@
       <c r="BT124" s="3"/>
       <c r="BU124" s="3"/>
       <c r="BV124" s="3"/>
-    </row>
-    <row r="125" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW124" s="3"/>
+      <c r="BX124" s="3"/>
+      <c r="BY124" s="3"/>
+      <c r="BZ124" s="3"/>
+    </row>
+    <row r="125" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -11102,8 +11750,12 @@
       <c r="BT125" s="3"/>
       <c r="BU125" s="3"/>
       <c r="BV125" s="3"/>
-    </row>
-    <row r="126" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW125" s="3"/>
+      <c r="BX125" s="3"/>
+      <c r="BY125" s="3"/>
+      <c r="BZ125" s="3"/>
+    </row>
+    <row r="126" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -11176,8 +11828,12 @@
       <c r="BT126" s="3"/>
       <c r="BU126" s="3"/>
       <c r="BV126" s="3"/>
-    </row>
-    <row r="127" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW126" s="3"/>
+      <c r="BX126" s="3"/>
+      <c r="BY126" s="3"/>
+      <c r="BZ126" s="3"/>
+    </row>
+    <row r="127" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -11250,8 +11906,12 @@
       <c r="BT127" s="3"/>
       <c r="BU127" s="3"/>
       <c r="BV127" s="3"/>
-    </row>
-    <row r="128" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW127" s="3"/>
+      <c r="BX127" s="3"/>
+      <c r="BY127" s="3"/>
+      <c r="BZ127" s="3"/>
+    </row>
+    <row r="128" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -11324,8 +11984,12 @@
       <c r="BT128" s="3"/>
       <c r="BU128" s="3"/>
       <c r="BV128" s="3"/>
-    </row>
-    <row r="129" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW128" s="3"/>
+      <c r="BX128" s="3"/>
+      <c r="BY128" s="3"/>
+      <c r="BZ128" s="3"/>
+    </row>
+    <row r="129" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -11398,8 +12062,12 @@
       <c r="BT129" s="3"/>
       <c r="BU129" s="3"/>
       <c r="BV129" s="3"/>
-    </row>
-    <row r="130" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW129" s="3"/>
+      <c r="BX129" s="3"/>
+      <c r="BY129" s="3"/>
+      <c r="BZ129" s="3"/>
+    </row>
+    <row r="130" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -11472,8 +12140,12 @@
       <c r="BT130" s="3"/>
       <c r="BU130" s="3"/>
       <c r="BV130" s="3"/>
-    </row>
-    <row r="131" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW130" s="3"/>
+      <c r="BX130" s="3"/>
+      <c r="BY130" s="3"/>
+      <c r="BZ130" s="3"/>
+    </row>
+    <row r="131" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -11546,8 +12218,12 @@
       <c r="BT131" s="3"/>
       <c r="BU131" s="3"/>
       <c r="BV131" s="3"/>
-    </row>
-    <row r="132" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW131" s="3"/>
+      <c r="BX131" s="3"/>
+      <c r="BY131" s="3"/>
+      <c r="BZ131" s="3"/>
+    </row>
+    <row r="132" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -11620,8 +12296,12 @@
       <c r="BT132" s="3"/>
       <c r="BU132" s="3"/>
       <c r="BV132" s="3"/>
-    </row>
-    <row r="133" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW132" s="3"/>
+      <c r="BX132" s="3"/>
+      <c r="BY132" s="3"/>
+      <c r="BZ132" s="3"/>
+    </row>
+    <row r="133" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -11694,8 +12374,12 @@
       <c r="BT133" s="3"/>
       <c r="BU133" s="3"/>
       <c r="BV133" s="3"/>
-    </row>
-    <row r="134" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW133" s="3"/>
+      <c r="BX133" s="3"/>
+      <c r="BY133" s="3"/>
+      <c r="BZ133" s="3"/>
+    </row>
+    <row r="134" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -11768,8 +12452,12 @@
       <c r="BT134" s="3"/>
       <c r="BU134" s="3"/>
       <c r="BV134" s="3"/>
-    </row>
-    <row r="135" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW134" s="3"/>
+      <c r="BX134" s="3"/>
+      <c r="BY134" s="3"/>
+      <c r="BZ134" s="3"/>
+    </row>
+    <row r="135" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -11842,8 +12530,12 @@
       <c r="BT135" s="3"/>
       <c r="BU135" s="3"/>
       <c r="BV135" s="3"/>
-    </row>
-    <row r="136" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW135" s="3"/>
+      <c r="BX135" s="3"/>
+      <c r="BY135" s="3"/>
+      <c r="BZ135" s="3"/>
+    </row>
+    <row r="136" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -11916,8 +12608,12 @@
       <c r="BT136" s="3"/>
       <c r="BU136" s="3"/>
       <c r="BV136" s="3"/>
-    </row>
-    <row r="137" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW136" s="3"/>
+      <c r="BX136" s="3"/>
+      <c r="BY136" s="3"/>
+      <c r="BZ136" s="3"/>
+    </row>
+    <row r="137" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -11990,8 +12686,12 @@
       <c r="BT137" s="3"/>
       <c r="BU137" s="3"/>
       <c r="BV137" s="3"/>
-    </row>
-    <row r="138" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW137" s="3"/>
+      <c r="BX137" s="3"/>
+      <c r="BY137" s="3"/>
+      <c r="BZ137" s="3"/>
+    </row>
+    <row r="138" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -12064,8 +12764,12 @@
       <c r="BT138" s="3"/>
       <c r="BU138" s="3"/>
       <c r="BV138" s="3"/>
-    </row>
-    <row r="139" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW138" s="3"/>
+      <c r="BX138" s="3"/>
+      <c r="BY138" s="3"/>
+      <c r="BZ138" s="3"/>
+    </row>
+    <row r="139" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -12138,8 +12842,12 @@
       <c r="BT139" s="3"/>
       <c r="BU139" s="3"/>
       <c r="BV139" s="3"/>
-    </row>
-    <row r="140" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW139" s="3"/>
+      <c r="BX139" s="3"/>
+      <c r="BY139" s="3"/>
+      <c r="BZ139" s="3"/>
+    </row>
+    <row r="140" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -12212,8 +12920,12 @@
       <c r="BT140" s="3"/>
       <c r="BU140" s="3"/>
       <c r="BV140" s="3"/>
-    </row>
-    <row r="141" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW140" s="3"/>
+      <c r="BX140" s="3"/>
+      <c r="BY140" s="3"/>
+      <c r="BZ140" s="3"/>
+    </row>
+    <row r="141" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -12286,8 +12998,12 @@
       <c r="BT141" s="3"/>
       <c r="BU141" s="3"/>
       <c r="BV141" s="3"/>
-    </row>
-    <row r="142" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW141" s="3"/>
+      <c r="BX141" s="3"/>
+      <c r="BY141" s="3"/>
+      <c r="BZ141" s="3"/>
+    </row>
+    <row r="142" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -12360,8 +13076,12 @@
       <c r="BT142" s="3"/>
       <c r="BU142" s="3"/>
       <c r="BV142" s="3"/>
-    </row>
-    <row r="143" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW142" s="3"/>
+      <c r="BX142" s="3"/>
+      <c r="BY142" s="3"/>
+      <c r="BZ142" s="3"/>
+    </row>
+    <row r="143" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -12434,8 +13154,12 @@
       <c r="BT143" s="3"/>
       <c r="BU143" s="3"/>
       <c r="BV143" s="3"/>
-    </row>
-    <row r="144" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW143" s="3"/>
+      <c r="BX143" s="3"/>
+      <c r="BY143" s="3"/>
+      <c r="BZ143" s="3"/>
+    </row>
+    <row r="144" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -12508,8 +13232,12 @@
       <c r="BT144" s="3"/>
       <c r="BU144" s="3"/>
       <c r="BV144" s="3"/>
-    </row>
-    <row r="145" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW144" s="3"/>
+      <c r="BX144" s="3"/>
+      <c r="BY144" s="3"/>
+      <c r="BZ144" s="3"/>
+    </row>
+    <row r="145" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -12582,8 +13310,12 @@
       <c r="BT145" s="3"/>
       <c r="BU145" s="3"/>
       <c r="BV145" s="3"/>
-    </row>
-    <row r="146" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW145" s="3"/>
+      <c r="BX145" s="3"/>
+      <c r="BY145" s="3"/>
+      <c r="BZ145" s="3"/>
+    </row>
+    <row r="146" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -12656,8 +13388,12 @@
       <c r="BT146" s="3"/>
       <c r="BU146" s="3"/>
       <c r="BV146" s="3"/>
-    </row>
-    <row r="147" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW146" s="3"/>
+      <c r="BX146" s="3"/>
+      <c r="BY146" s="3"/>
+      <c r="BZ146" s="3"/>
+    </row>
+    <row r="147" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -12730,8 +13466,12 @@
       <c r="BT147" s="3"/>
       <c r="BU147" s="3"/>
       <c r="BV147" s="3"/>
-    </row>
-    <row r="148" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW147" s="3"/>
+      <c r="BX147" s="3"/>
+      <c r="BY147" s="3"/>
+      <c r="BZ147" s="3"/>
+    </row>
+    <row r="148" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -12804,8 +13544,12 @@
       <c r="BT148" s="3"/>
       <c r="BU148" s="3"/>
       <c r="BV148" s="3"/>
-    </row>
-    <row r="149" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW148" s="3"/>
+      <c r="BX148" s="3"/>
+      <c r="BY148" s="3"/>
+      <c r="BZ148" s="3"/>
+    </row>
+    <row r="149" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -12878,8 +13622,12 @@
       <c r="BT149" s="3"/>
       <c r="BU149" s="3"/>
       <c r="BV149" s="3"/>
-    </row>
-    <row r="150" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW149" s="3"/>
+      <c r="BX149" s="3"/>
+      <c r="BY149" s="3"/>
+      <c r="BZ149" s="3"/>
+    </row>
+    <row r="150" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -12952,8 +13700,12 @@
       <c r="BT150" s="3"/>
       <c r="BU150" s="3"/>
       <c r="BV150" s="3"/>
-    </row>
-    <row r="151" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW150" s="3"/>
+      <c r="BX150" s="3"/>
+      <c r="BY150" s="3"/>
+      <c r="BZ150" s="3"/>
+    </row>
+    <row r="151" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -13026,8 +13778,12 @@
       <c r="BT151" s="3"/>
       <c r="BU151" s="3"/>
       <c r="BV151" s="3"/>
-    </row>
-    <row r="152" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW151" s="3"/>
+      <c r="BX151" s="3"/>
+      <c r="BY151" s="3"/>
+      <c r="BZ151" s="3"/>
+    </row>
+    <row r="152" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -13100,8 +13856,12 @@
       <c r="BT152" s="3"/>
       <c r="BU152" s="3"/>
       <c r="BV152" s="3"/>
-    </row>
-    <row r="153" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW152" s="3"/>
+      <c r="BX152" s="3"/>
+      <c r="BY152" s="3"/>
+      <c r="BZ152" s="3"/>
+    </row>
+    <row r="153" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -13174,8 +13934,12 @@
       <c r="BT153" s="3"/>
       <c r="BU153" s="3"/>
       <c r="BV153" s="3"/>
-    </row>
-    <row r="154" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW153" s="3"/>
+      <c r="BX153" s="3"/>
+      <c r="BY153" s="3"/>
+      <c r="BZ153" s="3"/>
+    </row>
+    <row r="154" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -13248,8 +14012,12 @@
       <c r="BT154" s="3"/>
       <c r="BU154" s="3"/>
       <c r="BV154" s="3"/>
-    </row>
-    <row r="155" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW154" s="3"/>
+      <c r="BX154" s="3"/>
+      <c r="BY154" s="3"/>
+      <c r="BZ154" s="3"/>
+    </row>
+    <row r="155" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -13322,8 +14090,12 @@
       <c r="BT155" s="3"/>
       <c r="BU155" s="3"/>
       <c r="BV155" s="3"/>
-    </row>
-    <row r="156" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW155" s="3"/>
+      <c r="BX155" s="3"/>
+      <c r="BY155" s="3"/>
+      <c r="BZ155" s="3"/>
+    </row>
+    <row r="156" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -13396,8 +14168,12 @@
       <c r="BT156" s="3"/>
       <c r="BU156" s="3"/>
       <c r="BV156" s="3"/>
-    </row>
-    <row r="157" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW156" s="3"/>
+      <c r="BX156" s="3"/>
+      <c r="BY156" s="3"/>
+      <c r="BZ156" s="3"/>
+    </row>
+    <row r="157" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -13470,8 +14246,12 @@
       <c r="BT157" s="3"/>
       <c r="BU157" s="3"/>
       <c r="BV157" s="3"/>
-    </row>
-    <row r="158" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW157" s="3"/>
+      <c r="BX157" s="3"/>
+      <c r="BY157" s="3"/>
+      <c r="BZ157" s="3"/>
+    </row>
+    <row r="158" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -13544,8 +14324,12 @@
       <c r="BT158" s="3"/>
       <c r="BU158" s="3"/>
       <c r="BV158" s="3"/>
-    </row>
-    <row r="159" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW158" s="3"/>
+      <c r="BX158" s="3"/>
+      <c r="BY158" s="3"/>
+      <c r="BZ158" s="3"/>
+    </row>
+    <row r="159" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -13618,8 +14402,12 @@
       <c r="BT159" s="3"/>
       <c r="BU159" s="3"/>
       <c r="BV159" s="3"/>
-    </row>
-    <row r="160" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW159" s="3"/>
+      <c r="BX159" s="3"/>
+      <c r="BY159" s="3"/>
+      <c r="BZ159" s="3"/>
+    </row>
+    <row r="160" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -13692,8 +14480,12 @@
       <c r="BT160" s="3"/>
       <c r="BU160" s="3"/>
       <c r="BV160" s="3"/>
-    </row>
-    <row r="161" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW160" s="3"/>
+      <c r="BX160" s="3"/>
+      <c r="BY160" s="3"/>
+      <c r="BZ160" s="3"/>
+    </row>
+    <row r="161" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -13766,8 +14558,12 @@
       <c r="BT161" s="3"/>
       <c r="BU161" s="3"/>
       <c r="BV161" s="3"/>
-    </row>
-    <row r="162" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW161" s="3"/>
+      <c r="BX161" s="3"/>
+      <c r="BY161" s="3"/>
+      <c r="BZ161" s="3"/>
+    </row>
+    <row r="162" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -13840,8 +14636,12 @@
       <c r="BT162" s="3"/>
       <c r="BU162" s="3"/>
       <c r="BV162" s="3"/>
-    </row>
-    <row r="163" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW162" s="3"/>
+      <c r="BX162" s="3"/>
+      <c r="BY162" s="3"/>
+      <c r="BZ162" s="3"/>
+    </row>
+    <row r="163" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -13914,8 +14714,12 @@
       <c r="BT163" s="3"/>
       <c r="BU163" s="3"/>
       <c r="BV163" s="3"/>
-    </row>
-    <row r="164" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW163" s="3"/>
+      <c r="BX163" s="3"/>
+      <c r="BY163" s="3"/>
+      <c r="BZ163" s="3"/>
+    </row>
+    <row r="164" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -13988,8 +14792,12 @@
       <c r="BT164" s="3"/>
       <c r="BU164" s="3"/>
       <c r="BV164" s="3"/>
-    </row>
-    <row r="165" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW164" s="3"/>
+      <c r="BX164" s="3"/>
+      <c r="BY164" s="3"/>
+      <c r="BZ164" s="3"/>
+    </row>
+    <row r="165" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -14062,8 +14870,12 @@
       <c r="BT165" s="3"/>
       <c r="BU165" s="3"/>
       <c r="BV165" s="3"/>
-    </row>
-    <row r="166" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW165" s="3"/>
+      <c r="BX165" s="3"/>
+      <c r="BY165" s="3"/>
+      <c r="BZ165" s="3"/>
+    </row>
+    <row r="166" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -14136,8 +14948,12 @@
       <c r="BT166" s="3"/>
       <c r="BU166" s="3"/>
       <c r="BV166" s="3"/>
-    </row>
-    <row r="167" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW166" s="3"/>
+      <c r="BX166" s="3"/>
+      <c r="BY166" s="3"/>
+      <c r="BZ166" s="3"/>
+    </row>
+    <row r="167" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -14210,8 +15026,12 @@
       <c r="BT167" s="3"/>
       <c r="BU167" s="3"/>
       <c r="BV167" s="3"/>
-    </row>
-    <row r="168" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW167" s="3"/>
+      <c r="BX167" s="3"/>
+      <c r="BY167" s="3"/>
+      <c r="BZ167" s="3"/>
+    </row>
+    <row r="168" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -14284,8 +15104,12 @@
       <c r="BT168" s="3"/>
       <c r="BU168" s="3"/>
       <c r="BV168" s="3"/>
-    </row>
-    <row r="169" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW168" s="3"/>
+      <c r="BX168" s="3"/>
+      <c r="BY168" s="3"/>
+      <c r="BZ168" s="3"/>
+    </row>
+    <row r="169" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -14358,8 +15182,12 @@
       <c r="BT169" s="3"/>
       <c r="BU169" s="3"/>
       <c r="BV169" s="3"/>
-    </row>
-    <row r="170" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW169" s="3"/>
+      <c r="BX169" s="3"/>
+      <c r="BY169" s="3"/>
+      <c r="BZ169" s="3"/>
+    </row>
+    <row r="170" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -14432,8 +15260,12 @@
       <c r="BT170" s="3"/>
       <c r="BU170" s="3"/>
       <c r="BV170" s="3"/>
-    </row>
-    <row r="171" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW170" s="3"/>
+      <c r="BX170" s="3"/>
+      <c r="BY170" s="3"/>
+      <c r="BZ170" s="3"/>
+    </row>
+    <row r="171" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -14506,8 +15338,12 @@
       <c r="BT171" s="3"/>
       <c r="BU171" s="3"/>
       <c r="BV171" s="3"/>
-    </row>
-    <row r="172" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW171" s="3"/>
+      <c r="BX171" s="3"/>
+      <c r="BY171" s="3"/>
+      <c r="BZ171" s="3"/>
+    </row>
+    <row r="172" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -14580,8 +15416,12 @@
       <c r="BT172" s="3"/>
       <c r="BU172" s="3"/>
       <c r="BV172" s="3"/>
-    </row>
-    <row r="173" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW172" s="3"/>
+      <c r="BX172" s="3"/>
+      <c r="BY172" s="3"/>
+      <c r="BZ172" s="3"/>
+    </row>
+    <row r="173" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -14654,8 +15494,12 @@
       <c r="BT173" s="3"/>
       <c r="BU173" s="3"/>
       <c r="BV173" s="3"/>
-    </row>
-    <row r="174" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW173" s="3"/>
+      <c r="BX173" s="3"/>
+      <c r="BY173" s="3"/>
+      <c r="BZ173" s="3"/>
+    </row>
+    <row r="174" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -14728,8 +15572,12 @@
       <c r="BT174" s="3"/>
       <c r="BU174" s="3"/>
       <c r="BV174" s="3"/>
-    </row>
-    <row r="175" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW174" s="3"/>
+      <c r="BX174" s="3"/>
+      <c r="BY174" s="3"/>
+      <c r="BZ174" s="3"/>
+    </row>
+    <row r="175" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -14802,8 +15650,12 @@
       <c r="BT175" s="3"/>
       <c r="BU175" s="3"/>
       <c r="BV175" s="3"/>
-    </row>
-    <row r="176" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW175" s="3"/>
+      <c r="BX175" s="3"/>
+      <c r="BY175" s="3"/>
+      <c r="BZ175" s="3"/>
+    </row>
+    <row r="176" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -14876,8 +15728,12 @@
       <c r="BT176" s="3"/>
       <c r="BU176" s="3"/>
       <c r="BV176" s="3"/>
-    </row>
-    <row r="177" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW176" s="3"/>
+      <c r="BX176" s="3"/>
+      <c r="BY176" s="3"/>
+      <c r="BZ176" s="3"/>
+    </row>
+    <row r="177" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -14950,8 +15806,12 @@
       <c r="BT177" s="3"/>
       <c r="BU177" s="3"/>
       <c r="BV177" s="3"/>
-    </row>
-    <row r="178" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW177" s="3"/>
+      <c r="BX177" s="3"/>
+      <c r="BY177" s="3"/>
+      <c r="BZ177" s="3"/>
+    </row>
+    <row r="178" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -15024,8 +15884,12 @@
       <c r="BT178" s="3"/>
       <c r="BU178" s="3"/>
       <c r="BV178" s="3"/>
-    </row>
-    <row r="179" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW178" s="3"/>
+      <c r="BX178" s="3"/>
+      <c r="BY178" s="3"/>
+      <c r="BZ178" s="3"/>
+    </row>
+    <row r="179" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -15098,8 +15962,12 @@
       <c r="BT179" s="3"/>
       <c r="BU179" s="3"/>
       <c r="BV179" s="3"/>
-    </row>
-    <row r="180" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW179" s="3"/>
+      <c r="BX179" s="3"/>
+      <c r="BY179" s="3"/>
+      <c r="BZ179" s="3"/>
+    </row>
+    <row r="180" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -15172,8 +16040,12 @@
       <c r="BT180" s="3"/>
       <c r="BU180" s="3"/>
       <c r="BV180" s="3"/>
-    </row>
-    <row r="181" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW180" s="3"/>
+      <c r="BX180" s="3"/>
+      <c r="BY180" s="3"/>
+      <c r="BZ180" s="3"/>
+    </row>
+    <row r="181" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -15246,8 +16118,12 @@
       <c r="BT181" s="3"/>
       <c r="BU181" s="3"/>
       <c r="BV181" s="3"/>
-    </row>
-    <row r="182" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW181" s="3"/>
+      <c r="BX181" s="3"/>
+      <c r="BY181" s="3"/>
+      <c r="BZ181" s="3"/>
+    </row>
+    <row r="182" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -15320,8 +16196,12 @@
       <c r="BT182" s="3"/>
       <c r="BU182" s="3"/>
       <c r="BV182" s="3"/>
-    </row>
-    <row r="183" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW182" s="3"/>
+      <c r="BX182" s="3"/>
+      <c r="BY182" s="3"/>
+      <c r="BZ182" s="3"/>
+    </row>
+    <row r="183" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -15394,8 +16274,12 @@
       <c r="BT183" s="3"/>
       <c r="BU183" s="3"/>
       <c r="BV183" s="3"/>
-    </row>
-    <row r="184" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW183" s="3"/>
+      <c r="BX183" s="3"/>
+      <c r="BY183" s="3"/>
+      <c r="BZ183" s="3"/>
+    </row>
+    <row r="184" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -15468,8 +16352,12 @@
       <c r="BT184" s="3"/>
       <c r="BU184" s="3"/>
       <c r="BV184" s="3"/>
-    </row>
-    <row r="185" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW184" s="3"/>
+      <c r="BX184" s="3"/>
+      <c r="BY184" s="3"/>
+      <c r="BZ184" s="3"/>
+    </row>
+    <row r="185" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -15542,8 +16430,12 @@
       <c r="BT185" s="3"/>
       <c r="BU185" s="3"/>
       <c r="BV185" s="3"/>
-    </row>
-    <row r="186" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW185" s="3"/>
+      <c r="BX185" s="3"/>
+      <c r="BY185" s="3"/>
+      <c r="BZ185" s="3"/>
+    </row>
+    <row r="186" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -15616,8 +16508,12 @@
       <c r="BT186" s="3"/>
       <c r="BU186" s="3"/>
       <c r="BV186" s="3"/>
-    </row>
-    <row r="187" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW186" s="3"/>
+      <c r="BX186" s="3"/>
+      <c r="BY186" s="3"/>
+      <c r="BZ186" s="3"/>
+    </row>
+    <row r="187" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -15690,8 +16586,12 @@
       <c r="BT187" s="3"/>
       <c r="BU187" s="3"/>
       <c r="BV187" s="3"/>
-    </row>
-    <row r="188" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW187" s="3"/>
+      <c r="BX187" s="3"/>
+      <c r="BY187" s="3"/>
+      <c r="BZ187" s="3"/>
+    </row>
+    <row r="188" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -15764,8 +16664,12 @@
       <c r="BT188" s="3"/>
       <c r="BU188" s="3"/>
       <c r="BV188" s="3"/>
-    </row>
-    <row r="189" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW188" s="3"/>
+      <c r="BX188" s="3"/>
+      <c r="BY188" s="3"/>
+      <c r="BZ188" s="3"/>
+    </row>
+    <row r="189" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -15838,8 +16742,12 @@
       <c r="BT189" s="3"/>
       <c r="BU189" s="3"/>
       <c r="BV189" s="3"/>
-    </row>
-    <row r="190" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW189" s="3"/>
+      <c r="BX189" s="3"/>
+      <c r="BY189" s="3"/>
+      <c r="BZ189" s="3"/>
+    </row>
+    <row r="190" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -15912,8 +16820,12 @@
       <c r="BT190" s="3"/>
       <c r="BU190" s="3"/>
       <c r="BV190" s="3"/>
-    </row>
-    <row r="191" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW190" s="3"/>
+      <c r="BX190" s="3"/>
+      <c r="BY190" s="3"/>
+      <c r="BZ190" s="3"/>
+    </row>
+    <row r="191" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -15986,8 +16898,12 @@
       <c r="BT191" s="3"/>
       <c r="BU191" s="3"/>
       <c r="BV191" s="3"/>
-    </row>
-    <row r="192" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW191" s="3"/>
+      <c r="BX191" s="3"/>
+      <c r="BY191" s="3"/>
+      <c r="BZ191" s="3"/>
+    </row>
+    <row r="192" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -16060,8 +16976,12 @@
       <c r="BT192" s="3"/>
       <c r="BU192" s="3"/>
       <c r="BV192" s="3"/>
-    </row>
-    <row r="193" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW192" s="3"/>
+      <c r="BX192" s="3"/>
+      <c r="BY192" s="3"/>
+      <c r="BZ192" s="3"/>
+    </row>
+    <row r="193" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -16134,8 +17054,12 @@
       <c r="BT193" s="3"/>
       <c r="BU193" s="3"/>
       <c r="BV193" s="3"/>
-    </row>
-    <row r="194" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW193" s="3"/>
+      <c r="BX193" s="3"/>
+      <c r="BY193" s="3"/>
+      <c r="BZ193" s="3"/>
+    </row>
+    <row r="194" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -16208,8 +17132,12 @@
       <c r="BT194" s="3"/>
       <c r="BU194" s="3"/>
       <c r="BV194" s="3"/>
-    </row>
-    <row r="195" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW194" s="3"/>
+      <c r="BX194" s="3"/>
+      <c r="BY194" s="3"/>
+      <c r="BZ194" s="3"/>
+    </row>
+    <row r="195" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -16282,8 +17210,12 @@
       <c r="BT195" s="3"/>
       <c r="BU195" s="3"/>
       <c r="BV195" s="3"/>
-    </row>
-    <row r="196" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW195" s="3"/>
+      <c r="BX195" s="3"/>
+      <c r="BY195" s="3"/>
+      <c r="BZ195" s="3"/>
+    </row>
+    <row r="196" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -16356,8 +17288,12 @@
       <c r="BT196" s="3"/>
       <c r="BU196" s="3"/>
       <c r="BV196" s="3"/>
-    </row>
-    <row r="197" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW196" s="3"/>
+      <c r="BX196" s="3"/>
+      <c r="BY196" s="3"/>
+      <c r="BZ196" s="3"/>
+    </row>
+    <row r="197" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -16430,8 +17366,12 @@
       <c r="BT197" s="3"/>
       <c r="BU197" s="3"/>
       <c r="BV197" s="3"/>
-    </row>
-    <row r="198" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW197" s="3"/>
+      <c r="BX197" s="3"/>
+      <c r="BY197" s="3"/>
+      <c r="BZ197" s="3"/>
+    </row>
+    <row r="198" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -16504,8 +17444,12 @@
       <c r="BT198" s="3"/>
       <c r="BU198" s="3"/>
       <c r="BV198" s="3"/>
-    </row>
-    <row r="199" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW198" s="3"/>
+      <c r="BX198" s="3"/>
+      <c r="BY198" s="3"/>
+      <c r="BZ198" s="3"/>
+    </row>
+    <row r="199" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -16578,8 +17522,12 @@
       <c r="BT199" s="3"/>
       <c r="BU199" s="3"/>
       <c r="BV199" s="3"/>
-    </row>
-    <row r="200" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW199" s="3"/>
+      <c r="BX199" s="3"/>
+      <c r="BY199" s="3"/>
+      <c r="BZ199" s="3"/>
+    </row>
+    <row r="200" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -16652,8 +17600,12 @@
       <c r="BT200" s="3"/>
       <c r="BU200" s="3"/>
       <c r="BV200" s="3"/>
-    </row>
-    <row r="201" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW200" s="3"/>
+      <c r="BX200" s="3"/>
+      <c r="BY200" s="3"/>
+      <c r="BZ200" s="3"/>
+    </row>
+    <row r="201" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -16726,8 +17678,12 @@
       <c r="BT201" s="3"/>
       <c r="BU201" s="3"/>
       <c r="BV201" s="3"/>
-    </row>
-    <row r="202" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW201" s="3"/>
+      <c r="BX201" s="3"/>
+      <c r="BY201" s="3"/>
+      <c r="BZ201" s="3"/>
+    </row>
+    <row r="202" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -16800,8 +17756,12 @@
       <c r="BT202" s="3"/>
       <c r="BU202" s="3"/>
       <c r="BV202" s="3"/>
-    </row>
-    <row r="203" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW202" s="3"/>
+      <c r="BX202" s="3"/>
+      <c r="BY202" s="3"/>
+      <c r="BZ202" s="3"/>
+    </row>
+    <row r="203" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -16874,8 +17834,12 @@
       <c r="BT203" s="3"/>
       <c r="BU203" s="3"/>
       <c r="BV203" s="3"/>
-    </row>
-    <row r="204" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW203" s="3"/>
+      <c r="BX203" s="3"/>
+      <c r="BY203" s="3"/>
+      <c r="BZ203" s="3"/>
+    </row>
+    <row r="204" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -16948,8 +17912,12 @@
       <c r="BT204" s="3"/>
       <c r="BU204" s="3"/>
       <c r="BV204" s="3"/>
-    </row>
-    <row r="205" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW204" s="3"/>
+      <c r="BX204" s="3"/>
+      <c r="BY204" s="3"/>
+      <c r="BZ204" s="3"/>
+    </row>
+    <row r="205" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -17022,8 +17990,12 @@
       <c r="BT205" s="3"/>
       <c r="BU205" s="3"/>
       <c r="BV205" s="3"/>
-    </row>
-    <row r="206" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW205" s="3"/>
+      <c r="BX205" s="3"/>
+      <c r="BY205" s="3"/>
+      <c r="BZ205" s="3"/>
+    </row>
+    <row r="206" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -17096,8 +18068,12 @@
       <c r="BT206" s="3"/>
       <c r="BU206" s="3"/>
       <c r="BV206" s="3"/>
-    </row>
-    <row r="207" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW206" s="3"/>
+      <c r="BX206" s="3"/>
+      <c r="BY206" s="3"/>
+      <c r="BZ206" s="3"/>
+    </row>
+    <row r="207" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -17170,8 +18146,12 @@
       <c r="BT207" s="3"/>
       <c r="BU207" s="3"/>
       <c r="BV207" s="3"/>
-    </row>
-    <row r="208" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW207" s="3"/>
+      <c r="BX207" s="3"/>
+      <c r="BY207" s="3"/>
+      <c r="BZ207" s="3"/>
+    </row>
+    <row r="208" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -17244,8 +18224,12 @@
       <c r="BT208" s="3"/>
       <c r="BU208" s="3"/>
       <c r="BV208" s="3"/>
-    </row>
-    <row r="209" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW208" s="3"/>
+      <c r="BX208" s="3"/>
+      <c r="BY208" s="3"/>
+      <c r="BZ208" s="3"/>
+    </row>
+    <row r="209" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -17318,8 +18302,12 @@
       <c r="BT209" s="3"/>
       <c r="BU209" s="3"/>
       <c r="BV209" s="3"/>
-    </row>
-    <row r="210" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW209" s="3"/>
+      <c r="BX209" s="3"/>
+      <c r="BY209" s="3"/>
+      <c r="BZ209" s="3"/>
+    </row>
+    <row r="210" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -17392,8 +18380,12 @@
       <c r="BT210" s="3"/>
       <c r="BU210" s="3"/>
       <c r="BV210" s="3"/>
-    </row>
-    <row r="211" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW210" s="3"/>
+      <c r="BX210" s="3"/>
+      <c r="BY210" s="3"/>
+      <c r="BZ210" s="3"/>
+    </row>
+    <row r="211" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -17466,8 +18458,12 @@
       <c r="BT211" s="3"/>
       <c r="BU211" s="3"/>
       <c r="BV211" s="3"/>
-    </row>
-    <row r="212" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW211" s="3"/>
+      <c r="BX211" s="3"/>
+      <c r="BY211" s="3"/>
+      <c r="BZ211" s="3"/>
+    </row>
+    <row r="212" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -17540,8 +18536,12 @@
       <c r="BT212" s="3"/>
       <c r="BU212" s="3"/>
       <c r="BV212" s="3"/>
-    </row>
-    <row r="213" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW212" s="3"/>
+      <c r="BX212" s="3"/>
+      <c r="BY212" s="3"/>
+      <c r="BZ212" s="3"/>
+    </row>
+    <row r="213" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -17614,8 +18614,12 @@
       <c r="BT213" s="3"/>
       <c r="BU213" s="3"/>
       <c r="BV213" s="3"/>
-    </row>
-    <row r="214" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW213" s="3"/>
+      <c r="BX213" s="3"/>
+      <c r="BY213" s="3"/>
+      <c r="BZ213" s="3"/>
+    </row>
+    <row r="214" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -17688,8 +18692,12 @@
       <c r="BT214" s="3"/>
       <c r="BU214" s="3"/>
       <c r="BV214" s="3"/>
-    </row>
-    <row r="215" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW214" s="3"/>
+      <c r="BX214" s="3"/>
+      <c r="BY214" s="3"/>
+      <c r="BZ214" s="3"/>
+    </row>
+    <row r="215" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -17762,8 +18770,12 @@
       <c r="BT215" s="3"/>
       <c r="BU215" s="3"/>
       <c r="BV215" s="3"/>
-    </row>
-    <row r="216" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW215" s="3"/>
+      <c r="BX215" s="3"/>
+      <c r="BY215" s="3"/>
+      <c r="BZ215" s="3"/>
+    </row>
+    <row r="216" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -17836,8 +18848,12 @@
       <c r="BT216" s="3"/>
       <c r="BU216" s="3"/>
       <c r="BV216" s="3"/>
-    </row>
-    <row r="217" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW216" s="3"/>
+      <c r="BX216" s="3"/>
+      <c r="BY216" s="3"/>
+      <c r="BZ216" s="3"/>
+    </row>
+    <row r="217" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -17910,8 +18926,12 @@
       <c r="BT217" s="3"/>
       <c r="BU217" s="3"/>
       <c r="BV217" s="3"/>
-    </row>
-    <row r="218" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW217" s="3"/>
+      <c r="BX217" s="3"/>
+      <c r="BY217" s="3"/>
+      <c r="BZ217" s="3"/>
+    </row>
+    <row r="218" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -17984,8 +19004,12 @@
       <c r="BT218" s="3"/>
       <c r="BU218" s="3"/>
       <c r="BV218" s="3"/>
-    </row>
-    <row r="219" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW218" s="3"/>
+      <c r="BX218" s="3"/>
+      <c r="BY218" s="3"/>
+      <c r="BZ218" s="3"/>
+    </row>
+    <row r="219" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -18058,8 +19082,12 @@
       <c r="BT219" s="3"/>
       <c r="BU219" s="3"/>
       <c r="BV219" s="3"/>
-    </row>
-    <row r="220" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW219" s="3"/>
+      <c r="BX219" s="3"/>
+      <c r="BY219" s="3"/>
+      <c r="BZ219" s="3"/>
+    </row>
+    <row r="220" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -18132,8 +19160,12 @@
       <c r="BT220" s="3"/>
       <c r="BU220" s="3"/>
       <c r="BV220" s="3"/>
-    </row>
-    <row r="221" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW220" s="3"/>
+      <c r="BX220" s="3"/>
+      <c r="BY220" s="3"/>
+      <c r="BZ220" s="3"/>
+    </row>
+    <row r="221" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -18206,8 +19238,12 @@
       <c r="BT221" s="3"/>
       <c r="BU221" s="3"/>
       <c r="BV221" s="3"/>
-    </row>
-    <row r="222" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW221" s="3"/>
+      <c r="BX221" s="3"/>
+      <c r="BY221" s="3"/>
+      <c r="BZ221" s="3"/>
+    </row>
+    <row r="222" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -18280,8 +19316,12 @@
       <c r="BT222" s="3"/>
       <c r="BU222" s="3"/>
       <c r="BV222" s="3"/>
-    </row>
-    <row r="223" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW222" s="3"/>
+      <c r="BX222" s="3"/>
+      <c r="BY222" s="3"/>
+      <c r="BZ222" s="3"/>
+    </row>
+    <row r="223" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -18354,8 +19394,12 @@
       <c r="BT223" s="3"/>
       <c r="BU223" s="3"/>
       <c r="BV223" s="3"/>
-    </row>
-    <row r="224" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW223" s="3"/>
+      <c r="BX223" s="3"/>
+      <c r="BY223" s="3"/>
+      <c r="BZ223" s="3"/>
+    </row>
+    <row r="224" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -18428,8 +19472,12 @@
       <c r="BT224" s="3"/>
       <c r="BU224" s="3"/>
       <c r="BV224" s="3"/>
-    </row>
-    <row r="225" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW224" s="3"/>
+      <c r="BX224" s="3"/>
+      <c r="BY224" s="3"/>
+      <c r="BZ224" s="3"/>
+    </row>
+    <row r="225" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -18502,8 +19550,12 @@
       <c r="BT225" s="3"/>
       <c r="BU225" s="3"/>
       <c r="BV225" s="3"/>
-    </row>
-    <row r="226" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW225" s="3"/>
+      <c r="BX225" s="3"/>
+      <c r="BY225" s="3"/>
+      <c r="BZ225" s="3"/>
+    </row>
+    <row r="226" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -18576,8 +19628,12 @@
       <c r="BT226" s="3"/>
       <c r="BU226" s="3"/>
       <c r="BV226" s="3"/>
-    </row>
-    <row r="227" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW226" s="3"/>
+      <c r="BX226" s="3"/>
+      <c r="BY226" s="3"/>
+      <c r="BZ226" s="3"/>
+    </row>
+    <row r="227" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -18650,8 +19706,12 @@
       <c r="BT227" s="3"/>
       <c r="BU227" s="3"/>
       <c r="BV227" s="3"/>
-    </row>
-    <row r="228" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW227" s="3"/>
+      <c r="BX227" s="3"/>
+      <c r="BY227" s="3"/>
+      <c r="BZ227" s="3"/>
+    </row>
+    <row r="228" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -18724,8 +19784,12 @@
       <c r="BT228" s="3"/>
       <c r="BU228" s="3"/>
       <c r="BV228" s="3"/>
-    </row>
-    <row r="229" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW228" s="3"/>
+      <c r="BX228" s="3"/>
+      <c r="BY228" s="3"/>
+      <c r="BZ228" s="3"/>
+    </row>
+    <row r="229" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -18798,8 +19862,12 @@
       <c r="BT229" s="3"/>
       <c r="BU229" s="3"/>
       <c r="BV229" s="3"/>
-    </row>
-    <row r="230" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW229" s="3"/>
+      <c r="BX229" s="3"/>
+      <c r="BY229" s="3"/>
+      <c r="BZ229" s="3"/>
+    </row>
+    <row r="230" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -18872,8 +19940,12 @@
       <c r="BT230" s="3"/>
       <c r="BU230" s="3"/>
       <c r="BV230" s="3"/>
-    </row>
-    <row r="231" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW230" s="3"/>
+      <c r="BX230" s="3"/>
+      <c r="BY230" s="3"/>
+      <c r="BZ230" s="3"/>
+    </row>
+    <row r="231" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -18946,8 +20018,12 @@
       <c r="BT231" s="3"/>
       <c r="BU231" s="3"/>
       <c r="BV231" s="3"/>
-    </row>
-    <row r="232" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW231" s="3"/>
+      <c r="BX231" s="3"/>
+      <c r="BY231" s="3"/>
+      <c r="BZ231" s="3"/>
+    </row>
+    <row r="232" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -19020,8 +20096,12 @@
       <c r="BT232" s="3"/>
       <c r="BU232" s="3"/>
       <c r="BV232" s="3"/>
-    </row>
-    <row r="233" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW232" s="3"/>
+      <c r="BX232" s="3"/>
+      <c r="BY232" s="3"/>
+      <c r="BZ232" s="3"/>
+    </row>
+    <row r="233" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -19094,8 +20174,12 @@
       <c r="BT233" s="3"/>
       <c r="BU233" s="3"/>
       <c r="BV233" s="3"/>
-    </row>
-    <row r="234" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW233" s="3"/>
+      <c r="BX233" s="3"/>
+      <c r="BY233" s="3"/>
+      <c r="BZ233" s="3"/>
+    </row>
+    <row r="234" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -19168,8 +20252,12 @@
       <c r="BT234" s="3"/>
       <c r="BU234" s="3"/>
       <c r="BV234" s="3"/>
-    </row>
-    <row r="235" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW234" s="3"/>
+      <c r="BX234" s="3"/>
+      <c r="BY234" s="3"/>
+      <c r="BZ234" s="3"/>
+    </row>
+    <row r="235" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -19242,8 +20330,12 @@
       <c r="BT235" s="3"/>
       <c r="BU235" s="3"/>
       <c r="BV235" s="3"/>
-    </row>
-    <row r="236" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW235" s="3"/>
+      <c r="BX235" s="3"/>
+      <c r="BY235" s="3"/>
+      <c r="BZ235" s="3"/>
+    </row>
+    <row r="236" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -19316,8 +20408,12 @@
       <c r="BT236" s="3"/>
       <c r="BU236" s="3"/>
       <c r="BV236" s="3"/>
-    </row>
-    <row r="237" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW236" s="3"/>
+      <c r="BX236" s="3"/>
+      <c r="BY236" s="3"/>
+      <c r="BZ236" s="3"/>
+    </row>
+    <row r="237" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -19390,8 +20486,12 @@
       <c r="BT237" s="3"/>
       <c r="BU237" s="3"/>
       <c r="BV237" s="3"/>
-    </row>
-    <row r="238" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW237" s="3"/>
+      <c r="BX237" s="3"/>
+      <c r="BY237" s="3"/>
+      <c r="BZ237" s="3"/>
+    </row>
+    <row r="238" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -19464,8 +20564,12 @@
       <c r="BT238" s="3"/>
       <c r="BU238" s="3"/>
       <c r="BV238" s="3"/>
-    </row>
-    <row r="239" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW238" s="3"/>
+      <c r="BX238" s="3"/>
+      <c r="BY238" s="3"/>
+      <c r="BZ238" s="3"/>
+    </row>
+    <row r="239" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -19538,8 +20642,12 @@
       <c r="BT239" s="3"/>
       <c r="BU239" s="3"/>
       <c r="BV239" s="3"/>
-    </row>
-    <row r="240" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW239" s="3"/>
+      <c r="BX239" s="3"/>
+      <c r="BY239" s="3"/>
+      <c r="BZ239" s="3"/>
+    </row>
+    <row r="240" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -19612,8 +20720,12 @@
       <c r="BT240" s="3"/>
       <c r="BU240" s="3"/>
       <c r="BV240" s="3"/>
-    </row>
-    <row r="241" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW240" s="3"/>
+      <c r="BX240" s="3"/>
+      <c r="BY240" s="3"/>
+      <c r="BZ240" s="3"/>
+    </row>
+    <row r="241" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -19686,8 +20798,12 @@
       <c r="BT241" s="3"/>
       <c r="BU241" s="3"/>
       <c r="BV241" s="3"/>
-    </row>
-    <row r="242" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW241" s="3"/>
+      <c r="BX241" s="3"/>
+      <c r="BY241" s="3"/>
+      <c r="BZ241" s="3"/>
+    </row>
+    <row r="242" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -19760,8 +20876,12 @@
       <c r="BT242" s="3"/>
       <c r="BU242" s="3"/>
       <c r="BV242" s="3"/>
-    </row>
-    <row r="243" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW242" s="3"/>
+      <c r="BX242" s="3"/>
+      <c r="BY242" s="3"/>
+      <c r="BZ242" s="3"/>
+    </row>
+    <row r="243" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -19834,8 +20954,12 @@
       <c r="BT243" s="3"/>
       <c r="BU243" s="3"/>
       <c r="BV243" s="3"/>
-    </row>
-    <row r="244" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW243" s="3"/>
+      <c r="BX243" s="3"/>
+      <c r="BY243" s="3"/>
+      <c r="BZ243" s="3"/>
+    </row>
+    <row r="244" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -19908,8 +21032,12 @@
       <c r="BT244" s="3"/>
       <c r="BU244" s="3"/>
       <c r="BV244" s="3"/>
-    </row>
-    <row r="245" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW244" s="3"/>
+      <c r="BX244" s="3"/>
+      <c r="BY244" s="3"/>
+      <c r="BZ244" s="3"/>
+    </row>
+    <row r="245" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -19982,8 +21110,12 @@
       <c r="BT245" s="3"/>
       <c r="BU245" s="3"/>
       <c r="BV245" s="3"/>
-    </row>
-    <row r="246" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW245" s="3"/>
+      <c r="BX245" s="3"/>
+      <c r="BY245" s="3"/>
+      <c r="BZ245" s="3"/>
+    </row>
+    <row r="246" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -20056,8 +21188,12 @@
       <c r="BT246" s="3"/>
       <c r="BU246" s="3"/>
       <c r="BV246" s="3"/>
-    </row>
-    <row r="247" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW246" s="3"/>
+      <c r="BX246" s="3"/>
+      <c r="BY246" s="3"/>
+      <c r="BZ246" s="3"/>
+    </row>
+    <row r="247" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -20130,8 +21266,12 @@
       <c r="BT247" s="3"/>
       <c r="BU247" s="3"/>
       <c r="BV247" s="3"/>
-    </row>
-    <row r="248" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW247" s="3"/>
+      <c r="BX247" s="3"/>
+      <c r="BY247" s="3"/>
+      <c r="BZ247" s="3"/>
+    </row>
+    <row r="248" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -20204,8 +21344,12 @@
       <c r="BT248" s="3"/>
       <c r="BU248" s="3"/>
       <c r="BV248" s="3"/>
-    </row>
-    <row r="249" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW248" s="3"/>
+      <c r="BX248" s="3"/>
+      <c r="BY248" s="3"/>
+      <c r="BZ248" s="3"/>
+    </row>
+    <row r="249" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -20278,8 +21422,12 @@
       <c r="BT249" s="3"/>
       <c r="BU249" s="3"/>
       <c r="BV249" s="3"/>
-    </row>
-    <row r="250" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW249" s="3"/>
+      <c r="BX249" s="3"/>
+      <c r="BY249" s="3"/>
+      <c r="BZ249" s="3"/>
+    </row>
+    <row r="250" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -20352,8 +21500,12 @@
       <c r="BT250" s="3"/>
       <c r="BU250" s="3"/>
       <c r="BV250" s="3"/>
-    </row>
-    <row r="251" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW250" s="3"/>
+      <c r="BX250" s="3"/>
+      <c r="BY250" s="3"/>
+      <c r="BZ250" s="3"/>
+    </row>
+    <row r="251" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -20426,8 +21578,12 @@
       <c r="BT251" s="3"/>
       <c r="BU251" s="3"/>
       <c r="BV251" s="3"/>
-    </row>
-    <row r="252" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW251" s="3"/>
+      <c r="BX251" s="3"/>
+      <c r="BY251" s="3"/>
+      <c r="BZ251" s="3"/>
+    </row>
+    <row r="252" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -20500,8 +21656,12 @@
       <c r="BT252" s="3"/>
       <c r="BU252" s="3"/>
       <c r="BV252" s="3"/>
-    </row>
-    <row r="253" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW252" s="3"/>
+      <c r="BX252" s="3"/>
+      <c r="BY252" s="3"/>
+      <c r="BZ252" s="3"/>
+    </row>
+    <row r="253" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -20574,8 +21734,12 @@
       <c r="BT253" s="3"/>
       <c r="BU253" s="3"/>
       <c r="BV253" s="3"/>
-    </row>
-    <row r="254" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW253" s="3"/>
+      <c r="BX253" s="3"/>
+      <c r="BY253" s="3"/>
+      <c r="BZ253" s="3"/>
+    </row>
+    <row r="254" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -20648,8 +21812,12 @@
       <c r="BT254" s="3"/>
       <c r="BU254" s="3"/>
       <c r="BV254" s="3"/>
-    </row>
-    <row r="255" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW254" s="3"/>
+      <c r="BX254" s="3"/>
+      <c r="BY254" s="3"/>
+      <c r="BZ254" s="3"/>
+    </row>
+    <row r="255" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -20722,8 +21890,12 @@
       <c r="BT255" s="3"/>
       <c r="BU255" s="3"/>
       <c r="BV255" s="3"/>
-    </row>
-    <row r="256" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW255" s="3"/>
+      <c r="BX255" s="3"/>
+      <c r="BY255" s="3"/>
+      <c r="BZ255" s="3"/>
+    </row>
+    <row r="256" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -20796,8 +21968,12 @@
       <c r="BT256" s="3"/>
       <c r="BU256" s="3"/>
       <c r="BV256" s="3"/>
-    </row>
-    <row r="257" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW256" s="3"/>
+      <c r="BX256" s="3"/>
+      <c r="BY256" s="3"/>
+      <c r="BZ256" s="3"/>
+    </row>
+    <row r="257" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -20870,8 +22046,12 @@
       <c r="BT257" s="3"/>
       <c r="BU257" s="3"/>
       <c r="BV257" s="3"/>
-    </row>
-    <row r="258" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW257" s="3"/>
+      <c r="BX257" s="3"/>
+      <c r="BY257" s="3"/>
+      <c r="BZ257" s="3"/>
+    </row>
+    <row r="258" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -20944,8 +22124,12 @@
       <c r="BT258" s="3"/>
       <c r="BU258" s="3"/>
       <c r="BV258" s="3"/>
-    </row>
-    <row r="259" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW258" s="3"/>
+      <c r="BX258" s="3"/>
+      <c r="BY258" s="3"/>
+      <c r="BZ258" s="3"/>
+    </row>
+    <row r="259" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -21018,8 +22202,12 @@
       <c r="BT259" s="3"/>
       <c r="BU259" s="3"/>
       <c r="BV259" s="3"/>
-    </row>
-    <row r="260" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW259" s="3"/>
+      <c r="BX259" s="3"/>
+      <c r="BY259" s="3"/>
+      <c r="BZ259" s="3"/>
+    </row>
+    <row r="260" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -21092,8 +22280,12 @@
       <c r="BT260" s="3"/>
       <c r="BU260" s="3"/>
       <c r="BV260" s="3"/>
-    </row>
-    <row r="261" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW260" s="3"/>
+      <c r="BX260" s="3"/>
+      <c r="BY260" s="3"/>
+      <c r="BZ260" s="3"/>
+    </row>
+    <row r="261" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -21166,8 +22358,12 @@
       <c r="BT261" s="3"/>
       <c r="BU261" s="3"/>
       <c r="BV261" s="3"/>
-    </row>
-    <row r="262" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW261" s="3"/>
+      <c r="BX261" s="3"/>
+      <c r="BY261" s="3"/>
+      <c r="BZ261" s="3"/>
+    </row>
+    <row r="262" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -21240,8 +22436,12 @@
       <c r="BT262" s="3"/>
       <c r="BU262" s="3"/>
       <c r="BV262" s="3"/>
-    </row>
-    <row r="263" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW262" s="3"/>
+      <c r="BX262" s="3"/>
+      <c r="BY262" s="3"/>
+      <c r="BZ262" s="3"/>
+    </row>
+    <row r="263" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -21314,8 +22514,12 @@
       <c r="BT263" s="3"/>
       <c r="BU263" s="3"/>
       <c r="BV263" s="3"/>
-    </row>
-    <row r="264" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW263" s="3"/>
+      <c r="BX263" s="3"/>
+      <c r="BY263" s="3"/>
+      <c r="BZ263" s="3"/>
+    </row>
+    <row r="264" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -21388,8 +22592,12 @@
       <c r="BT264" s="3"/>
       <c r="BU264" s="3"/>
       <c r="BV264" s="3"/>
-    </row>
-    <row r="265" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW264" s="3"/>
+      <c r="BX264" s="3"/>
+      <c r="BY264" s="3"/>
+      <c r="BZ264" s="3"/>
+    </row>
+    <row r="265" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -21462,8 +22670,12 @@
       <c r="BT265" s="3"/>
       <c r="BU265" s="3"/>
       <c r="BV265" s="3"/>
-    </row>
-    <row r="266" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW265" s="3"/>
+      <c r="BX265" s="3"/>
+      <c r="BY265" s="3"/>
+      <c r="BZ265" s="3"/>
+    </row>
+    <row r="266" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -21536,8 +22748,12 @@
       <c r="BT266" s="3"/>
       <c r="BU266" s="3"/>
       <c r="BV266" s="3"/>
-    </row>
-    <row r="267" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW266" s="3"/>
+      <c r="BX266" s="3"/>
+      <c r="BY266" s="3"/>
+      <c r="BZ266" s="3"/>
+    </row>
+    <row r="267" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -21610,8 +22826,12 @@
       <c r="BT267" s="3"/>
       <c r="BU267" s="3"/>
       <c r="BV267" s="3"/>
-    </row>
-    <row r="268" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW267" s="3"/>
+      <c r="BX267" s="3"/>
+      <c r="BY267" s="3"/>
+      <c r="BZ267" s="3"/>
+    </row>
+    <row r="268" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -21684,8 +22904,12 @@
       <c r="BT268" s="3"/>
       <c r="BU268" s="3"/>
       <c r="BV268" s="3"/>
-    </row>
-    <row r="269" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW268" s="3"/>
+      <c r="BX268" s="3"/>
+      <c r="BY268" s="3"/>
+      <c r="BZ268" s="3"/>
+    </row>
+    <row r="269" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -21758,8 +22982,12 @@
       <c r="BT269" s="3"/>
       <c r="BU269" s="3"/>
       <c r="BV269" s="3"/>
-    </row>
-    <row r="270" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW269" s="3"/>
+      <c r="BX269" s="3"/>
+      <c r="BY269" s="3"/>
+      <c r="BZ269" s="3"/>
+    </row>
+    <row r="270" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -21832,8 +23060,12 @@
       <c r="BT270" s="3"/>
       <c r="BU270" s="3"/>
       <c r="BV270" s="3"/>
-    </row>
-    <row r="271" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW270" s="3"/>
+      <c r="BX270" s="3"/>
+      <c r="BY270" s="3"/>
+      <c r="BZ270" s="3"/>
+    </row>
+    <row r="271" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -21906,8 +23138,12 @@
       <c r="BT271" s="3"/>
       <c r="BU271" s="3"/>
       <c r="BV271" s="3"/>
-    </row>
-    <row r="272" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW271" s="3"/>
+      <c r="BX271" s="3"/>
+      <c r="BY271" s="3"/>
+      <c r="BZ271" s="3"/>
+    </row>
+    <row r="272" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -21980,8 +23216,12 @@
       <c r="BT272" s="3"/>
       <c r="BU272" s="3"/>
       <c r="BV272" s="3"/>
-    </row>
-    <row r="273" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW272" s="3"/>
+      <c r="BX272" s="3"/>
+      <c r="BY272" s="3"/>
+      <c r="BZ272" s="3"/>
+    </row>
+    <row r="273" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -22054,8 +23294,12 @@
       <c r="BT273" s="3"/>
       <c r="BU273" s="3"/>
       <c r="BV273" s="3"/>
-    </row>
-    <row r="274" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW273" s="3"/>
+      <c r="BX273" s="3"/>
+      <c r="BY273" s="3"/>
+      <c r="BZ273" s="3"/>
+    </row>
+    <row r="274" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -22128,8 +23372,12 @@
       <c r="BT274" s="3"/>
       <c r="BU274" s="3"/>
       <c r="BV274" s="3"/>
-    </row>
-    <row r="275" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW274" s="3"/>
+      <c r="BX274" s="3"/>
+      <c r="BY274" s="3"/>
+      <c r="BZ274" s="3"/>
+    </row>
+    <row r="275" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -22202,8 +23450,12 @@
       <c r="BT275" s="3"/>
       <c r="BU275" s="3"/>
       <c r="BV275" s="3"/>
-    </row>
-    <row r="276" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW275" s="3"/>
+      <c r="BX275" s="3"/>
+      <c r="BY275" s="3"/>
+      <c r="BZ275" s="3"/>
+    </row>
+    <row r="276" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -22276,8 +23528,12 @@
       <c r="BT276" s="3"/>
       <c r="BU276" s="3"/>
       <c r="BV276" s="3"/>
-    </row>
-    <row r="277" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW276" s="3"/>
+      <c r="BX276" s="3"/>
+      <c r="BY276" s="3"/>
+      <c r="BZ276" s="3"/>
+    </row>
+    <row r="277" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -22350,8 +23606,12 @@
       <c r="BT277" s="3"/>
       <c r="BU277" s="3"/>
       <c r="BV277" s="3"/>
-    </row>
-    <row r="278" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW277" s="3"/>
+      <c r="BX277" s="3"/>
+      <c r="BY277" s="3"/>
+      <c r="BZ277" s="3"/>
+    </row>
+    <row r="278" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -22424,8 +23684,12 @@
       <c r="BT278" s="3"/>
       <c r="BU278" s="3"/>
       <c r="BV278" s="3"/>
-    </row>
-    <row r="279" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW278" s="3"/>
+      <c r="BX278" s="3"/>
+      <c r="BY278" s="3"/>
+      <c r="BZ278" s="3"/>
+    </row>
+    <row r="279" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -22498,8 +23762,12 @@
       <c r="BT279" s="3"/>
       <c r="BU279" s="3"/>
       <c r="BV279" s="3"/>
-    </row>
-    <row r="280" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW279" s="3"/>
+      <c r="BX279" s="3"/>
+      <c r="BY279" s="3"/>
+      <c r="BZ279" s="3"/>
+    </row>
+    <row r="280" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -22572,8 +23840,12 @@
       <c r="BT280" s="3"/>
       <c r="BU280" s="3"/>
       <c r="BV280" s="3"/>
-    </row>
-    <row r="281" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW280" s="3"/>
+      <c r="BX280" s="3"/>
+      <c r="BY280" s="3"/>
+      <c r="BZ280" s="3"/>
+    </row>
+    <row r="281" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -22646,8 +23918,12 @@
       <c r="BT281" s="3"/>
       <c r="BU281" s="3"/>
       <c r="BV281" s="3"/>
-    </row>
-    <row r="282" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW281" s="3"/>
+      <c r="BX281" s="3"/>
+      <c r="BY281" s="3"/>
+      <c r="BZ281" s="3"/>
+    </row>
+    <row r="282" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -22720,8 +23996,12 @@
       <c r="BT282" s="3"/>
       <c r="BU282" s="3"/>
       <c r="BV282" s="3"/>
-    </row>
-    <row r="283" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW282" s="3"/>
+      <c r="BX282" s="3"/>
+      <c r="BY282" s="3"/>
+      <c r="BZ282" s="3"/>
+    </row>
+    <row r="283" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -22794,8 +24074,12 @@
       <c r="BT283" s="3"/>
       <c r="BU283" s="3"/>
       <c r="BV283" s="3"/>
-    </row>
-    <row r="284" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW283" s="3"/>
+      <c r="BX283" s="3"/>
+      <c r="BY283" s="3"/>
+      <c r="BZ283" s="3"/>
+    </row>
+    <row r="284" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -22868,8 +24152,12 @@
       <c r="BT284" s="3"/>
       <c r="BU284" s="3"/>
       <c r="BV284" s="3"/>
-    </row>
-    <row r="285" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW284" s="3"/>
+      <c r="BX284" s="3"/>
+      <c r="BY284" s="3"/>
+      <c r="BZ284" s="3"/>
+    </row>
+    <row r="285" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -22942,8 +24230,12 @@
       <c r="BT285" s="3"/>
       <c r="BU285" s="3"/>
       <c r="BV285" s="3"/>
-    </row>
-    <row r="286" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW285" s="3"/>
+      <c r="BX285" s="3"/>
+      <c r="BY285" s="3"/>
+      <c r="BZ285" s="3"/>
+    </row>
+    <row r="286" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -23016,8 +24308,12 @@
       <c r="BT286" s="3"/>
       <c r="BU286" s="3"/>
       <c r="BV286" s="3"/>
-    </row>
-    <row r="287" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW286" s="3"/>
+      <c r="BX286" s="3"/>
+      <c r="BY286" s="3"/>
+      <c r="BZ286" s="3"/>
+    </row>
+    <row r="287" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -23090,8 +24386,12 @@
       <c r="BT287" s="3"/>
       <c r="BU287" s="3"/>
       <c r="BV287" s="3"/>
-    </row>
-    <row r="288" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW287" s="3"/>
+      <c r="BX287" s="3"/>
+      <c r="BY287" s="3"/>
+      <c r="BZ287" s="3"/>
+    </row>
+    <row r="288" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -23164,8 +24464,12 @@
       <c r="BT288" s="3"/>
       <c r="BU288" s="3"/>
       <c r="BV288" s="3"/>
-    </row>
-    <row r="289" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW288" s="3"/>
+      <c r="BX288" s="3"/>
+      <c r="BY288" s="3"/>
+      <c r="BZ288" s="3"/>
+    </row>
+    <row r="289" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -23238,8 +24542,12 @@
       <c r="BT289" s="3"/>
       <c r="BU289" s="3"/>
       <c r="BV289" s="3"/>
-    </row>
-    <row r="290" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW289" s="3"/>
+      <c r="BX289" s="3"/>
+      <c r="BY289" s="3"/>
+      <c r="BZ289" s="3"/>
+    </row>
+    <row r="290" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -23312,8 +24620,12 @@
       <c r="BT290" s="3"/>
       <c r="BU290" s="3"/>
       <c r="BV290" s="3"/>
-    </row>
-    <row r="291" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW290" s="3"/>
+      <c r="BX290" s="3"/>
+      <c r="BY290" s="3"/>
+      <c r="BZ290" s="3"/>
+    </row>
+    <row r="291" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -23386,8 +24698,12 @@
       <c r="BT291" s="3"/>
       <c r="BU291" s="3"/>
       <c r="BV291" s="3"/>
-    </row>
-    <row r="292" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW291" s="3"/>
+      <c r="BX291" s="3"/>
+      <c r="BY291" s="3"/>
+      <c r="BZ291" s="3"/>
+    </row>
+    <row r="292" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -23460,8 +24776,12 @@
       <c r="BT292" s="3"/>
       <c r="BU292" s="3"/>
       <c r="BV292" s="3"/>
-    </row>
-    <row r="293" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW292" s="3"/>
+      <c r="BX292" s="3"/>
+      <c r="BY292" s="3"/>
+      <c r="BZ292" s="3"/>
+    </row>
+    <row r="293" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -23534,8 +24854,12 @@
       <c r="BT293" s="3"/>
       <c r="BU293" s="3"/>
       <c r="BV293" s="3"/>
-    </row>
-    <row r="294" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW293" s="3"/>
+      <c r="BX293" s="3"/>
+      <c r="BY293" s="3"/>
+      <c r="BZ293" s="3"/>
+    </row>
+    <row r="294" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -23608,8 +24932,12 @@
       <c r="BT294" s="3"/>
       <c r="BU294" s="3"/>
       <c r="BV294" s="3"/>
-    </row>
-    <row r="295" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW294" s="3"/>
+      <c r="BX294" s="3"/>
+      <c r="BY294" s="3"/>
+      <c r="BZ294" s="3"/>
+    </row>
+    <row r="295" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -23682,8 +25010,12 @@
       <c r="BT295" s="3"/>
       <c r="BU295" s="3"/>
       <c r="BV295" s="3"/>
-    </row>
-    <row r="296" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW295" s="3"/>
+      <c r="BX295" s="3"/>
+      <c r="BY295" s="3"/>
+      <c r="BZ295" s="3"/>
+    </row>
+    <row r="296" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -23756,8 +25088,12 @@
       <c r="BT296" s="3"/>
       <c r="BU296" s="3"/>
       <c r="BV296" s="3"/>
-    </row>
-    <row r="297" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW296" s="3"/>
+      <c r="BX296" s="3"/>
+      <c r="BY296" s="3"/>
+      <c r="BZ296" s="3"/>
+    </row>
+    <row r="297" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -23830,8 +25166,12 @@
       <c r="BT297" s="3"/>
       <c r="BU297" s="3"/>
       <c r="BV297" s="3"/>
-    </row>
-    <row r="298" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW297" s="3"/>
+      <c r="BX297" s="3"/>
+      <c r="BY297" s="3"/>
+      <c r="BZ297" s="3"/>
+    </row>
+    <row r="298" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -23904,8 +25244,12 @@
       <c r="BT298" s="3"/>
       <c r="BU298" s="3"/>
       <c r="BV298" s="3"/>
-    </row>
-    <row r="299" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW298" s="3"/>
+      <c r="BX298" s="3"/>
+      <c r="BY298" s="3"/>
+      <c r="BZ298" s="3"/>
+    </row>
+    <row r="299" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="3"/>
@@ -23978,8 +25322,12 @@
       <c r="BT299" s="3"/>
       <c r="BU299" s="3"/>
       <c r="BV299" s="3"/>
-    </row>
-    <row r="300" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW299" s="3"/>
+      <c r="BX299" s="3"/>
+      <c r="BY299" s="3"/>
+      <c r="BZ299" s="3"/>
+    </row>
+    <row r="300" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -24052,8 +25400,12 @@
       <c r="BT300" s="3"/>
       <c r="BU300" s="3"/>
       <c r="BV300" s="3"/>
-    </row>
-    <row r="301" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW300" s="3"/>
+      <c r="BX300" s="3"/>
+      <c r="BY300" s="3"/>
+      <c r="BZ300" s="3"/>
+    </row>
+    <row r="301" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="3"/>
@@ -24126,8 +25478,12 @@
       <c r="BT301" s="3"/>
       <c r="BU301" s="3"/>
       <c r="BV301" s="3"/>
-    </row>
-    <row r="302" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW301" s="3"/>
+      <c r="BX301" s="3"/>
+      <c r="BY301" s="3"/>
+      <c r="BZ301" s="3"/>
+    </row>
+    <row r="302" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
       <c r="E302" s="3"/>
@@ -24200,8 +25556,12 @@
       <c r="BT302" s="3"/>
       <c r="BU302" s="3"/>
       <c r="BV302" s="3"/>
-    </row>
-    <row r="303" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW302" s="3"/>
+      <c r="BX302" s="3"/>
+      <c r="BY302" s="3"/>
+      <c r="BZ302" s="3"/>
+    </row>
+    <row r="303" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
       <c r="E303" s="3"/>
@@ -24274,8 +25634,12 @@
       <c r="BT303" s="3"/>
       <c r="BU303" s="3"/>
       <c r="BV303" s="3"/>
-    </row>
-    <row r="304" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW303" s="3"/>
+      <c r="BX303" s="3"/>
+      <c r="BY303" s="3"/>
+      <c r="BZ303" s="3"/>
+    </row>
+    <row r="304" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="3"/>
@@ -24348,8 +25712,12 @@
       <c r="BT304" s="3"/>
       <c r="BU304" s="3"/>
       <c r="BV304" s="3"/>
-    </row>
-    <row r="305" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW304" s="3"/>
+      <c r="BX304" s="3"/>
+      <c r="BY304" s="3"/>
+      <c r="BZ304" s="3"/>
+    </row>
+    <row r="305" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="3"/>
@@ -24422,8 +25790,12 @@
       <c r="BT305" s="3"/>
       <c r="BU305" s="3"/>
       <c r="BV305" s="3"/>
-    </row>
-    <row r="306" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW305" s="3"/>
+      <c r="BX305" s="3"/>
+      <c r="BY305" s="3"/>
+      <c r="BZ305" s="3"/>
+    </row>
+    <row r="306" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
       <c r="E306" s="3"/>
@@ -24496,8 +25868,12 @@
       <c r="BT306" s="3"/>
       <c r="BU306" s="3"/>
       <c r="BV306" s="3"/>
-    </row>
-    <row r="307" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW306" s="3"/>
+      <c r="BX306" s="3"/>
+      <c r="BY306" s="3"/>
+      <c r="BZ306" s="3"/>
+    </row>
+    <row r="307" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
       <c r="E307" s="3"/>
@@ -24570,8 +25946,12 @@
       <c r="BT307" s="3"/>
       <c r="BU307" s="3"/>
       <c r="BV307" s="3"/>
-    </row>
-    <row r="308" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW307" s="3"/>
+      <c r="BX307" s="3"/>
+      <c r="BY307" s="3"/>
+      <c r="BZ307" s="3"/>
+    </row>
+    <row r="308" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
       <c r="E308" s="3"/>
@@ -24644,8 +26024,12 @@
       <c r="BT308" s="3"/>
       <c r="BU308" s="3"/>
       <c r="BV308" s="3"/>
-    </row>
-    <row r="309" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW308" s="3"/>
+      <c r="BX308" s="3"/>
+      <c r="BY308" s="3"/>
+      <c r="BZ308" s="3"/>
+    </row>
+    <row r="309" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
       <c r="E309" s="3"/>
@@ -24718,8 +26102,12 @@
       <c r="BT309" s="3"/>
       <c r="BU309" s="3"/>
       <c r="BV309" s="3"/>
-    </row>
-    <row r="310" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW309" s="3"/>
+      <c r="BX309" s="3"/>
+      <c r="BY309" s="3"/>
+      <c r="BZ309" s="3"/>
+    </row>
+    <row r="310" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
       <c r="E310" s="3"/>
@@ -24792,8 +26180,12 @@
       <c r="BT310" s="3"/>
       <c r="BU310" s="3"/>
       <c r="BV310" s="3"/>
-    </row>
-    <row r="311" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW310" s="3"/>
+      <c r="BX310" s="3"/>
+      <c r="BY310" s="3"/>
+      <c r="BZ310" s="3"/>
+    </row>
+    <row r="311" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
       <c r="E311" s="3"/>
@@ -24866,8 +26258,12 @@
       <c r="BT311" s="3"/>
       <c r="BU311" s="3"/>
       <c r="BV311" s="3"/>
-    </row>
-    <row r="312" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW311" s="3"/>
+      <c r="BX311" s="3"/>
+      <c r="BY311" s="3"/>
+      <c r="BZ311" s="3"/>
+    </row>
+    <row r="312" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
       <c r="E312" s="3"/>
@@ -24940,8 +26336,12 @@
       <c r="BT312" s="3"/>
       <c r="BU312" s="3"/>
       <c r="BV312" s="3"/>
-    </row>
-    <row r="313" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW312" s="3"/>
+      <c r="BX312" s="3"/>
+      <c r="BY312" s="3"/>
+      <c r="BZ312" s="3"/>
+    </row>
+    <row r="313" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
       <c r="E313" s="3"/>
@@ -25014,8 +26414,12 @@
       <c r="BT313" s="3"/>
       <c r="BU313" s="3"/>
       <c r="BV313" s="3"/>
-    </row>
-    <row r="314" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW313" s="3"/>
+      <c r="BX313" s="3"/>
+      <c r="BY313" s="3"/>
+      <c r="BZ313" s="3"/>
+    </row>
+    <row r="314" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
       <c r="E314" s="3"/>
@@ -25088,8 +26492,12 @@
       <c r="BT314" s="3"/>
       <c r="BU314" s="3"/>
       <c r="BV314" s="3"/>
-    </row>
-    <row r="315" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW314" s="3"/>
+      <c r="BX314" s="3"/>
+      <c r="BY314" s="3"/>
+      <c r="BZ314" s="3"/>
+    </row>
+    <row r="315" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
       <c r="E315" s="3"/>
@@ -25162,8 +26570,12 @@
       <c r="BT315" s="3"/>
       <c r="BU315" s="3"/>
       <c r="BV315" s="3"/>
-    </row>
-    <row r="316" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW315" s="3"/>
+      <c r="BX315" s="3"/>
+      <c r="BY315" s="3"/>
+      <c r="BZ315" s="3"/>
+    </row>
+    <row r="316" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
       <c r="E316" s="3"/>
@@ -25236,8 +26648,12 @@
       <c r="BT316" s="3"/>
       <c r="BU316" s="3"/>
       <c r="BV316" s="3"/>
-    </row>
-    <row r="317" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW316" s="3"/>
+      <c r="BX316" s="3"/>
+      <c r="BY316" s="3"/>
+      <c r="BZ316" s="3"/>
+    </row>
+    <row r="317" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
       <c r="E317" s="3"/>
@@ -25310,8 +26726,12 @@
       <c r="BT317" s="3"/>
       <c r="BU317" s="3"/>
       <c r="BV317" s="3"/>
-    </row>
-    <row r="318" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW317" s="3"/>
+      <c r="BX317" s="3"/>
+      <c r="BY317" s="3"/>
+      <c r="BZ317" s="3"/>
+    </row>
+    <row r="318" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
       <c r="E318" s="3"/>
@@ -25384,8 +26804,12 @@
       <c r="BT318" s="3"/>
       <c r="BU318" s="3"/>
       <c r="BV318" s="3"/>
-    </row>
-    <row r="319" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW318" s="3"/>
+      <c r="BX318" s="3"/>
+      <c r="BY318" s="3"/>
+      <c r="BZ318" s="3"/>
+    </row>
+    <row r="319" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
       <c r="E319" s="3"/>
@@ -25458,8 +26882,12 @@
       <c r="BT319" s="3"/>
       <c r="BU319" s="3"/>
       <c r="BV319" s="3"/>
-    </row>
-    <row r="320" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW319" s="3"/>
+      <c r="BX319" s="3"/>
+      <c r="BY319" s="3"/>
+      <c r="BZ319" s="3"/>
+    </row>
+    <row r="320" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
       <c r="E320" s="3"/>
@@ -25532,8 +26960,12 @@
       <c r="BT320" s="3"/>
       <c r="BU320" s="3"/>
       <c r="BV320" s="3"/>
-    </row>
-    <row r="321" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW320" s="3"/>
+      <c r="BX320" s="3"/>
+      <c r="BY320" s="3"/>
+      <c r="BZ320" s="3"/>
+    </row>
+    <row r="321" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
       <c r="E321" s="3"/>
@@ -25606,8 +27038,12 @@
       <c r="BT321" s="3"/>
       <c r="BU321" s="3"/>
       <c r="BV321" s="3"/>
-    </row>
-    <row r="322" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW321" s="3"/>
+      <c r="BX321" s="3"/>
+      <c r="BY321" s="3"/>
+      <c r="BZ321" s="3"/>
+    </row>
+    <row r="322" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
       <c r="E322" s="3"/>
@@ -25680,8 +27116,12 @@
       <c r="BT322" s="3"/>
       <c r="BU322" s="3"/>
       <c r="BV322" s="3"/>
-    </row>
-    <row r="323" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW322" s="3"/>
+      <c r="BX322" s="3"/>
+      <c r="BY322" s="3"/>
+      <c r="BZ322" s="3"/>
+    </row>
+    <row r="323" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
       <c r="E323" s="3"/>
@@ -25754,8 +27194,12 @@
       <c r="BT323" s="3"/>
       <c r="BU323" s="3"/>
       <c r="BV323" s="3"/>
-    </row>
-    <row r="324" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW323" s="3"/>
+      <c r="BX323" s="3"/>
+      <c r="BY323" s="3"/>
+      <c r="BZ323" s="3"/>
+    </row>
+    <row r="324" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
       <c r="E324" s="3"/>
@@ -25828,8 +27272,12 @@
       <c r="BT324" s="3"/>
       <c r="BU324" s="3"/>
       <c r="BV324" s="3"/>
-    </row>
-    <row r="325" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW324" s="3"/>
+      <c r="BX324" s="3"/>
+      <c r="BY324" s="3"/>
+      <c r="BZ324" s="3"/>
+    </row>
+    <row r="325" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
       <c r="E325" s="3"/>
@@ -25902,8 +27350,12 @@
       <c r="BT325" s="3"/>
       <c r="BU325" s="3"/>
       <c r="BV325" s="3"/>
-    </row>
-    <row r="326" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW325" s="3"/>
+      <c r="BX325" s="3"/>
+      <c r="BY325" s="3"/>
+      <c r="BZ325" s="3"/>
+    </row>
+    <row r="326" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C326" s="3"/>
       <c r="D326" s="3"/>
       <c r="E326" s="3"/>
@@ -25976,8 +27428,12 @@
       <c r="BT326" s="3"/>
       <c r="BU326" s="3"/>
       <c r="BV326" s="3"/>
-    </row>
-    <row r="327" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW326" s="3"/>
+      <c r="BX326" s="3"/>
+      <c r="BY326" s="3"/>
+      <c r="BZ326" s="3"/>
+    </row>
+    <row r="327" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
       <c r="E327" s="3"/>
@@ -26050,8 +27506,12 @@
       <c r="BT327" s="3"/>
       <c r="BU327" s="3"/>
       <c r="BV327" s="3"/>
-    </row>
-    <row r="328" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW327" s="3"/>
+      <c r="BX327" s="3"/>
+      <c r="BY327" s="3"/>
+      <c r="BZ327" s="3"/>
+    </row>
+    <row r="328" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
       <c r="E328" s="3"/>
@@ -26124,8 +27584,12 @@
       <c r="BT328" s="3"/>
       <c r="BU328" s="3"/>
       <c r="BV328" s="3"/>
-    </row>
-    <row r="329" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW328" s="3"/>
+      <c r="BX328" s="3"/>
+      <c r="BY328" s="3"/>
+      <c r="BZ328" s="3"/>
+    </row>
+    <row r="329" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
       <c r="E329" s="3"/>
@@ -26198,8 +27662,12 @@
       <c r="BT329" s="3"/>
       <c r="BU329" s="3"/>
       <c r="BV329" s="3"/>
-    </row>
-    <row r="330" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW329" s="3"/>
+      <c r="BX329" s="3"/>
+      <c r="BY329" s="3"/>
+      <c r="BZ329" s="3"/>
+    </row>
+    <row r="330" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
       <c r="E330" s="3"/>
@@ -26272,8 +27740,12 @@
       <c r="BT330" s="3"/>
       <c r="BU330" s="3"/>
       <c r="BV330" s="3"/>
-    </row>
-    <row r="331" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW330" s="3"/>
+      <c r="BX330" s="3"/>
+      <c r="BY330" s="3"/>
+      <c r="BZ330" s="3"/>
+    </row>
+    <row r="331" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
       <c r="E331" s="3"/>
@@ -26346,8 +27818,12 @@
       <c r="BT331" s="3"/>
       <c r="BU331" s="3"/>
       <c r="BV331" s="3"/>
-    </row>
-    <row r="332" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW331" s="3"/>
+      <c r="BX331" s="3"/>
+      <c r="BY331" s="3"/>
+      <c r="BZ331" s="3"/>
+    </row>
+    <row r="332" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
       <c r="E332" s="3"/>
@@ -26420,8 +27896,12 @@
       <c r="BT332" s="3"/>
       <c r="BU332" s="3"/>
       <c r="BV332" s="3"/>
-    </row>
-    <row r="333" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW332" s="3"/>
+      <c r="BX332" s="3"/>
+      <c r="BY332" s="3"/>
+      <c r="BZ332" s="3"/>
+    </row>
+    <row r="333" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C333" s="3"/>
       <c r="D333" s="3"/>
       <c r="E333" s="3"/>
@@ -26494,8 +27974,12 @@
       <c r="BT333" s="3"/>
       <c r="BU333" s="3"/>
       <c r="BV333" s="3"/>
-    </row>
-    <row r="334" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW333" s="3"/>
+      <c r="BX333" s="3"/>
+      <c r="BY333" s="3"/>
+      <c r="BZ333" s="3"/>
+    </row>
+    <row r="334" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
       <c r="E334" s="3"/>
@@ -26568,8 +28052,12 @@
       <c r="BT334" s="3"/>
       <c r="BU334" s="3"/>
       <c r="BV334" s="3"/>
-    </row>
-    <row r="335" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW334" s="3"/>
+      <c r="BX334" s="3"/>
+      <c r="BY334" s="3"/>
+      <c r="BZ334" s="3"/>
+    </row>
+    <row r="335" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
       <c r="E335" s="3"/>
@@ -26642,8 +28130,12 @@
       <c r="BT335" s="3"/>
       <c r="BU335" s="3"/>
       <c r="BV335" s="3"/>
-    </row>
-    <row r="336" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW335" s="3"/>
+      <c r="BX335" s="3"/>
+      <c r="BY335" s="3"/>
+      <c r="BZ335" s="3"/>
+    </row>
+    <row r="336" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C336" s="3"/>
       <c r="D336" s="3"/>
       <c r="E336" s="3"/>
@@ -26716,8 +28208,12 @@
       <c r="BT336" s="3"/>
       <c r="BU336" s="3"/>
       <c r="BV336" s="3"/>
-    </row>
-    <row r="337" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW336" s="3"/>
+      <c r="BX336" s="3"/>
+      <c r="BY336" s="3"/>
+      <c r="BZ336" s="3"/>
+    </row>
+    <row r="337" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C337" s="3"/>
       <c r="D337" s="3"/>
       <c r="E337" s="3"/>
@@ -26790,8 +28286,12 @@
       <c r="BT337" s="3"/>
       <c r="BU337" s="3"/>
       <c r="BV337" s="3"/>
-    </row>
-    <row r="338" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW337" s="3"/>
+      <c r="BX337" s="3"/>
+      <c r="BY337" s="3"/>
+      <c r="BZ337" s="3"/>
+    </row>
+    <row r="338" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C338" s="3"/>
       <c r="D338" s="3"/>
       <c r="E338" s="3"/>
@@ -26864,8 +28364,12 @@
       <c r="BT338" s="3"/>
       <c r="BU338" s="3"/>
       <c r="BV338" s="3"/>
-    </row>
-    <row r="339" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW338" s="3"/>
+      <c r="BX338" s="3"/>
+      <c r="BY338" s="3"/>
+      <c r="BZ338" s="3"/>
+    </row>
+    <row r="339" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C339" s="3"/>
       <c r="D339" s="3"/>
       <c r="E339" s="3"/>
@@ -26938,8 +28442,12 @@
       <c r="BT339" s="3"/>
       <c r="BU339" s="3"/>
       <c r="BV339" s="3"/>
-    </row>
-    <row r="340" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW339" s="3"/>
+      <c r="BX339" s="3"/>
+      <c r="BY339" s="3"/>
+      <c r="BZ339" s="3"/>
+    </row>
+    <row r="340" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C340" s="3"/>
       <c r="D340" s="3"/>
       <c r="E340" s="3"/>
@@ -27012,8 +28520,12 @@
       <c r="BT340" s="3"/>
       <c r="BU340" s="3"/>
       <c r="BV340" s="3"/>
-    </row>
-    <row r="341" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW340" s="3"/>
+      <c r="BX340" s="3"/>
+      <c r="BY340" s="3"/>
+      <c r="BZ340" s="3"/>
+    </row>
+    <row r="341" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C341" s="3"/>
       <c r="D341" s="3"/>
       <c r="E341" s="3"/>
@@ -27086,8 +28598,12 @@
       <c r="BT341" s="3"/>
       <c r="BU341" s="3"/>
       <c r="BV341" s="3"/>
-    </row>
-    <row r="342" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW341" s="3"/>
+      <c r="BX341" s="3"/>
+      <c r="BY341" s="3"/>
+      <c r="BZ341" s="3"/>
+    </row>
+    <row r="342" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C342" s="3"/>
       <c r="D342" s="3"/>
       <c r="E342" s="3"/>
@@ -27160,8 +28676,12 @@
       <c r="BT342" s="3"/>
       <c r="BU342" s="3"/>
       <c r="BV342" s="3"/>
-    </row>
-    <row r="343" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW342" s="3"/>
+      <c r="BX342" s="3"/>
+      <c r="BY342" s="3"/>
+      <c r="BZ342" s="3"/>
+    </row>
+    <row r="343" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
       <c r="E343" s="3"/>
@@ -27234,8 +28754,12 @@
       <c r="BT343" s="3"/>
       <c r="BU343" s="3"/>
       <c r="BV343" s="3"/>
-    </row>
-    <row r="344" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW343" s="3"/>
+      <c r="BX343" s="3"/>
+      <c r="BY343" s="3"/>
+      <c r="BZ343" s="3"/>
+    </row>
+    <row r="344" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
       <c r="E344" s="3"/>
@@ -27308,8 +28832,12 @@
       <c r="BT344" s="3"/>
       <c r="BU344" s="3"/>
       <c r="BV344" s="3"/>
-    </row>
-    <row r="345" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW344" s="3"/>
+      <c r="BX344" s="3"/>
+      <c r="BY344" s="3"/>
+      <c r="BZ344" s="3"/>
+    </row>
+    <row r="345" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
       <c r="E345" s="3"/>
@@ -27382,8 +28910,12 @@
       <c r="BT345" s="3"/>
       <c r="BU345" s="3"/>
       <c r="BV345" s="3"/>
-    </row>
-    <row r="346" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW345" s="3"/>
+      <c r="BX345" s="3"/>
+      <c r="BY345" s="3"/>
+      <c r="BZ345" s="3"/>
+    </row>
+    <row r="346" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C346" s="3"/>
       <c r="D346" s="3"/>
       <c r="E346" s="3"/>
@@ -27456,8 +28988,12 @@
       <c r="BT346" s="3"/>
       <c r="BU346" s="3"/>
       <c r="BV346" s="3"/>
-    </row>
-    <row r="347" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW346" s="3"/>
+      <c r="BX346" s="3"/>
+      <c r="BY346" s="3"/>
+      <c r="BZ346" s="3"/>
+    </row>
+    <row r="347" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
       <c r="E347" s="3"/>
@@ -27530,8 +29066,12 @@
       <c r="BT347" s="3"/>
       <c r="BU347" s="3"/>
       <c r="BV347" s="3"/>
-    </row>
-    <row r="348" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW347" s="3"/>
+      <c r="BX347" s="3"/>
+      <c r="BY347" s="3"/>
+      <c r="BZ347" s="3"/>
+    </row>
+    <row r="348" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
       <c r="E348" s="3"/>
@@ -27604,8 +29144,12 @@
       <c r="BT348" s="3"/>
       <c r="BU348" s="3"/>
       <c r="BV348" s="3"/>
-    </row>
-    <row r="349" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW348" s="3"/>
+      <c r="BX348" s="3"/>
+      <c r="BY348" s="3"/>
+      <c r="BZ348" s="3"/>
+    </row>
+    <row r="349" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C349" s="3"/>
       <c r="D349" s="3"/>
       <c r="E349" s="3"/>
@@ -27678,8 +29222,12 @@
       <c r="BT349" s="3"/>
       <c r="BU349" s="3"/>
       <c r="BV349" s="3"/>
-    </row>
-    <row r="350" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW349" s="3"/>
+      <c r="BX349" s="3"/>
+      <c r="BY349" s="3"/>
+      <c r="BZ349" s="3"/>
+    </row>
+    <row r="350" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C350" s="3"/>
       <c r="D350" s="3"/>
       <c r="E350" s="3"/>
@@ -27752,8 +29300,12 @@
       <c r="BT350" s="3"/>
       <c r="BU350" s="3"/>
       <c r="BV350" s="3"/>
-    </row>
-    <row r="351" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW350" s="3"/>
+      <c r="BX350" s="3"/>
+      <c r="BY350" s="3"/>
+      <c r="BZ350" s="3"/>
+    </row>
+    <row r="351" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C351" s="3"/>
       <c r="D351" s="3"/>
       <c r="E351" s="3"/>
@@ -27826,8 +29378,12 @@
       <c r="BT351" s="3"/>
       <c r="BU351" s="3"/>
       <c r="BV351" s="3"/>
-    </row>
-    <row r="352" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW351" s="3"/>
+      <c r="BX351" s="3"/>
+      <c r="BY351" s="3"/>
+      <c r="BZ351" s="3"/>
+    </row>
+    <row r="352" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C352" s="3"/>
       <c r="D352" s="3"/>
       <c r="E352" s="3"/>
@@ -27900,8 +29456,12 @@
       <c r="BT352" s="3"/>
       <c r="BU352" s="3"/>
       <c r="BV352" s="3"/>
-    </row>
-    <row r="353" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW352" s="3"/>
+      <c r="BX352" s="3"/>
+      <c r="BY352" s="3"/>
+      <c r="BZ352" s="3"/>
+    </row>
+    <row r="353" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C353" s="3"/>
       <c r="D353" s="3"/>
       <c r="E353" s="3"/>
@@ -27974,8 +29534,12 @@
       <c r="BT353" s="3"/>
       <c r="BU353" s="3"/>
       <c r="BV353" s="3"/>
-    </row>
-    <row r="354" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW353" s="3"/>
+      <c r="BX353" s="3"/>
+      <c r="BY353" s="3"/>
+      <c r="BZ353" s="3"/>
+    </row>
+    <row r="354" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C354" s="3"/>
       <c r="D354" s="3"/>
       <c r="E354" s="3"/>
@@ -28048,8 +29612,12 @@
       <c r="BT354" s="3"/>
       <c r="BU354" s="3"/>
       <c r="BV354" s="3"/>
-    </row>
-    <row r="355" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW354" s="3"/>
+      <c r="BX354" s="3"/>
+      <c r="BY354" s="3"/>
+      <c r="BZ354" s="3"/>
+    </row>
+    <row r="355" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C355" s="3"/>
       <c r="D355" s="3"/>
       <c r="E355" s="3"/>
@@ -28122,8 +29690,12 @@
       <c r="BT355" s="3"/>
       <c r="BU355" s="3"/>
       <c r="BV355" s="3"/>
-    </row>
-    <row r="356" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW355" s="3"/>
+      <c r="BX355" s="3"/>
+      <c r="BY355" s="3"/>
+      <c r="BZ355" s="3"/>
+    </row>
+    <row r="356" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C356" s="3"/>
       <c r="D356" s="3"/>
       <c r="E356" s="3"/>
@@ -28196,8 +29768,12 @@
       <c r="BT356" s="3"/>
       <c r="BU356" s="3"/>
       <c r="BV356" s="3"/>
-    </row>
-    <row r="357" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW356" s="3"/>
+      <c r="BX356" s="3"/>
+      <c r="BY356" s="3"/>
+      <c r="BZ356" s="3"/>
+    </row>
+    <row r="357" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C357" s="3"/>
       <c r="D357" s="3"/>
       <c r="E357" s="3"/>
@@ -28270,8 +29846,12 @@
       <c r="BT357" s="3"/>
       <c r="BU357" s="3"/>
       <c r="BV357" s="3"/>
-    </row>
-    <row r="358" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW357" s="3"/>
+      <c r="BX357" s="3"/>
+      <c r="BY357" s="3"/>
+      <c r="BZ357" s="3"/>
+    </row>
+    <row r="358" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C358" s="3"/>
       <c r="D358" s="3"/>
       <c r="E358" s="3"/>
@@ -28344,8 +29924,12 @@
       <c r="BT358" s="3"/>
       <c r="BU358" s="3"/>
       <c r="BV358" s="3"/>
-    </row>
-    <row r="359" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW358" s="3"/>
+      <c r="BX358" s="3"/>
+      <c r="BY358" s="3"/>
+      <c r="BZ358" s="3"/>
+    </row>
+    <row r="359" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C359" s="3"/>
       <c r="D359" s="3"/>
       <c r="E359" s="3"/>
@@ -28418,8 +30002,12 @@
       <c r="BT359" s="3"/>
       <c r="BU359" s="3"/>
       <c r="BV359" s="3"/>
-    </row>
-    <row r="360" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW359" s="3"/>
+      <c r="BX359" s="3"/>
+      <c r="BY359" s="3"/>
+      <c r="BZ359" s="3"/>
+    </row>
+    <row r="360" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C360" s="3"/>
       <c r="D360" s="3"/>
       <c r="E360" s="3"/>
@@ -28492,8 +30080,12 @@
       <c r="BT360" s="3"/>
       <c r="BU360" s="3"/>
       <c r="BV360" s="3"/>
-    </row>
-    <row r="361" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW360" s="3"/>
+      <c r="BX360" s="3"/>
+      <c r="BY360" s="3"/>
+      <c r="BZ360" s="3"/>
+    </row>
+    <row r="361" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C361" s="3"/>
       <c r="D361" s="3"/>
       <c r="E361" s="3"/>
@@ -28566,8 +30158,12 @@
       <c r="BT361" s="3"/>
       <c r="BU361" s="3"/>
       <c r="BV361" s="3"/>
-    </row>
-    <row r="362" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW361" s="3"/>
+      <c r="BX361" s="3"/>
+      <c r="BY361" s="3"/>
+      <c r="BZ361" s="3"/>
+    </row>
+    <row r="362" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C362" s="3"/>
       <c r="D362" s="3"/>
       <c r="E362" s="3"/>
@@ -28640,8 +30236,12 @@
       <c r="BT362" s="3"/>
       <c r="BU362" s="3"/>
       <c r="BV362" s="3"/>
-    </row>
-    <row r="363" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW362" s="3"/>
+      <c r="BX362" s="3"/>
+      <c r="BY362" s="3"/>
+      <c r="BZ362" s="3"/>
+    </row>
+    <row r="363" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C363" s="3"/>
       <c r="D363" s="3"/>
       <c r="E363" s="3"/>
@@ -28714,8 +30314,12 @@
       <c r="BT363" s="3"/>
       <c r="BU363" s="3"/>
       <c r="BV363" s="3"/>
-    </row>
-    <row r="364" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW363" s="3"/>
+      <c r="BX363" s="3"/>
+      <c r="BY363" s="3"/>
+      <c r="BZ363" s="3"/>
+    </row>
+    <row r="364" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C364" s="3"/>
       <c r="D364" s="3"/>
       <c r="E364" s="3"/>
@@ -28788,8 +30392,12 @@
       <c r="BT364" s="3"/>
       <c r="BU364" s="3"/>
       <c r="BV364" s="3"/>
-    </row>
-    <row r="365" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW364" s="3"/>
+      <c r="BX364" s="3"/>
+      <c r="BY364" s="3"/>
+      <c r="BZ364" s="3"/>
+    </row>
+    <row r="365" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C365" s="3"/>
       <c r="D365" s="3"/>
       <c r="E365" s="3"/>
@@ -28862,8 +30470,12 @@
       <c r="BT365" s="3"/>
       <c r="BU365" s="3"/>
       <c r="BV365" s="3"/>
-    </row>
-    <row r="366" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW365" s="3"/>
+      <c r="BX365" s="3"/>
+      <c r="BY365" s="3"/>
+      <c r="BZ365" s="3"/>
+    </row>
+    <row r="366" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C366" s="3"/>
       <c r="D366" s="3"/>
       <c r="E366" s="3"/>
@@ -28936,8 +30548,12 @@
       <c r="BT366" s="3"/>
       <c r="BU366" s="3"/>
       <c r="BV366" s="3"/>
-    </row>
-    <row r="367" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW366" s="3"/>
+      <c r="BX366" s="3"/>
+      <c r="BY366" s="3"/>
+      <c r="BZ366" s="3"/>
+    </row>
+    <row r="367" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C367" s="3"/>
       <c r="D367" s="3"/>
       <c r="E367" s="3"/>
@@ -29010,8 +30626,12 @@
       <c r="BT367" s="3"/>
       <c r="BU367" s="3"/>
       <c r="BV367" s="3"/>
-    </row>
-    <row r="368" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW367" s="3"/>
+      <c r="BX367" s="3"/>
+      <c r="BY367" s="3"/>
+      <c r="BZ367" s="3"/>
+    </row>
+    <row r="368" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C368" s="3"/>
       <c r="D368" s="3"/>
       <c r="E368" s="3"/>
@@ -29084,8 +30704,12 @@
       <c r="BT368" s="3"/>
       <c r="BU368" s="3"/>
       <c r="BV368" s="3"/>
-    </row>
-    <row r="369" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW368" s="3"/>
+      <c r="BX368" s="3"/>
+      <c r="BY368" s="3"/>
+      <c r="BZ368" s="3"/>
+    </row>
+    <row r="369" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C369" s="3"/>
       <c r="D369" s="3"/>
       <c r="E369" s="3"/>
@@ -29158,8 +30782,12 @@
       <c r="BT369" s="3"/>
       <c r="BU369" s="3"/>
       <c r="BV369" s="3"/>
-    </row>
-    <row r="370" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW369" s="3"/>
+      <c r="BX369" s="3"/>
+      <c r="BY369" s="3"/>
+      <c r="BZ369" s="3"/>
+    </row>
+    <row r="370" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C370" s="3"/>
       <c r="D370" s="3"/>
       <c r="E370" s="3"/>
@@ -29232,8 +30860,12 @@
       <c r="BT370" s="3"/>
       <c r="BU370" s="3"/>
       <c r="BV370" s="3"/>
-    </row>
-    <row r="371" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW370" s="3"/>
+      <c r="BX370" s="3"/>
+      <c r="BY370" s="3"/>
+      <c r="BZ370" s="3"/>
+    </row>
+    <row r="371" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C371" s="3"/>
       <c r="D371" s="3"/>
       <c r="E371" s="3"/>
@@ -29306,8 +30938,12 @@
       <c r="BT371" s="3"/>
       <c r="BU371" s="3"/>
       <c r="BV371" s="3"/>
-    </row>
-    <row r="372" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW371" s="3"/>
+      <c r="BX371" s="3"/>
+      <c r="BY371" s="3"/>
+      <c r="BZ371" s="3"/>
+    </row>
+    <row r="372" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C372" s="3"/>
       <c r="D372" s="3"/>
       <c r="E372" s="3"/>
@@ -29380,8 +31016,12 @@
       <c r="BT372" s="3"/>
       <c r="BU372" s="3"/>
       <c r="BV372" s="3"/>
-    </row>
-    <row r="373" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW372" s="3"/>
+      <c r="BX372" s="3"/>
+      <c r="BY372" s="3"/>
+      <c r="BZ372" s="3"/>
+    </row>
+    <row r="373" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C373" s="3"/>
       <c r="D373" s="3"/>
       <c r="E373" s="3"/>
@@ -29454,8 +31094,12 @@
       <c r="BT373" s="3"/>
       <c r="BU373" s="3"/>
       <c r="BV373" s="3"/>
-    </row>
-    <row r="374" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW373" s="3"/>
+      <c r="BX373" s="3"/>
+      <c r="BY373" s="3"/>
+      <c r="BZ373" s="3"/>
+    </row>
+    <row r="374" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C374" s="3"/>
       <c r="D374" s="3"/>
       <c r="E374" s="3"/>
@@ -29528,8 +31172,12 @@
       <c r="BT374" s="3"/>
       <c r="BU374" s="3"/>
       <c r="BV374" s="3"/>
-    </row>
-    <row r="375" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW374" s="3"/>
+      <c r="BX374" s="3"/>
+      <c r="BY374" s="3"/>
+      <c r="BZ374" s="3"/>
+    </row>
+    <row r="375" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C375" s="3"/>
       <c r="D375" s="3"/>
       <c r="E375" s="3"/>
@@ -29602,8 +31250,12 @@
       <c r="BT375" s="3"/>
       <c r="BU375" s="3"/>
       <c r="BV375" s="3"/>
-    </row>
-    <row r="376" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW375" s="3"/>
+      <c r="BX375" s="3"/>
+      <c r="BY375" s="3"/>
+      <c r="BZ375" s="3"/>
+    </row>
+    <row r="376" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C376" s="3"/>
       <c r="D376" s="3"/>
       <c r="E376" s="3"/>
@@ -29676,8 +31328,12 @@
       <c r="BT376" s="3"/>
       <c r="BU376" s="3"/>
       <c r="BV376" s="3"/>
-    </row>
-    <row r="377" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW376" s="3"/>
+      <c r="BX376" s="3"/>
+      <c r="BY376" s="3"/>
+      <c r="BZ376" s="3"/>
+    </row>
+    <row r="377" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C377" s="3"/>
       <c r="D377" s="3"/>
       <c r="E377" s="3"/>
@@ -29750,8 +31406,12 @@
       <c r="BT377" s="3"/>
       <c r="BU377" s="3"/>
       <c r="BV377" s="3"/>
-    </row>
-    <row r="378" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW377" s="3"/>
+      <c r="BX377" s="3"/>
+      <c r="BY377" s="3"/>
+      <c r="BZ377" s="3"/>
+    </row>
+    <row r="378" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C378" s="3"/>
       <c r="D378" s="3"/>
       <c r="E378" s="3"/>
@@ -29824,8 +31484,12 @@
       <c r="BT378" s="3"/>
       <c r="BU378" s="3"/>
       <c r="BV378" s="3"/>
-    </row>
-    <row r="379" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW378" s="3"/>
+      <c r="BX378" s="3"/>
+      <c r="BY378" s="3"/>
+      <c r="BZ378" s="3"/>
+    </row>
+    <row r="379" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
       <c r="E379" s="3"/>
@@ -29898,8 +31562,12 @@
       <c r="BT379" s="3"/>
       <c r="BU379" s="3"/>
       <c r="BV379" s="3"/>
-    </row>
-    <row r="380" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW379" s="3"/>
+      <c r="BX379" s="3"/>
+      <c r="BY379" s="3"/>
+      <c r="BZ379" s="3"/>
+    </row>
+    <row r="380" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C380" s="3"/>
       <c r="D380" s="3"/>
       <c r="E380" s="3"/>
@@ -29972,8 +31640,12 @@
       <c r="BT380" s="3"/>
       <c r="BU380" s="3"/>
       <c r="BV380" s="3"/>
-    </row>
-    <row r="381" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW380" s="3"/>
+      <c r="BX380" s="3"/>
+      <c r="BY380" s="3"/>
+      <c r="BZ380" s="3"/>
+    </row>
+    <row r="381" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C381" s="3"/>
       <c r="D381" s="3"/>
       <c r="E381" s="3"/>
@@ -30046,8 +31718,12 @@
       <c r="BT381" s="3"/>
       <c r="BU381" s="3"/>
       <c r="BV381" s="3"/>
-    </row>
-    <row r="382" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW381" s="3"/>
+      <c r="BX381" s="3"/>
+      <c r="BY381" s="3"/>
+      <c r="BZ381" s="3"/>
+    </row>
+    <row r="382" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C382" s="3"/>
       <c r="D382" s="3"/>
       <c r="E382" s="3"/>
@@ -30120,8 +31796,12 @@
       <c r="BT382" s="3"/>
       <c r="BU382" s="3"/>
       <c r="BV382" s="3"/>
-    </row>
-    <row r="383" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW382" s="3"/>
+      <c r="BX382" s="3"/>
+      <c r="BY382" s="3"/>
+      <c r="BZ382" s="3"/>
+    </row>
+    <row r="383" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C383" s="3"/>
       <c r="D383" s="3"/>
       <c r="E383" s="3"/>
@@ -30194,8 +31874,12 @@
       <c r="BT383" s="3"/>
       <c r="BU383" s="3"/>
       <c r="BV383" s="3"/>
-    </row>
-    <row r="384" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW383" s="3"/>
+      <c r="BX383" s="3"/>
+      <c r="BY383" s="3"/>
+      <c r="BZ383" s="3"/>
+    </row>
+    <row r="384" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C384" s="3"/>
       <c r="D384" s="3"/>
       <c r="E384" s="3"/>
@@ -30268,8 +31952,12 @@
       <c r="BT384" s="3"/>
       <c r="BU384" s="3"/>
       <c r="BV384" s="3"/>
-    </row>
-    <row r="385" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW384" s="3"/>
+      <c r="BX384" s="3"/>
+      <c r="BY384" s="3"/>
+      <c r="BZ384" s="3"/>
+    </row>
+    <row r="385" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C385" s="3"/>
       <c r="D385" s="3"/>
       <c r="E385" s="3"/>
@@ -30342,8 +32030,12 @@
       <c r="BT385" s="3"/>
       <c r="BU385" s="3"/>
       <c r="BV385" s="3"/>
-    </row>
-    <row r="386" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW385" s="3"/>
+      <c r="BX385" s="3"/>
+      <c r="BY385" s="3"/>
+      <c r="BZ385" s="3"/>
+    </row>
+    <row r="386" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C386" s="3"/>
       <c r="D386" s="3"/>
       <c r="E386" s="3"/>
@@ -30416,8 +32108,12 @@
       <c r="BT386" s="3"/>
       <c r="BU386" s="3"/>
       <c r="BV386" s="3"/>
-    </row>
-    <row r="387" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW386" s="3"/>
+      <c r="BX386" s="3"/>
+      <c r="BY386" s="3"/>
+      <c r="BZ386" s="3"/>
+    </row>
+    <row r="387" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C387" s="3"/>
       <c r="D387" s="3"/>
       <c r="E387" s="3"/>
@@ -30490,8 +32186,12 @@
       <c r="BT387" s="3"/>
       <c r="BU387" s="3"/>
       <c r="BV387" s="3"/>
-    </row>
-    <row r="388" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW387" s="3"/>
+      <c r="BX387" s="3"/>
+      <c r="BY387" s="3"/>
+      <c r="BZ387" s="3"/>
+    </row>
+    <row r="388" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C388" s="3"/>
       <c r="D388" s="3"/>
       <c r="E388" s="3"/>
@@ -30564,8 +32264,12 @@
       <c r="BT388" s="3"/>
       <c r="BU388" s="3"/>
       <c r="BV388" s="3"/>
-    </row>
-    <row r="389" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW388" s="3"/>
+      <c r="BX388" s="3"/>
+      <c r="BY388" s="3"/>
+      <c r="BZ388" s="3"/>
+    </row>
+    <row r="389" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C389" s="3"/>
       <c r="D389" s="3"/>
       <c r="E389" s="3"/>
@@ -30638,8 +32342,12 @@
       <c r="BT389" s="3"/>
       <c r="BU389" s="3"/>
       <c r="BV389" s="3"/>
-    </row>
-    <row r="390" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW389" s="3"/>
+      <c r="BX389" s="3"/>
+      <c r="BY389" s="3"/>
+      <c r="BZ389" s="3"/>
+    </row>
+    <row r="390" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C390" s="3"/>
       <c r="D390" s="3"/>
       <c r="E390" s="3"/>
@@ -30712,8 +32420,12 @@
       <c r="BT390" s="3"/>
       <c r="BU390" s="3"/>
       <c r="BV390" s="3"/>
-    </row>
-    <row r="391" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW390" s="3"/>
+      <c r="BX390" s="3"/>
+      <c r="BY390" s="3"/>
+      <c r="BZ390" s="3"/>
+    </row>
+    <row r="391" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C391" s="3"/>
       <c r="D391" s="3"/>
       <c r="E391" s="3"/>
@@ -30786,8 +32498,12 @@
       <c r="BT391" s="3"/>
       <c r="BU391" s="3"/>
       <c r="BV391" s="3"/>
-    </row>
-    <row r="392" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW391" s="3"/>
+      <c r="BX391" s="3"/>
+      <c r="BY391" s="3"/>
+      <c r="BZ391" s="3"/>
+    </row>
+    <row r="392" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C392" s="3"/>
       <c r="D392" s="3"/>
       <c r="E392" s="3"/>
@@ -30860,8 +32576,12 @@
       <c r="BT392" s="3"/>
       <c r="BU392" s="3"/>
       <c r="BV392" s="3"/>
-    </row>
-    <row r="393" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW392" s="3"/>
+      <c r="BX392" s="3"/>
+      <c r="BY392" s="3"/>
+      <c r="BZ392" s="3"/>
+    </row>
+    <row r="393" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C393" s="3"/>
       <c r="D393" s="3"/>
       <c r="E393" s="3"/>
@@ -30934,8 +32654,12 @@
       <c r="BT393" s="3"/>
       <c r="BU393" s="3"/>
       <c r="BV393" s="3"/>
-    </row>
-    <row r="394" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW393" s="3"/>
+      <c r="BX393" s="3"/>
+      <c r="BY393" s="3"/>
+      <c r="BZ393" s="3"/>
+    </row>
+    <row r="394" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C394" s="3"/>
       <c r="D394" s="3"/>
       <c r="E394" s="3"/>
@@ -31008,8 +32732,12 @@
       <c r="BT394" s="3"/>
       <c r="BU394" s="3"/>
       <c r="BV394" s="3"/>
-    </row>
-    <row r="395" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW394" s="3"/>
+      <c r="BX394" s="3"/>
+      <c r="BY394" s="3"/>
+      <c r="BZ394" s="3"/>
+    </row>
+    <row r="395" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C395" s="3"/>
       <c r="D395" s="3"/>
       <c r="E395" s="3"/>
@@ -31082,8 +32810,12 @@
       <c r="BT395" s="3"/>
       <c r="BU395" s="3"/>
       <c r="BV395" s="3"/>
-    </row>
-    <row r="396" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW395" s="3"/>
+      <c r="BX395" s="3"/>
+      <c r="BY395" s="3"/>
+      <c r="BZ395" s="3"/>
+    </row>
+    <row r="396" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C396" s="3"/>
       <c r="D396" s="3"/>
       <c r="E396" s="3"/>
@@ -31156,8 +32888,12 @@
       <c r="BT396" s="3"/>
       <c r="BU396" s="3"/>
       <c r="BV396" s="3"/>
-    </row>
-    <row r="397" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW396" s="3"/>
+      <c r="BX396" s="3"/>
+      <c r="BY396" s="3"/>
+      <c r="BZ396" s="3"/>
+    </row>
+    <row r="397" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C397" s="3"/>
       <c r="D397" s="3"/>
       <c r="E397" s="3"/>
@@ -31230,8 +32966,12 @@
       <c r="BT397" s="3"/>
       <c r="BU397" s="3"/>
       <c r="BV397" s="3"/>
-    </row>
-    <row r="398" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW397" s="3"/>
+      <c r="BX397" s="3"/>
+      <c r="BY397" s="3"/>
+      <c r="BZ397" s="3"/>
+    </row>
+    <row r="398" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C398" s="3"/>
       <c r="D398" s="3"/>
       <c r="E398" s="3"/>
@@ -31304,8 +33044,12 @@
       <c r="BT398" s="3"/>
       <c r="BU398" s="3"/>
       <c r="BV398" s="3"/>
-    </row>
-    <row r="399" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW398" s="3"/>
+      <c r="BX398" s="3"/>
+      <c r="BY398" s="3"/>
+      <c r="BZ398" s="3"/>
+    </row>
+    <row r="399" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C399" s="3"/>
       <c r="D399" s="3"/>
       <c r="E399" s="3"/>
@@ -31378,8 +33122,12 @@
       <c r="BT399" s="3"/>
       <c r="BU399" s="3"/>
       <c r="BV399" s="3"/>
-    </row>
-    <row r="400" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW399" s="3"/>
+      <c r="BX399" s="3"/>
+      <c r="BY399" s="3"/>
+      <c r="BZ399" s="3"/>
+    </row>
+    <row r="400" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C400" s="3"/>
       <c r="D400" s="3"/>
       <c r="E400" s="3"/>
@@ -31452,8 +33200,12 @@
       <c r="BT400" s="3"/>
       <c r="BU400" s="3"/>
       <c r="BV400" s="3"/>
-    </row>
-    <row r="401" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW400" s="3"/>
+      <c r="BX400" s="3"/>
+      <c r="BY400" s="3"/>
+      <c r="BZ400" s="3"/>
+    </row>
+    <row r="401" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C401" s="3"/>
       <c r="D401" s="3"/>
       <c r="E401" s="3"/>
@@ -31526,8 +33278,12 @@
       <c r="BT401" s="3"/>
       <c r="BU401" s="3"/>
       <c r="BV401" s="3"/>
-    </row>
-    <row r="402" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW401" s="3"/>
+      <c r="BX401" s="3"/>
+      <c r="BY401" s="3"/>
+      <c r="BZ401" s="3"/>
+    </row>
+    <row r="402" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C402" s="3"/>
       <c r="D402" s="3"/>
       <c r="E402" s="3"/>
@@ -31600,8 +33356,12 @@
       <c r="BT402" s="3"/>
       <c r="BU402" s="3"/>
       <c r="BV402" s="3"/>
-    </row>
-    <row r="403" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW402" s="3"/>
+      <c r="BX402" s="3"/>
+      <c r="BY402" s="3"/>
+      <c r="BZ402" s="3"/>
+    </row>
+    <row r="403" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C403" s="3"/>
       <c r="D403" s="3"/>
       <c r="E403" s="3"/>
@@ -31674,8 +33434,12 @@
       <c r="BT403" s="3"/>
       <c r="BU403" s="3"/>
       <c r="BV403" s="3"/>
-    </row>
-    <row r="404" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW403" s="3"/>
+      <c r="BX403" s="3"/>
+      <c r="BY403" s="3"/>
+      <c r="BZ403" s="3"/>
+    </row>
+    <row r="404" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C404" s="3"/>
       <c r="D404" s="3"/>
       <c r="E404" s="3"/>
@@ -31748,8 +33512,12 @@
       <c r="BT404" s="3"/>
       <c r="BU404" s="3"/>
       <c r="BV404" s="3"/>
-    </row>
-    <row r="405" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW404" s="3"/>
+      <c r="BX404" s="3"/>
+      <c r="BY404" s="3"/>
+      <c r="BZ404" s="3"/>
+    </row>
+    <row r="405" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C405" s="3"/>
       <c r="D405" s="3"/>
       <c r="E405" s="3"/>
@@ -31822,8 +33590,12 @@
       <c r="BT405" s="3"/>
       <c r="BU405" s="3"/>
       <c r="BV405" s="3"/>
-    </row>
-    <row r="406" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW405" s="3"/>
+      <c r="BX405" s="3"/>
+      <c r="BY405" s="3"/>
+      <c r="BZ405" s="3"/>
+    </row>
+    <row r="406" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C406" s="3"/>
       <c r="D406" s="3"/>
       <c r="E406" s="3"/>
@@ -31896,8 +33668,12 @@
       <c r="BT406" s="3"/>
       <c r="BU406" s="3"/>
       <c r="BV406" s="3"/>
-    </row>
-    <row r="407" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW406" s="3"/>
+      <c r="BX406" s="3"/>
+      <c r="BY406" s="3"/>
+      <c r="BZ406" s="3"/>
+    </row>
+    <row r="407" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C407" s="3"/>
       <c r="D407" s="3"/>
       <c r="E407" s="3"/>
@@ -31970,8 +33746,12 @@
       <c r="BT407" s="3"/>
       <c r="BU407" s="3"/>
       <c r="BV407" s="3"/>
-    </row>
-    <row r="408" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW407" s="3"/>
+      <c r="BX407" s="3"/>
+      <c r="BY407" s="3"/>
+      <c r="BZ407" s="3"/>
+    </row>
+    <row r="408" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C408" s="3"/>
       <c r="D408" s="3"/>
       <c r="E408" s="3"/>
@@ -32044,8 +33824,12 @@
       <c r="BT408" s="3"/>
       <c r="BU408" s="3"/>
       <c r="BV408" s="3"/>
-    </row>
-    <row r="409" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW408" s="3"/>
+      <c r="BX408" s="3"/>
+      <c r="BY408" s="3"/>
+      <c r="BZ408" s="3"/>
+    </row>
+    <row r="409" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C409" s="3"/>
       <c r="D409" s="3"/>
       <c r="E409" s="3"/>
@@ -32118,8 +33902,12 @@
       <c r="BT409" s="3"/>
       <c r="BU409" s="3"/>
       <c r="BV409" s="3"/>
-    </row>
-    <row r="410" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW409" s="3"/>
+      <c r="BX409" s="3"/>
+      <c r="BY409" s="3"/>
+      <c r="BZ409" s="3"/>
+    </row>
+    <row r="410" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C410" s="3"/>
       <c r="D410" s="3"/>
       <c r="E410" s="3"/>
@@ -32192,8 +33980,12 @@
       <c r="BT410" s="3"/>
       <c r="BU410" s="3"/>
       <c r="BV410" s="3"/>
-    </row>
-    <row r="411" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW410" s="3"/>
+      <c r="BX410" s="3"/>
+      <c r="BY410" s="3"/>
+      <c r="BZ410" s="3"/>
+    </row>
+    <row r="411" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C411" s="3"/>
       <c r="D411" s="3"/>
       <c r="E411" s="3"/>
@@ -32266,8 +34058,12 @@
       <c r="BT411" s="3"/>
       <c r="BU411" s="3"/>
       <c r="BV411" s="3"/>
-    </row>
-    <row r="412" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW411" s="3"/>
+      <c r="BX411" s="3"/>
+      <c r="BY411" s="3"/>
+      <c r="BZ411" s="3"/>
+    </row>
+    <row r="412" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C412" s="3"/>
       <c r="D412" s="3"/>
       <c r="E412" s="3"/>
@@ -32340,8 +34136,12 @@
       <c r="BT412" s="3"/>
       <c r="BU412" s="3"/>
       <c r="BV412" s="3"/>
-    </row>
-    <row r="413" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW412" s="3"/>
+      <c r="BX412" s="3"/>
+      <c r="BY412" s="3"/>
+      <c r="BZ412" s="3"/>
+    </row>
+    <row r="413" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C413" s="3"/>
       <c r="D413" s="3"/>
       <c r="E413" s="3"/>
@@ -32414,8 +34214,12 @@
       <c r="BT413" s="3"/>
       <c r="BU413" s="3"/>
       <c r="BV413" s="3"/>
-    </row>
-    <row r="414" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW413" s="3"/>
+      <c r="BX413" s="3"/>
+      <c r="BY413" s="3"/>
+      <c r="BZ413" s="3"/>
+    </row>
+    <row r="414" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C414" s="3"/>
       <c r="D414" s="3"/>
       <c r="E414" s="3"/>
@@ -32488,8 +34292,12 @@
       <c r="BT414" s="3"/>
       <c r="BU414" s="3"/>
       <c r="BV414" s="3"/>
-    </row>
-    <row r="415" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW414" s="3"/>
+      <c r="BX414" s="3"/>
+      <c r="BY414" s="3"/>
+      <c r="BZ414" s="3"/>
+    </row>
+    <row r="415" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C415" s="3"/>
       <c r="D415" s="3"/>
       <c r="E415" s="3"/>
@@ -32562,8 +34370,12 @@
       <c r="BT415" s="3"/>
       <c r="BU415" s="3"/>
       <c r="BV415" s="3"/>
-    </row>
-    <row r="416" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW415" s="3"/>
+      <c r="BX415" s="3"/>
+      <c r="BY415" s="3"/>
+      <c r="BZ415" s="3"/>
+    </row>
+    <row r="416" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C416" s="3"/>
       <c r="D416" s="3"/>
       <c r="E416" s="3"/>
@@ -32636,8 +34448,12 @@
       <c r="BT416" s="3"/>
       <c r="BU416" s="3"/>
       <c r="BV416" s="3"/>
-    </row>
-    <row r="417" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW416" s="3"/>
+      <c r="BX416" s="3"/>
+      <c r="BY416" s="3"/>
+      <c r="BZ416" s="3"/>
+    </row>
+    <row r="417" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C417" s="3"/>
       <c r="D417" s="3"/>
       <c r="E417" s="3"/>
@@ -32710,8 +34526,12 @@
       <c r="BT417" s="3"/>
       <c r="BU417" s="3"/>
       <c r="BV417" s="3"/>
-    </row>
-    <row r="418" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW417" s="3"/>
+      <c r="BX417" s="3"/>
+      <c r="BY417" s="3"/>
+      <c r="BZ417" s="3"/>
+    </row>
+    <row r="418" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C418" s="3"/>
       <c r="D418" s="3"/>
       <c r="E418" s="3"/>
@@ -32784,8 +34604,12 @@
       <c r="BT418" s="3"/>
       <c r="BU418" s="3"/>
       <c r="BV418" s="3"/>
-    </row>
-    <row r="419" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW418" s="3"/>
+      <c r="BX418" s="3"/>
+      <c r="BY418" s="3"/>
+      <c r="BZ418" s="3"/>
+    </row>
+    <row r="419" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C419" s="3"/>
       <c r="D419" s="3"/>
       <c r="E419" s="3"/>
@@ -32858,8 +34682,12 @@
       <c r="BT419" s="3"/>
       <c r="BU419" s="3"/>
       <c r="BV419" s="3"/>
-    </row>
-    <row r="420" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW419" s="3"/>
+      <c r="BX419" s="3"/>
+      <c r="BY419" s="3"/>
+      <c r="BZ419" s="3"/>
+    </row>
+    <row r="420" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C420" s="3"/>
       <c r="D420" s="3"/>
       <c r="E420" s="3"/>
@@ -32932,8 +34760,12 @@
       <c r="BT420" s="3"/>
       <c r="BU420" s="3"/>
       <c r="BV420" s="3"/>
-    </row>
-    <row r="421" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW420" s="3"/>
+      <c r="BX420" s="3"/>
+      <c r="BY420" s="3"/>
+      <c r="BZ420" s="3"/>
+    </row>
+    <row r="421" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C421" s="3"/>
       <c r="D421" s="3"/>
       <c r="E421" s="3"/>
@@ -33006,8 +34838,12 @@
       <c r="BT421" s="3"/>
       <c r="BU421" s="3"/>
       <c r="BV421" s="3"/>
-    </row>
-    <row r="422" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW421" s="3"/>
+      <c r="BX421" s="3"/>
+      <c r="BY421" s="3"/>
+      <c r="BZ421" s="3"/>
+    </row>
+    <row r="422" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C422" s="3"/>
       <c r="D422" s="3"/>
       <c r="E422" s="3"/>
@@ -33080,8 +34916,12 @@
       <c r="BT422" s="3"/>
       <c r="BU422" s="3"/>
       <c r="BV422" s="3"/>
-    </row>
-    <row r="423" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW422" s="3"/>
+      <c r="BX422" s="3"/>
+      <c r="BY422" s="3"/>
+      <c r="BZ422" s="3"/>
+    </row>
+    <row r="423" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C423" s="3"/>
       <c r="D423" s="3"/>
       <c r="E423" s="3"/>
@@ -33154,8 +34994,12 @@
       <c r="BT423" s="3"/>
       <c r="BU423" s="3"/>
       <c r="BV423" s="3"/>
-    </row>
-    <row r="424" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW423" s="3"/>
+      <c r="BX423" s="3"/>
+      <c r="BY423" s="3"/>
+      <c r="BZ423" s="3"/>
+    </row>
+    <row r="424" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C424" s="3"/>
       <c r="D424" s="3"/>
       <c r="E424" s="3"/>
@@ -33228,8 +35072,12 @@
       <c r="BT424" s="3"/>
       <c r="BU424" s="3"/>
       <c r="BV424" s="3"/>
-    </row>
-    <row r="425" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW424" s="3"/>
+      <c r="BX424" s="3"/>
+      <c r="BY424" s="3"/>
+      <c r="BZ424" s="3"/>
+    </row>
+    <row r="425" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C425" s="3"/>
       <c r="D425" s="3"/>
       <c r="E425" s="3"/>
@@ -33302,8 +35150,12 @@
       <c r="BT425" s="3"/>
       <c r="BU425" s="3"/>
       <c r="BV425" s="3"/>
-    </row>
-    <row r="426" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW425" s="3"/>
+      <c r="BX425" s="3"/>
+      <c r="BY425" s="3"/>
+      <c r="BZ425" s="3"/>
+    </row>
+    <row r="426" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C426" s="3"/>
       <c r="D426" s="3"/>
       <c r="E426" s="3"/>
@@ -33376,8 +35228,12 @@
       <c r="BT426" s="3"/>
       <c r="BU426" s="3"/>
       <c r="BV426" s="3"/>
-    </row>
-    <row r="427" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW426" s="3"/>
+      <c r="BX426" s="3"/>
+      <c r="BY426" s="3"/>
+      <c r="BZ426" s="3"/>
+    </row>
+    <row r="427" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C427" s="3"/>
       <c r="D427" s="3"/>
       <c r="E427" s="3"/>
@@ -33450,8 +35306,12 @@
       <c r="BT427" s="3"/>
       <c r="BU427" s="3"/>
       <c r="BV427" s="3"/>
-    </row>
-    <row r="428" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW427" s="3"/>
+      <c r="BX427" s="3"/>
+      <c r="BY427" s="3"/>
+      <c r="BZ427" s="3"/>
+    </row>
+    <row r="428" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C428" s="3"/>
       <c r="D428" s="3"/>
       <c r="E428" s="3"/>
@@ -33524,8 +35384,12 @@
       <c r="BT428" s="3"/>
       <c r="BU428" s="3"/>
       <c r="BV428" s="3"/>
-    </row>
-    <row r="429" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW428" s="3"/>
+      <c r="BX428" s="3"/>
+      <c r="BY428" s="3"/>
+      <c r="BZ428" s="3"/>
+    </row>
+    <row r="429" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C429" s="3"/>
       <c r="D429" s="3"/>
       <c r="E429" s="3"/>
@@ -33598,8 +35462,12 @@
       <c r="BT429" s="3"/>
       <c r="BU429" s="3"/>
       <c r="BV429" s="3"/>
-    </row>
-    <row r="430" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW429" s="3"/>
+      <c r="BX429" s="3"/>
+      <c r="BY429" s="3"/>
+      <c r="BZ429" s="3"/>
+    </row>
+    <row r="430" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C430" s="3"/>
       <c r="D430" s="3"/>
       <c r="E430" s="3"/>
@@ -33672,8 +35540,12 @@
       <c r="BT430" s="3"/>
       <c r="BU430" s="3"/>
       <c r="BV430" s="3"/>
-    </row>
-    <row r="431" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW430" s="3"/>
+      <c r="BX430" s="3"/>
+      <c r="BY430" s="3"/>
+      <c r="BZ430" s="3"/>
+    </row>
+    <row r="431" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C431" s="3"/>
       <c r="D431" s="3"/>
       <c r="E431" s="3"/>
@@ -33746,8 +35618,12 @@
       <c r="BT431" s="3"/>
       <c r="BU431" s="3"/>
       <c r="BV431" s="3"/>
-    </row>
-    <row r="432" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW431" s="3"/>
+      <c r="BX431" s="3"/>
+      <c r="BY431" s="3"/>
+      <c r="BZ431" s="3"/>
+    </row>
+    <row r="432" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C432" s="3"/>
       <c r="D432" s="3"/>
       <c r="E432" s="3"/>
@@ -33820,8 +35696,12 @@
       <c r="BT432" s="3"/>
       <c r="BU432" s="3"/>
       <c r="BV432" s="3"/>
-    </row>
-    <row r="433" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW432" s="3"/>
+      <c r="BX432" s="3"/>
+      <c r="BY432" s="3"/>
+      <c r="BZ432" s="3"/>
+    </row>
+    <row r="433" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C433" s="3"/>
       <c r="D433" s="3"/>
       <c r="E433" s="3"/>
@@ -33894,8 +35774,12 @@
       <c r="BT433" s="3"/>
       <c r="BU433" s="3"/>
       <c r="BV433" s="3"/>
-    </row>
-    <row r="434" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW433" s="3"/>
+      <c r="BX433" s="3"/>
+      <c r="BY433" s="3"/>
+      <c r="BZ433" s="3"/>
+    </row>
+    <row r="434" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C434" s="3"/>
       <c r="D434" s="3"/>
       <c r="E434" s="3"/>
@@ -33968,8 +35852,12 @@
       <c r="BT434" s="3"/>
       <c r="BU434" s="3"/>
       <c r="BV434" s="3"/>
-    </row>
-    <row r="435" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW434" s="3"/>
+      <c r="BX434" s="3"/>
+      <c r="BY434" s="3"/>
+      <c r="BZ434" s="3"/>
+    </row>
+    <row r="435" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C435" s="3"/>
       <c r="D435" s="3"/>
       <c r="E435" s="3"/>
@@ -34042,8 +35930,12 @@
       <c r="BT435" s="3"/>
       <c r="BU435" s="3"/>
       <c r="BV435" s="3"/>
-    </row>
-    <row r="436" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW435" s="3"/>
+      <c r="BX435" s="3"/>
+      <c r="BY435" s="3"/>
+      <c r="BZ435" s="3"/>
+    </row>
+    <row r="436" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C436" s="3"/>
       <c r="D436" s="3"/>
       <c r="E436" s="3"/>
@@ -34116,8 +36008,12 @@
       <c r="BT436" s="3"/>
       <c r="BU436" s="3"/>
       <c r="BV436" s="3"/>
-    </row>
-    <row r="437" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW436" s="3"/>
+      <c r="BX436" s="3"/>
+      <c r="BY436" s="3"/>
+      <c r="BZ436" s="3"/>
+    </row>
+    <row r="437" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C437" s="3"/>
       <c r="D437" s="3"/>
       <c r="E437" s="3"/>
@@ -34190,8 +36086,12 @@
       <c r="BT437" s="3"/>
       <c r="BU437" s="3"/>
       <c r="BV437" s="3"/>
-    </row>
-    <row r="438" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW437" s="3"/>
+      <c r="BX437" s="3"/>
+      <c r="BY437" s="3"/>
+      <c r="BZ437" s="3"/>
+    </row>
+    <row r="438" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C438" s="3"/>
       <c r="D438" s="3"/>
       <c r="E438" s="3"/>
@@ -34264,8 +36164,12 @@
       <c r="BT438" s="3"/>
       <c r="BU438" s="3"/>
       <c r="BV438" s="3"/>
-    </row>
-    <row r="439" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW438" s="3"/>
+      <c r="BX438" s="3"/>
+      <c r="BY438" s="3"/>
+      <c r="BZ438" s="3"/>
+    </row>
+    <row r="439" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C439" s="3"/>
       <c r="D439" s="3"/>
       <c r="E439" s="3"/>
@@ -34338,8 +36242,12 @@
       <c r="BT439" s="3"/>
       <c r="BU439" s="3"/>
       <c r="BV439" s="3"/>
-    </row>
-    <row r="440" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW439" s="3"/>
+      <c r="BX439" s="3"/>
+      <c r="BY439" s="3"/>
+      <c r="BZ439" s="3"/>
+    </row>
+    <row r="440" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C440" s="3"/>
       <c r="D440" s="3"/>
       <c r="E440" s="3"/>
@@ -34412,8 +36320,12 @@
       <c r="BT440" s="3"/>
       <c r="BU440" s="3"/>
       <c r="BV440" s="3"/>
-    </row>
-    <row r="441" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW440" s="3"/>
+      <c r="BX440" s="3"/>
+      <c r="BY440" s="3"/>
+      <c r="BZ440" s="3"/>
+    </row>
+    <row r="441" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C441" s="3"/>
       <c r="D441" s="3"/>
       <c r="E441" s="3"/>
@@ -34486,8 +36398,12 @@
       <c r="BT441" s="3"/>
       <c r="BU441" s="3"/>
       <c r="BV441" s="3"/>
-    </row>
-    <row r="442" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW441" s="3"/>
+      <c r="BX441" s="3"/>
+      <c r="BY441" s="3"/>
+      <c r="BZ441" s="3"/>
+    </row>
+    <row r="442" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C442" s="3"/>
       <c r="D442" s="3"/>
       <c r="E442" s="3"/>
@@ -34560,8 +36476,12 @@
       <c r="BT442" s="3"/>
       <c r="BU442" s="3"/>
       <c r="BV442" s="3"/>
-    </row>
-    <row r="443" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW442" s="3"/>
+      <c r="BX442" s="3"/>
+      <c r="BY442" s="3"/>
+      <c r="BZ442" s="3"/>
+    </row>
+    <row r="443" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C443" s="3"/>
       <c r="D443" s="3"/>
       <c r="E443" s="3"/>
@@ -34634,8 +36554,12 @@
       <c r="BT443" s="3"/>
       <c r="BU443" s="3"/>
       <c r="BV443" s="3"/>
-    </row>
-    <row r="444" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW443" s="3"/>
+      <c r="BX443" s="3"/>
+      <c r="BY443" s="3"/>
+      <c r="BZ443" s="3"/>
+    </row>
+    <row r="444" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C444" s="3"/>
       <c r="D444" s="3"/>
       <c r="E444" s="3"/>
@@ -34708,8 +36632,12 @@
       <c r="BT444" s="3"/>
       <c r="BU444" s="3"/>
       <c r="BV444" s="3"/>
-    </row>
-    <row r="445" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW444" s="3"/>
+      <c r="BX444" s="3"/>
+      <c r="BY444" s="3"/>
+      <c r="BZ444" s="3"/>
+    </row>
+    <row r="445" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C445" s="3"/>
       <c r="D445" s="3"/>
       <c r="E445" s="3"/>
@@ -34782,8 +36710,12 @@
       <c r="BT445" s="3"/>
       <c r="BU445" s="3"/>
       <c r="BV445" s="3"/>
-    </row>
-    <row r="446" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW445" s="3"/>
+      <c r="BX445" s="3"/>
+      <c r="BY445" s="3"/>
+      <c r="BZ445" s="3"/>
+    </row>
+    <row r="446" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C446" s="3"/>
       <c r="D446" s="3"/>
       <c r="E446" s="3"/>
@@ -34856,8 +36788,12 @@
       <c r="BT446" s="3"/>
       <c r="BU446" s="3"/>
       <c r="BV446" s="3"/>
-    </row>
-    <row r="447" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW446" s="3"/>
+      <c r="BX446" s="3"/>
+      <c r="BY446" s="3"/>
+      <c r="BZ446" s="3"/>
+    </row>
+    <row r="447" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C447" s="3"/>
       <c r="D447" s="3"/>
       <c r="E447" s="3"/>
@@ -34930,8 +36866,12 @@
       <c r="BT447" s="3"/>
       <c r="BU447" s="3"/>
       <c r="BV447" s="3"/>
-    </row>
-    <row r="448" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW447" s="3"/>
+      <c r="BX447" s="3"/>
+      <c r="BY447" s="3"/>
+      <c r="BZ447" s="3"/>
+    </row>
+    <row r="448" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C448" s="3"/>
       <c r="D448" s="3"/>
       <c r="E448" s="3"/>
@@ -35004,8 +36944,12 @@
       <c r="BT448" s="3"/>
       <c r="BU448" s="3"/>
       <c r="BV448" s="3"/>
-    </row>
-    <row r="449" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW448" s="3"/>
+      <c r="BX448" s="3"/>
+      <c r="BY448" s="3"/>
+      <c r="BZ448" s="3"/>
+    </row>
+    <row r="449" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C449" s="3"/>
       <c r="D449" s="3"/>
       <c r="E449" s="3"/>
@@ -35078,8 +37022,12 @@
       <c r="BT449" s="3"/>
       <c r="BU449" s="3"/>
       <c r="BV449" s="3"/>
-    </row>
-    <row r="450" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW449" s="3"/>
+      <c r="BX449" s="3"/>
+      <c r="BY449" s="3"/>
+      <c r="BZ449" s="3"/>
+    </row>
+    <row r="450" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C450" s="3"/>
       <c r="D450" s="3"/>
       <c r="E450" s="3"/>
@@ -35152,8 +37100,12 @@
       <c r="BT450" s="3"/>
       <c r="BU450" s="3"/>
       <c r="BV450" s="3"/>
-    </row>
-    <row r="451" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW450" s="3"/>
+      <c r="BX450" s="3"/>
+      <c r="BY450" s="3"/>
+      <c r="BZ450" s="3"/>
+    </row>
+    <row r="451" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C451" s="3"/>
       <c r="D451" s="3"/>
       <c r="E451" s="3"/>
@@ -35226,8 +37178,12 @@
       <c r="BT451" s="3"/>
       <c r="BU451" s="3"/>
       <c r="BV451" s="3"/>
-    </row>
-    <row r="452" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW451" s="3"/>
+      <c r="BX451" s="3"/>
+      <c r="BY451" s="3"/>
+      <c r="BZ451" s="3"/>
+    </row>
+    <row r="452" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C452" s="3"/>
       <c r="D452" s="3"/>
       <c r="E452" s="3"/>
@@ -35300,8 +37256,12 @@
       <c r="BT452" s="3"/>
       <c r="BU452" s="3"/>
       <c r="BV452" s="3"/>
-    </row>
-    <row r="453" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW452" s="3"/>
+      <c r="BX452" s="3"/>
+      <c r="BY452" s="3"/>
+      <c r="BZ452" s="3"/>
+    </row>
+    <row r="453" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C453" s="3"/>
       <c r="D453" s="3"/>
       <c r="E453" s="3"/>
@@ -35374,8 +37334,12 @@
       <c r="BT453" s="3"/>
       <c r="BU453" s="3"/>
       <c r="BV453" s="3"/>
-    </row>
-    <row r="454" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW453" s="3"/>
+      <c r="BX453" s="3"/>
+      <c r="BY453" s="3"/>
+      <c r="BZ453" s="3"/>
+    </row>
+    <row r="454" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C454" s="3"/>
       <c r="D454" s="3"/>
       <c r="E454" s="3"/>
@@ -35448,8 +37412,12 @@
       <c r="BT454" s="3"/>
       <c r="BU454" s="3"/>
       <c r="BV454" s="3"/>
-    </row>
-    <row r="455" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW454" s="3"/>
+      <c r="BX454" s="3"/>
+      <c r="BY454" s="3"/>
+      <c r="BZ454" s="3"/>
+    </row>
+    <row r="455" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C455" s="3"/>
       <c r="D455" s="3"/>
       <c r="E455" s="3"/>
@@ -35522,8 +37490,12 @@
       <c r="BT455" s="3"/>
       <c r="BU455" s="3"/>
       <c r="BV455" s="3"/>
-    </row>
-    <row r="456" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW455" s="3"/>
+      <c r="BX455" s="3"/>
+      <c r="BY455" s="3"/>
+      <c r="BZ455" s="3"/>
+    </row>
+    <row r="456" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C456" s="3"/>
       <c r="D456" s="3"/>
       <c r="E456" s="3"/>
@@ -35596,8 +37568,12 @@
       <c r="BT456" s="3"/>
       <c r="BU456" s="3"/>
       <c r="BV456" s="3"/>
-    </row>
-    <row r="457" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW456" s="3"/>
+      <c r="BX456" s="3"/>
+      <c r="BY456" s="3"/>
+      <c r="BZ456" s="3"/>
+    </row>
+    <row r="457" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C457" s="3"/>
       <c r="D457" s="3"/>
       <c r="E457" s="3"/>
@@ -35670,8 +37646,12 @@
       <c r="BT457" s="3"/>
       <c r="BU457" s="3"/>
       <c r="BV457" s="3"/>
-    </row>
-    <row r="458" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW457" s="3"/>
+      <c r="BX457" s="3"/>
+      <c r="BY457" s="3"/>
+      <c r="BZ457" s="3"/>
+    </row>
+    <row r="458" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C458" s="3"/>
       <c r="D458" s="3"/>
       <c r="E458" s="3"/>
@@ -35744,8 +37724,12 @@
       <c r="BT458" s="3"/>
       <c r="BU458" s="3"/>
       <c r="BV458" s="3"/>
-    </row>
-    <row r="459" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW458" s="3"/>
+      <c r="BX458" s="3"/>
+      <c r="BY458" s="3"/>
+      <c r="BZ458" s="3"/>
+    </row>
+    <row r="459" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C459" s="3"/>
       <c r="D459" s="3"/>
       <c r="E459" s="3"/>
@@ -35818,8 +37802,12 @@
       <c r="BT459" s="3"/>
       <c r="BU459" s="3"/>
       <c r="BV459" s="3"/>
-    </row>
-    <row r="460" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW459" s="3"/>
+      <c r="BX459" s="3"/>
+      <c r="BY459" s="3"/>
+      <c r="BZ459" s="3"/>
+    </row>
+    <row r="460" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C460" s="3"/>
       <c r="D460" s="3"/>
       <c r="E460" s="3"/>
@@ -35892,8 +37880,12 @@
       <c r="BT460" s="3"/>
       <c r="BU460" s="3"/>
       <c r="BV460" s="3"/>
-    </row>
-    <row r="461" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW460" s="3"/>
+      <c r="BX460" s="3"/>
+      <c r="BY460" s="3"/>
+      <c r="BZ460" s="3"/>
+    </row>
+    <row r="461" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C461" s="3"/>
       <c r="D461" s="3"/>
       <c r="E461" s="3"/>
@@ -35966,8 +37958,12 @@
       <c r="BT461" s="3"/>
       <c r="BU461" s="3"/>
       <c r="BV461" s="3"/>
-    </row>
-    <row r="462" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW461" s="3"/>
+      <c r="BX461" s="3"/>
+      <c r="BY461" s="3"/>
+      <c r="BZ461" s="3"/>
+    </row>
+    <row r="462" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C462" s="3"/>
       <c r="D462" s="3"/>
       <c r="E462" s="3"/>
@@ -36040,8 +38036,12 @@
       <c r="BT462" s="3"/>
       <c r="BU462" s="3"/>
       <c r="BV462" s="3"/>
-    </row>
-    <row r="463" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW462" s="3"/>
+      <c r="BX462" s="3"/>
+      <c r="BY462" s="3"/>
+      <c r="BZ462" s="3"/>
+    </row>
+    <row r="463" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C463" s="3"/>
       <c r="D463" s="3"/>
       <c r="E463" s="3"/>
@@ -36114,8 +38114,12 @@
       <c r="BT463" s="3"/>
       <c r="BU463" s="3"/>
       <c r="BV463" s="3"/>
-    </row>
-    <row r="464" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW463" s="3"/>
+      <c r="BX463" s="3"/>
+      <c r="BY463" s="3"/>
+      <c r="BZ463" s="3"/>
+    </row>
+    <row r="464" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C464" s="3"/>
       <c r="D464" s="3"/>
       <c r="E464" s="3"/>
@@ -36188,8 +38192,12 @@
       <c r="BT464" s="3"/>
       <c r="BU464" s="3"/>
       <c r="BV464" s="3"/>
-    </row>
-    <row r="465" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW464" s="3"/>
+      <c r="BX464" s="3"/>
+      <c r="BY464" s="3"/>
+      <c r="BZ464" s="3"/>
+    </row>
+    <row r="465" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C465" s="3"/>
       <c r="D465" s="3"/>
       <c r="E465" s="3"/>
@@ -36262,8 +38270,12 @@
       <c r="BT465" s="3"/>
       <c r="BU465" s="3"/>
       <c r="BV465" s="3"/>
-    </row>
-    <row r="466" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW465" s="3"/>
+      <c r="BX465" s="3"/>
+      <c r="BY465" s="3"/>
+      <c r="BZ465" s="3"/>
+    </row>
+    <row r="466" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C466" s="3"/>
       <c r="D466" s="3"/>
       <c r="E466" s="3"/>
@@ -36336,8 +38348,12 @@
       <c r="BT466" s="3"/>
       <c r="BU466" s="3"/>
       <c r="BV466" s="3"/>
-    </row>
-    <row r="467" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW466" s="3"/>
+      <c r="BX466" s="3"/>
+      <c r="BY466" s="3"/>
+      <c r="BZ466" s="3"/>
+    </row>
+    <row r="467" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C467" s="3"/>
       <c r="D467" s="3"/>
       <c r="E467" s="3"/>
@@ -36410,8 +38426,12 @@
       <c r="BT467" s="3"/>
       <c r="BU467" s="3"/>
       <c r="BV467" s="3"/>
-    </row>
-    <row r="468" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW467" s="3"/>
+      <c r="BX467" s="3"/>
+      <c r="BY467" s="3"/>
+      <c r="BZ467" s="3"/>
+    </row>
+    <row r="468" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C468" s="3"/>
       <c r="D468" s="3"/>
       <c r="E468" s="3"/>
@@ -36484,8 +38504,12 @@
       <c r="BT468" s="3"/>
       <c r="BU468" s="3"/>
       <c r="BV468" s="3"/>
-    </row>
-    <row r="469" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW468" s="3"/>
+      <c r="BX468" s="3"/>
+      <c r="BY468" s="3"/>
+      <c r="BZ468" s="3"/>
+    </row>
+    <row r="469" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C469" s="3"/>
       <c r="D469" s="3"/>
       <c r="E469" s="3"/>
@@ -36558,8 +38582,12 @@
       <c r="BT469" s="3"/>
       <c r="BU469" s="3"/>
       <c r="BV469" s="3"/>
-    </row>
-    <row r="470" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW469" s="3"/>
+      <c r="BX469" s="3"/>
+      <c r="BY469" s="3"/>
+      <c r="BZ469" s="3"/>
+    </row>
+    <row r="470" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C470" s="3"/>
       <c r="D470" s="3"/>
       <c r="E470" s="3"/>
@@ -36632,8 +38660,12 @@
       <c r="BT470" s="3"/>
       <c r="BU470" s="3"/>
       <c r="BV470" s="3"/>
-    </row>
-    <row r="471" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW470" s="3"/>
+      <c r="BX470" s="3"/>
+      <c r="BY470" s="3"/>
+      <c r="BZ470" s="3"/>
+    </row>
+    <row r="471" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C471" s="3"/>
       <c r="D471" s="3"/>
       <c r="E471" s="3"/>
@@ -36706,8 +38738,12 @@
       <c r="BT471" s="3"/>
       <c r="BU471" s="3"/>
       <c r="BV471" s="3"/>
-    </row>
-    <row r="472" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW471" s="3"/>
+      <c r="BX471" s="3"/>
+      <c r="BY471" s="3"/>
+      <c r="BZ471" s="3"/>
+    </row>
+    <row r="472" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C472" s="3"/>
       <c r="D472" s="3"/>
       <c r="E472" s="3"/>
@@ -36780,8 +38816,12 @@
       <c r="BT472" s="3"/>
       <c r="BU472" s="3"/>
       <c r="BV472" s="3"/>
-    </row>
-    <row r="473" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW472" s="3"/>
+      <c r="BX472" s="3"/>
+      <c r="BY472" s="3"/>
+      <c r="BZ472" s="3"/>
+    </row>
+    <row r="473" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C473" s="3"/>
       <c r="D473" s="3"/>
       <c r="E473" s="3"/>
@@ -36854,8 +38894,12 @@
       <c r="BT473" s="3"/>
       <c r="BU473" s="3"/>
       <c r="BV473" s="3"/>
-    </row>
-    <row r="474" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW473" s="3"/>
+      <c r="BX473" s="3"/>
+      <c r="BY473" s="3"/>
+      <c r="BZ473" s="3"/>
+    </row>
+    <row r="474" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C474" s="3"/>
       <c r="D474" s="3"/>
       <c r="E474" s="3"/>
@@ -36928,8 +38972,12 @@
       <c r="BT474" s="3"/>
       <c r="BU474" s="3"/>
       <c r="BV474" s="3"/>
-    </row>
-    <row r="475" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW474" s="3"/>
+      <c r="BX474" s="3"/>
+      <c r="BY474" s="3"/>
+      <c r="BZ474" s="3"/>
+    </row>
+    <row r="475" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C475" s="3"/>
       <c r="D475" s="3"/>
       <c r="E475" s="3"/>
@@ -37002,8 +39050,12 @@
       <c r="BT475" s="3"/>
       <c r="BU475" s="3"/>
       <c r="BV475" s="3"/>
-    </row>
-    <row r="476" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW475" s="3"/>
+      <c r="BX475" s="3"/>
+      <c r="BY475" s="3"/>
+      <c r="BZ475" s="3"/>
+    </row>
+    <row r="476" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C476" s="3"/>
       <c r="D476" s="3"/>
       <c r="E476" s="3"/>
@@ -37076,8 +39128,12 @@
       <c r="BT476" s="3"/>
       <c r="BU476" s="3"/>
       <c r="BV476" s="3"/>
-    </row>
-    <row r="477" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW476" s="3"/>
+      <c r="BX476" s="3"/>
+      <c r="BY476" s="3"/>
+      <c r="BZ476" s="3"/>
+    </row>
+    <row r="477" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C477" s="3"/>
       <c r="D477" s="3"/>
       <c r="E477" s="3"/>
@@ -37150,8 +39206,12 @@
       <c r="BT477" s="3"/>
       <c r="BU477" s="3"/>
       <c r="BV477" s="3"/>
-    </row>
-    <row r="478" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW477" s="3"/>
+      <c r="BX477" s="3"/>
+      <c r="BY477" s="3"/>
+      <c r="BZ477" s="3"/>
+    </row>
+    <row r="478" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C478" s="3"/>
       <c r="D478" s="3"/>
       <c r="E478" s="3"/>
@@ -37224,8 +39284,12 @@
       <c r="BT478" s="3"/>
       <c r="BU478" s="3"/>
       <c r="BV478" s="3"/>
-    </row>
-    <row r="479" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW478" s="3"/>
+      <c r="BX478" s="3"/>
+      <c r="BY478" s="3"/>
+      <c r="BZ478" s="3"/>
+    </row>
+    <row r="479" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C479" s="3"/>
       <c r="D479" s="3"/>
       <c r="E479" s="3"/>
@@ -37298,8 +39362,12 @@
       <c r="BT479" s="3"/>
       <c r="BU479" s="3"/>
       <c r="BV479" s="3"/>
-    </row>
-    <row r="480" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW479" s="3"/>
+      <c r="BX479" s="3"/>
+      <c r="BY479" s="3"/>
+      <c r="BZ479" s="3"/>
+    </row>
+    <row r="480" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C480" s="3"/>
       <c r="D480" s="3"/>
       <c r="E480" s="3"/>
@@ -37372,8 +39440,12 @@
       <c r="BT480" s="3"/>
       <c r="BU480" s="3"/>
       <c r="BV480" s="3"/>
-    </row>
-    <row r="481" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW480" s="3"/>
+      <c r="BX480" s="3"/>
+      <c r="BY480" s="3"/>
+      <c r="BZ480" s="3"/>
+    </row>
+    <row r="481" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C481" s="3"/>
       <c r="D481" s="3"/>
       <c r="E481" s="3"/>
@@ -37446,8 +39518,12 @@
       <c r="BT481" s="3"/>
       <c r="BU481" s="3"/>
       <c r="BV481" s="3"/>
-    </row>
-    <row r="482" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW481" s="3"/>
+      <c r="BX481" s="3"/>
+      <c r="BY481" s="3"/>
+      <c r="BZ481" s="3"/>
+    </row>
+    <row r="482" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C482" s="3"/>
       <c r="D482" s="3"/>
       <c r="E482" s="3"/>
@@ -37520,8 +39596,12 @@
       <c r="BT482" s="3"/>
       <c r="BU482" s="3"/>
       <c r="BV482" s="3"/>
-    </row>
-    <row r="483" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW482" s="3"/>
+      <c r="BX482" s="3"/>
+      <c r="BY482" s="3"/>
+      <c r="BZ482" s="3"/>
+    </row>
+    <row r="483" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C483" s="3"/>
       <c r="D483" s="3"/>
       <c r="E483" s="3"/>
@@ -37594,8 +39674,12 @@
       <c r="BT483" s="3"/>
       <c r="BU483" s="3"/>
       <c r="BV483" s="3"/>
-    </row>
-    <row r="484" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW483" s="3"/>
+      <c r="BX483" s="3"/>
+      <c r="BY483" s="3"/>
+      <c r="BZ483" s="3"/>
+    </row>
+    <row r="484" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C484" s="3"/>
       <c r="D484" s="3"/>
       <c r="E484" s="3"/>
@@ -37668,8 +39752,12 @@
       <c r="BT484" s="3"/>
       <c r="BU484" s="3"/>
       <c r="BV484" s="3"/>
-    </row>
-    <row r="485" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW484" s="3"/>
+      <c r="BX484" s="3"/>
+      <c r="BY484" s="3"/>
+      <c r="BZ484" s="3"/>
+    </row>
+    <row r="485" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C485" s="3"/>
       <c r="D485" s="3"/>
       <c r="E485" s="3"/>
@@ -37742,8 +39830,12 @@
       <c r="BT485" s="3"/>
       <c r="BU485" s="3"/>
       <c r="BV485" s="3"/>
-    </row>
-    <row r="486" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW485" s="3"/>
+      <c r="BX485" s="3"/>
+      <c r="BY485" s="3"/>
+      <c r="BZ485" s="3"/>
+    </row>
+    <row r="486" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C486" s="3"/>
       <c r="D486" s="3"/>
       <c r="E486" s="3"/>
@@ -37816,8 +39908,12 @@
       <c r="BT486" s="3"/>
       <c r="BU486" s="3"/>
       <c r="BV486" s="3"/>
-    </row>
-    <row r="487" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW486" s="3"/>
+      <c r="BX486" s="3"/>
+      <c r="BY486" s="3"/>
+      <c r="BZ486" s="3"/>
+    </row>
+    <row r="487" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C487" s="3"/>
       <c r="D487" s="3"/>
       <c r="E487" s="3"/>
@@ -37890,8 +39986,12 @@
       <c r="BT487" s="3"/>
       <c r="BU487" s="3"/>
       <c r="BV487" s="3"/>
-    </row>
-    <row r="488" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW487" s="3"/>
+      <c r="BX487" s="3"/>
+      <c r="BY487" s="3"/>
+      <c r="BZ487" s="3"/>
+    </row>
+    <row r="488" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C488" s="3"/>
       <c r="D488" s="3"/>
       <c r="E488" s="3"/>
@@ -37964,8 +40064,12 @@
       <c r="BT488" s="3"/>
       <c r="BU488" s="3"/>
       <c r="BV488" s="3"/>
-    </row>
-    <row r="489" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW488" s="3"/>
+      <c r="BX488" s="3"/>
+      <c r="BY488" s="3"/>
+      <c r="BZ488" s="3"/>
+    </row>
+    <row r="489" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C489" s="3"/>
       <c r="D489" s="3"/>
       <c r="E489" s="3"/>
@@ -38038,8 +40142,12 @@
       <c r="BT489" s="3"/>
       <c r="BU489" s="3"/>
       <c r="BV489" s="3"/>
-    </row>
-    <row r="490" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW489" s="3"/>
+      <c r="BX489" s="3"/>
+      <c r="BY489" s="3"/>
+      <c r="BZ489" s="3"/>
+    </row>
+    <row r="490" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C490" s="3"/>
       <c r="D490" s="3"/>
       <c r="E490" s="3"/>
@@ -38112,8 +40220,12 @@
       <c r="BT490" s="3"/>
       <c r="BU490" s="3"/>
       <c r="BV490" s="3"/>
-    </row>
-    <row r="491" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW490" s="3"/>
+      <c r="BX490" s="3"/>
+      <c r="BY490" s="3"/>
+      <c r="BZ490" s="3"/>
+    </row>
+    <row r="491" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C491" s="3"/>
       <c r="D491" s="3"/>
       <c r="E491" s="3"/>
@@ -38186,8 +40298,12 @@
       <c r="BT491" s="3"/>
       <c r="BU491" s="3"/>
       <c r="BV491" s="3"/>
-    </row>
-    <row r="492" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW491" s="3"/>
+      <c r="BX491" s="3"/>
+      <c r="BY491" s="3"/>
+      <c r="BZ491" s="3"/>
+    </row>
+    <row r="492" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C492" s="3"/>
       <c r="D492" s="3"/>
       <c r="E492" s="3"/>
@@ -38260,8 +40376,12 @@
       <c r="BT492" s="3"/>
       <c r="BU492" s="3"/>
       <c r="BV492" s="3"/>
-    </row>
-    <row r="493" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW492" s="3"/>
+      <c r="BX492" s="3"/>
+      <c r="BY492" s="3"/>
+      <c r="BZ492" s="3"/>
+    </row>
+    <row r="493" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C493" s="3"/>
       <c r="D493" s="3"/>
       <c r="E493" s="3"/>
@@ -38334,8 +40454,12 @@
       <c r="BT493" s="3"/>
       <c r="BU493" s="3"/>
       <c r="BV493" s="3"/>
-    </row>
-    <row r="494" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW493" s="3"/>
+      <c r="BX493" s="3"/>
+      <c r="BY493" s="3"/>
+      <c r="BZ493" s="3"/>
+    </row>
+    <row r="494" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C494" s="3"/>
       <c r="D494" s="3"/>
       <c r="E494" s="3"/>
@@ -38408,8 +40532,12 @@
       <c r="BT494" s="3"/>
       <c r="BU494" s="3"/>
       <c r="BV494" s="3"/>
-    </row>
-    <row r="495" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW494" s="3"/>
+      <c r="BX494" s="3"/>
+      <c r="BY494" s="3"/>
+      <c r="BZ494" s="3"/>
+    </row>
+    <row r="495" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C495" s="3"/>
       <c r="D495" s="3"/>
       <c r="E495" s="3"/>
@@ -38482,8 +40610,12 @@
       <c r="BT495" s="3"/>
       <c r="BU495" s="3"/>
       <c r="BV495" s="3"/>
-    </row>
-    <row r="496" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW495" s="3"/>
+      <c r="BX495" s="3"/>
+      <c r="BY495" s="3"/>
+      <c r="BZ495" s="3"/>
+    </row>
+    <row r="496" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C496" s="3"/>
       <c r="D496" s="3"/>
       <c r="E496" s="3"/>
@@ -38556,8 +40688,12 @@
       <c r="BT496" s="3"/>
       <c r="BU496" s="3"/>
       <c r="BV496" s="3"/>
-    </row>
-    <row r="497" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW496" s="3"/>
+      <c r="BX496" s="3"/>
+      <c r="BY496" s="3"/>
+      <c r="BZ496" s="3"/>
+    </row>
+    <row r="497" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C497" s="3"/>
       <c r="D497" s="3"/>
       <c r="E497" s="3"/>
@@ -38630,8 +40766,12 @@
       <c r="BT497" s="3"/>
       <c r="BU497" s="3"/>
       <c r="BV497" s="3"/>
-    </row>
-    <row r="498" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW497" s="3"/>
+      <c r="BX497" s="3"/>
+      <c r="BY497" s="3"/>
+      <c r="BZ497" s="3"/>
+    </row>
+    <row r="498" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C498" s="3"/>
       <c r="D498" s="3"/>
       <c r="E498" s="3"/>
@@ -38704,8 +40844,12 @@
       <c r="BT498" s="3"/>
       <c r="BU498" s="3"/>
       <c r="BV498" s="3"/>
-    </row>
-    <row r="499" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW498" s="3"/>
+      <c r="BX498" s="3"/>
+      <c r="BY498" s="3"/>
+      <c r="BZ498" s="3"/>
+    </row>
+    <row r="499" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C499" s="3"/>
       <c r="D499" s="3"/>
       <c r="E499" s="3"/>
@@ -38778,8 +40922,12 @@
       <c r="BT499" s="3"/>
       <c r="BU499" s="3"/>
       <c r="BV499" s="3"/>
-    </row>
-    <row r="500" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW499" s="3"/>
+      <c r="BX499" s="3"/>
+      <c r="BY499" s="3"/>
+      <c r="BZ499" s="3"/>
+    </row>
+    <row r="500" spans="3:78" x14ac:dyDescent="0.2">
       <c r="C500" s="3"/>
       <c r="D500" s="3"/>
       <c r="E500" s="3"/>
@@ -38852,6 +41000,10 @@
       <c r="BT500" s="3"/>
       <c r="BU500" s="3"/>
       <c r="BV500" s="3"/>
+      <c r="BW500" s="3"/>
+      <c r="BX500" s="3"/>
+      <c r="BY500" s="3"/>
+      <c r="BZ500" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
